--- a/docs/ballpark/addition-ballpark-template.xlsx
+++ b/docs/ballpark/addition-ballpark-template.xlsx
@@ -16,10 +16,11 @@
     <sheet name="Calibration" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="LaborCost" vbProcedure="false">Rates!$C$9</definedName>
-    <definedName function="false" hidden="false" name="MarkupCodes" vbProcedure="false">Rates!$A$4:$A$8</definedName>
-    <definedName function="false" hidden="false" name="MarkupVals" vbProcedure="false">Rates!$C$4:$C$8</definedName>
+    <definedName function="false" hidden="false" name="LaborCost" vbProcedure="false">Rates!$C$11</definedName>
+    <definedName function="false" hidden="false" name="MarkupCodes" vbProcedure="false">Rates!$A$4:$A$9</definedName>
+    <definedName function="false" hidden="false" name="MarkupVals" vbProcedure="false">Rates!$C$4:$C$9</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Basement" vbProcedure="false">Calculator!$B$12</definedName>
+    <definedName function="false" hidden="false" name="p_Addition_Contingency_Rate" vbProcedure="false">Calculator!$B$33</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Crawl_Space" vbProcedure="false">Calculator!$B$10</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Depth" vbProcedure="false">Calculator!$B$6</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Detached" vbProcedure="false">Calculator!$B$9</definedName>
@@ -47,7 +48,7 @@
     <definedName function="false" hidden="false" name="p_Addition_Wall_Openings" vbProcedure="false">Calculator!$B$24</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Width" vbProcedure="false">Calculator!$B$5</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Windows" vbProcedure="false">Calculator!$B$19</definedName>
-    <definedName function="false" hidden="false" name="RangePct" vbProcedure="false">Rates!$C$12</definedName>
+    <definedName function="false" hidden="false" name="RangePct" vbProcedure="false">Rates!$C$14</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -59,12 +60,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="501">
   <si>
     <t xml:space="preserve">Addition Ballpark Template — DRAFT for review</t>
   </si>
   <si>
-    <t xml:space="preserve">Deitemeyer Brothers · General Construction · drafted 27 Sep 2026</t>
+    <t xml:space="preserve">Deitemeyer Brothers · General Construction · drafted 27 Sep 2026 · decisions applied 28 Sep 2026</t>
   </si>
   <si>
     <t xml:space="preserve">What this is</t>
@@ -88,7 +89,7 @@
     <t xml:space="preserve">2. Template tab: every JobTread line with its cost group, cost code, unit, exact quantity formula, and unit cost and price per tier.</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Parameters tab: the 28 JobTread job parameters. Each starts with 'Addition ' so it never collides with a bath or kitchen on the same job.</t>
+    <t xml:space="preserve">3. Parameters tab: the 28 site-visit parameters plus the contingency rate, which the estimator sets. Each starts with 'Addition ' so it never collides with a bath or kitchen on the same job.</t>
   </si>
   <si>
     <t xml:space="preserve">4. Rates tab: markup by cost type, and the ± band. It is set to ±20% for additions.</t>
@@ -118,16 +119,22 @@
     <t xml:space="preserve">Additions also vary more than bathrooms: foundation, roof and siding choices move the price more than the finish tier does. So the ballpark is quoted at ±20%, and every addition goes on to the Design &amp; Pricing Agreement.</t>
   </si>
   <si>
-    <t xml:space="preserve">Decisions still open (for Carl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allowance type on the selection lines: cost (marked up like other materials, as drafted), price, or cost plus fee.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name the shingle, siding, window and patio-door product for each tier so sales can show them.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Framing lumber: update the catalog to about $22.50 per SF, or keep the override in this template.</t>
+    <t xml:space="preserve">Decided 28 Sep 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency is its own line on each tier at 10%. The estimator sets the Addition Contingency Rate. The checks compare prices before contingency, because DB's past estimates carried none.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowances are stated as customer prices (JobTread allowance type: price). No total changes; an overage or a credit is simply the difference in price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products per tier: the estimator and the designer name one product per Good / Better / Best cell and lock the grid for six months (draft in the proposal, §9).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Framing lumber: the catalog item Framing/Sheathing Materials is updated to $22.50 per SF (from $17.65), so this template uses the catalog rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every $0 line on an estimate names who supplies it: (by owner), (by others) or (not included).</t>
   </si>
   <si>
     <t xml:space="preserve">Source for every rate: DB's catalog and addition estimates, read from JobTread (read-only) on 27 Sep 2026. See Calibration tab.</t>
@@ -232,30 +239,33 @@
     <t xml:space="preserve">{Addition Crawl Space}</t>
   </si>
   <si>
+    <t xml:space="preserve">Contingency (the Addition Contingency Rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addition Slab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = footed slab with a 6-inch stem wall (garages, slab rooms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{Addition Slab}</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ballpark total</t>
   </si>
   <si>
-    <t xml:space="preserve">Addition Slab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = footed slab with a 6-inch stem wall (garages, slab rooms)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{Addition Slab}</t>
+    <t xml:space="preserve">Addition Basement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = full basement under the addition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{Addition Basement}</t>
   </si>
   <si>
     <t xml:space="preserve">Check: equals Template total</t>
   </si>
   <si>
-    <t xml:space="preserve">Addition Basement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = full basement under the addition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{Addition Basement}</t>
-  </si>
-  <si>
     <t xml:space="preserve">Addition Piers</t>
   </si>
   <si>
@@ -265,42 +275,42 @@
     <t xml:space="preserve">{Addition Piers}</t>
   </si>
   <si>
+    <t xml:space="preserve">Addition Site Excavation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = DB digs, grades or trenches (tight access, slope, drainage). 0 = the concrete sub's price covers it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{Addition Site Excavation}</t>
+  </si>
+  <si>
     <t xml:space="preserve">Budget range shown to customer</t>
   </si>
   <si>
-    <t xml:space="preserve">Addition Site Excavation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = DB digs, grades or trenches (tight access, slope, drainage). 0 = the concrete sub's price covers it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{Addition Site Excavation}</t>
+    <t xml:space="preserve">Addition Roof Tie-In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = none (detached); 1 = simple shed or gable against the house; 2 = cross-gable or valley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{Addition Roof Tie-In}</t>
   </si>
   <si>
     <t xml:space="preserve">Low</t>
   </si>
   <si>
-    <t xml:space="preserve">Addition Roof Tie-In</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 = none (detached); 1 = simple shed or gable against the house; 2 = cross-gable or valley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{Addition Roof Tie-In}</t>
+    <t xml:space="preserve">Addition Electrical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = wired: outlets, lights, switches. 0 = shell only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{Addition Electrical}</t>
   </si>
   <si>
     <t xml:space="preserve">High</t>
   </si>
   <si>
-    <t xml:space="preserve">Addition Electrical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = wired: outlets, lights, switches. 0 = shell only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{Addition Electrical}</t>
-  </si>
-  <si>
     <t xml:space="preserve">Addition Drywall</t>
   </si>
   <si>
@@ -310,30 +320,30 @@
     <t xml:space="preserve">{Addition Drywall}</t>
   </si>
   <si>
+    <t xml:space="preserve">Addition Living Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = finished living space: flooring, trim and more coordination. 0 = garage, porch or shell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{Addition Living Space}</t>
+  </si>
+  <si>
     <t xml:space="preserve">Totals exclude sales tax and the design agreement fee.</t>
   </si>
   <si>
-    <t xml:space="preserve">Addition Living Space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = finished living space: flooring, trim and more coordination. 0 = garage, porch or shell.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{Addition Living Space}</t>
+    <t xml:space="preserve">Addition Windows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New windows in the addition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{Addition Windows}</t>
   </si>
   <si>
     <t xml:space="preserve">The ± band is set on the Rates tab.</t>
   </si>
   <si>
-    <t xml:space="preserve">Addition Windows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New windows in the addition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{Addition Windows}</t>
-  </si>
-  <si>
     <t xml:space="preserve">Addition Exterior Doors</t>
   </si>
   <si>
@@ -451,6 +461,15 @@
     <t xml:space="preserve">{Addition Travel Hours}</t>
   </si>
   <si>
+    <t xml:space="preserve">Addition Contingency Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency as a % of the tier total, set by the estimator: 10 for additions and structural work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{Addition Contingency Rate}</t>
+  </si>
+  <si>
     <t xml:space="preserve">JobTread build sheet: cost group "BALLPARK — Addition"</t>
   </si>
   <si>
@@ -514,7 +533,7 @@
     <t xml:space="preserve">Best total</t>
   </si>
   <si>
-    <t xml:space="preserve">Allowance line?</t>
+    <t xml:space="preserve">Allowance type</t>
   </si>
   <si>
     <t xml:space="preserve">Note</t>
@@ -730,7 +749,7 @@
     <t xml:space="preserve">{Addition Width}*{Addition Depth}*{Addition Stories}</t>
   </si>
   <si>
-    <t xml:space="preserve">$22.50 cost per SF of floor, from DB's two most recent lumber quotes ($22.8 and $22.4). The catalog item is still $17.65, which older estimates used.</t>
+    <t xml:space="preserve">DB catalog item, updated to $22.50 cost per SF of floor (from $17.65) to match DB's two most recent lumber quotes ($22.8 and $22.4). Check it against the latest quote every quarter.</t>
   </si>
   <si>
     <t xml:space="preserve">Header &amp; Opening Material</t>
@@ -835,7 +854,7 @@
     <t xml:space="preserve">Garage Door</t>
   </si>
   <si>
-    <t xml:space="preserve">Catalog Garage Door, installed by the sub. Neither garage estimate priced its overhead doors.</t>
+    <t xml:space="preserve">Catalog Garage Door, installed by the sub. Neither garage estimate priced its overhead doors; if the owner supplies them, keep the line at $0 and name it (by owner).</t>
   </si>
   <si>
     <t xml:space="preserve">Garage Door Wrapping</t>
@@ -1018,7 +1037,7 @@
     <t xml:space="preserve">ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In}</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes</t>
+    <t xml:space="preserve">Price</t>
   </si>
   <si>
     <t xml:space="preserve">Per square, including underlayment, ice and water, starter, ridge and drip edge. Good matches OC Duration ($203–$240 cost per square with accessories on 258410 and 25-8197). Stone-coated steel or PVC roofs cost 2–3 times Best; price those by hand.</t>
@@ -1051,6 +1070,42 @@
     <t xml:space="preserve">Good and Better are LVP; Best is engineered hardwood or premium LVP. All installed by the DB crew.</t>
   </si>
   <si>
+    <t xml:space="preserve">BALLPARK — Addition &gt; Finish Level (select one) &gt; Good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency — Good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{Addition Contingency Rate}/100*((1)*290 + (6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30))*100 + (1)*217.5 + (4 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/200))*100 + (1 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/400) + 3*{Addition Living Space})*435 + (4*(1 - {Addition Detached}) + ceil({Addition Structure Removed}/3) + 8*{Addition Wall Openings})*100 + ({Addition Dumpster Loads})*450 + (2 + 2*{Addition Living Space})*100 + ({Addition Travel Hours})*100 + ({Addition Utility Trench})*17.4 + (16*{Addition Site Excavation})*100 + (2*{Addition Site Excavation})*282.75 + ({Addition Crawl Space}*{Addition Width}*{Addition Depth})*26.2015 + ({Addition Slab}*{Addition Width}*{Addition Depth})*30.45 + ({Addition Basement}*{Addition Width}*{Addition Depth})*47.85 + ({Addition Piers})*725 + (3*{Addition Piers})*100 + ({Addition Width}*{Addition Depth}*{Addition Stories})*32.625 + ({Addition Wall Openings})*580 + (ceil({Addition Width}*{Addition Depth}*{Addition Stories}/6) + 8*{Addition Wall Openings} + 8*{Addition Roof Tie-In})*100 + ({Addition Width} + {Addition Depth} + 20)*11.9625 + ({Addition Width} + {Addition Depth} + 20)*5.075 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*11.6 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*5.85 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*100 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*232 + (2*(1 - {Addition Detached}))*217.5 + (ceil(2.5*{Addition Windows}))*100 + ({Addition Exterior Doors})*1783.5 + ({Addition Garage Doors})*1690 + ({Addition Garage Doors})*152.25 + (8*{Addition Exterior Doors} + 8*{Addition Patio Doors} + 3*{Addition Interior Doors})*100 + ({Addition Plumbing Fixtures})*362.5 + (9*{Addition Plumbing Fixtures})*100 + ({Addition HVAC Extend})*1703 + ({Addition HVAC New Unit})*9750 + ({Addition Electrical}*{Addition Width}*{Addition Depth}*{Addition Stories})*3.7845 + ({Addition Electrical}*(8 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/16)))*100 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*11.076 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.479 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.8995 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/12))*100 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/60))*123.25 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/15))*100 + ({Addition Interior Doors})*580 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.0875 + ({Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/25))*100 + ({Addition Living Space}*ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/12))*65.9605 + ({Addition Living Space}*({Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*53.8095 + ({Addition Living Space}*(4 + ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/8) + {Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*100 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*304.5 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*137.75 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*333.5 + ({Addition Windows})*688.75 + ({Addition Patio Doors})*2537.5 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*5.075)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency: the rate times this tier's whole price before contingency. JobTread formulas cannot reference other lines, so the subtotal is spelled out; regenerate this formula (run the build script) after any rate change. Unit price $1.00, cost type Other with markup 0, cost code Contingency.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALLPARK — Addition &gt; Finish Level (select one) &gt; Better</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency — Better</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{Addition Contingency Rate}/100*((1)*290 + (6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30))*100 + (1)*217.5 + (4 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/200))*100 + (1 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/400) + 3*{Addition Living Space})*435 + (4*(1 - {Addition Detached}) + ceil({Addition Structure Removed}/3) + 8*{Addition Wall Openings})*100 + ({Addition Dumpster Loads})*450 + (2 + 2*{Addition Living Space})*100 + ({Addition Travel Hours})*100 + ({Addition Utility Trench})*17.4 + (16*{Addition Site Excavation})*100 + (2*{Addition Site Excavation})*282.75 + ({Addition Crawl Space}*{Addition Width}*{Addition Depth})*26.2015 + ({Addition Slab}*{Addition Width}*{Addition Depth})*30.45 + ({Addition Basement}*{Addition Width}*{Addition Depth})*47.85 + ({Addition Piers})*725 + (3*{Addition Piers})*100 + ({Addition Width}*{Addition Depth}*{Addition Stories})*32.625 + ({Addition Wall Openings})*580 + (ceil({Addition Width}*{Addition Depth}*{Addition Stories}/6) + 8*{Addition Wall Openings} + 8*{Addition Roof Tie-In})*100 + ({Addition Width} + {Addition Depth} + 20)*11.9625 + ({Addition Width} + {Addition Depth} + 20)*5.075 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*11.6 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*5.85 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*100 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*232 + (2*(1 - {Addition Detached}))*217.5 + (ceil(2.5*{Addition Windows}))*100 + ({Addition Exterior Doors})*1783.5 + ({Addition Garage Doors})*1690 + ({Addition Garage Doors})*152.25 + (8*{Addition Exterior Doors} + 8*{Addition Patio Doors} + 3*{Addition Interior Doors})*100 + ({Addition Plumbing Fixtures})*362.5 + (9*{Addition Plumbing Fixtures})*100 + ({Addition HVAC Extend})*1703 + ({Addition HVAC New Unit})*9750 + ({Addition Electrical}*{Addition Width}*{Addition Depth}*{Addition Stories})*3.7845 + ({Addition Electrical}*(8 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/16)))*100 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*11.076 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.479 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.8995 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/12))*100 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/60))*123.25 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/15))*100 + ({Addition Interior Doors})*580 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.0875 + ({Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/25))*100 + ({Addition Living Space}*ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/12))*65.9605 + ({Addition Living Space}*({Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*53.8095 + ({Addition Living Space}*(4 + ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/8) + {Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*100 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*355.25 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*137.75 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*464 + ({Addition Windows})*1015 + ({Addition Patio Doors})*3625 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*7.25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALLPARK — Addition &gt; Finish Level (select one) &gt; Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency — Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{Addition Contingency Rate}/100*((1)*290 + (6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30))*100 + (1)*217.5 + (4 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/200))*100 + (1 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/400) + 3*{Addition Living Space})*435 + (4*(1 - {Addition Detached}) + ceil({Addition Structure Removed}/3) + 8*{Addition Wall Openings})*100 + ({Addition Dumpster Loads})*450 + (2 + 2*{Addition Living Space})*100 + ({Addition Travel Hours})*100 + ({Addition Utility Trench})*17.4 + (16*{Addition Site Excavation})*100 + (2*{Addition Site Excavation})*282.75 + ({Addition Crawl Space}*{Addition Width}*{Addition Depth})*26.2015 + ({Addition Slab}*{Addition Width}*{Addition Depth})*30.45 + ({Addition Basement}*{Addition Width}*{Addition Depth})*47.85 + ({Addition Piers})*725 + (3*{Addition Piers})*100 + ({Addition Width}*{Addition Depth}*{Addition Stories})*32.625 + ({Addition Wall Openings})*580 + (ceil({Addition Width}*{Addition Depth}*{Addition Stories}/6) + 8*{Addition Wall Openings} + 8*{Addition Roof Tie-In})*100 + ({Addition Width} + {Addition Depth} + 20)*11.9625 + ({Addition Width} + {Addition Depth} + 20)*5.075 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*11.6 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*5.85 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*100 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*232 + (2*(1 - {Addition Detached}))*217.5 + (ceil(2.5*{Addition Windows}))*100 + ({Addition Exterior Doors})*1783.5 + ({Addition Garage Doors})*1690 + ({Addition Garage Doors})*152.25 + (8*{Addition Exterior Doors} + 8*{Addition Patio Doors} + 3*{Addition Interior Doors})*100 + ({Addition Plumbing Fixtures})*362.5 + (9*{Addition Plumbing Fixtures})*100 + ({Addition HVAC Extend})*1703 + ({Addition HVAC New Unit})*9750 + ({Addition Electrical}*{Addition Width}*{Addition Depth}*{Addition Stories})*3.7845 + ({Addition Electrical}*(8 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/16)))*100 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*11.076 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.479 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.8995 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/12))*100 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/60))*123.25 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/15))*100 + ({Addition Interior Doors})*580 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.0875 + ({Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/25))*100 + ({Addition Living Space}*ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/12))*65.9605 + ({Addition Living Space}*({Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*53.8095 + ({Addition Living Space}*(4 + ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/8) + {Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*100 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*453.85 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*290 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*717.75 + ({Addition Windows})*1595 + ({Addition Patio Doors})*4350 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*13.05)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
@@ -1169,6 +1224,9 @@
   </si>
   <si>
     <t xml:space="preserve">Labor the catalog prices per square or foot (siding, roofing, gutters). JobTread cost type Labor, marked up ×1.45 like the catalog.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Its own line, carried at cost so it can be reported and credited. JobTread cost type Other with the markup set to 0, cost code Contingency.</t>
   </si>
   <si>
     <t xml:space="preserve">Labor cost per hour</t>
@@ -2094,7 +2152,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="120"/>
@@ -2215,7 +2273,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>20</v>
       </c>
@@ -2231,11 +2289,21 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3"/>
+      <c r="A29" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>23</v>
+      <c r="A30" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2254,7 +2322,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
@@ -2267,7 +2335,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2280,7 +2348,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2304,47 +2372,47 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G5" s="14" t="n">
         <f aca="false">SUMIFS(Template!K5:K54,Template!B5:B54,"*Phase 1 -*")</f>
@@ -2361,20 +2429,20 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>16</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G6" s="14" t="n">
         <f aca="false">SUMIFS(Template!K5:K54,Template!B5:B54,"*Phase 2 -*")</f>
@@ -2391,20 +2459,20 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G7" s="14" t="n">
         <f aca="false">SUMIFS(Template!K5:K54,Template!B5:B54,"*Phase 3 -*")</f>
@@ -2421,20 +2489,20 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>8</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" s="14" t="n">
         <f aca="false">SUMIFS(Template!K5:K54,Template!B5:B54,"*Phase 4 -*")</f>
@@ -2451,20 +2519,20 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G9" s="14" t="n">
         <f aca="false">SUM(Template!K55:K60)</f>
@@ -2481,220 +2549,229 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <f aca="false">SUM(G5:G9)</f>
-        <v>70256.81</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <f aca="false">SUM(H5:H9)</f>
-        <v>74302.31</v>
-      </c>
-      <c r="I10" s="16" t="n">
-        <f aca="false">SUM(I5:I9)</f>
-        <v>81977.16</v>
+      <c r="F10" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <f aca="false">SUM(Template!K61:K63)</f>
+        <v>7025.681</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <f aca="false">SUM(Template!O61:O63)</f>
+        <v>7430.231</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <f aca="false">SUM(Template!S61:S63)</f>
+        <v>8197.716</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" s="6"/>
-      <c r="F11" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="17" t="str">
-        <f aca="false">IF(ABS(G10-Template!K61)&lt;0.01,"OK","MISMATCH")</f>
-        <v>OK</v>
-      </c>
-      <c r="H11" s="17" t="str">
-        <f aca="false">IF(ABS(H10-Template!O61)&lt;0.01,"OK","MISMATCH")</f>
-        <v>OK</v>
-      </c>
-      <c r="I11" s="17" t="str">
-        <f aca="false">IF(ABS(I10-Template!S61)&lt;0.01,"OK","MISMATCH")</f>
-        <v>OK</v>
+      <c r="F11" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <f aca="false">SUM(G5:G10)</f>
+        <v>77282.491</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <f aca="false">SUM(H5:H10)</f>
+        <v>81732.541</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <f aca="false">SUM(I5:I10)</f>
+        <v>90174.876</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
+      <c r="F12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="17" t="str">
+        <f aca="false">IF(ABS(G11-Template!K64)&lt;0.01,"OK","MISMATCH")</f>
+        <v>OK</v>
+      </c>
+      <c r="H12" s="17" t="str">
+        <f aca="false">IF(ABS(H11-Template!O64)&lt;0.01,"OK","MISMATCH")</f>
+        <v>OK</v>
+      </c>
+      <c r="I12" s="17" t="str">
+        <f aca="false">IF(ABS(I11-Template!S64)&lt;0.01,"OK","MISMATCH")</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E13" s="6"/>
-      <c r="F13" s="15" t="s">
-        <v>68</v>
-      </c>
+      <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E14" s="6"/>
-      <c r="F14" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <f aca="false">ROUND(G10*(1-RangePct),-2)</f>
-        <v>56200</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <f aca="false">ROUND(H10*(1-RangePct),-2)</f>
-        <v>59400</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <f aca="false">ROUND(I10*(1-RangePct),-2)</f>
-        <v>65600</v>
-      </c>
+      <c r="F14" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G15" s="14" t="n">
-        <f aca="false">ROUND(G10*(1+RangePct),-2)</f>
-        <v>84300</v>
+        <f aca="false">ROUND(G11*(1-RangePct),-2)</f>
+        <v>61800</v>
       </c>
       <c r="H15" s="14" t="n">
-        <f aca="false">ROUND(H10*(1+RangePct),-2)</f>
-        <v>89200</v>
+        <f aca="false">ROUND(H11*(1-RangePct),-2)</f>
+        <v>65400</v>
       </c>
       <c r="I15" s="14" t="n">
-        <f aca="false">ROUND(I10*(1+RangePct),-2)</f>
-        <v>98400</v>
+        <f aca="false">ROUND(I11*(1-RangePct),-2)</f>
+        <v>72100</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
+      <c r="F16" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <f aca="false">ROUND(G11*(1+RangePct),-2)</f>
+        <v>92700</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <f aca="false">ROUND(H11*(1+RangePct),-2)</f>
+        <v>98100</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <f aca="false">ROUND(I11*(1+RangePct),-2)</f>
+        <v>108200</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E17" s="6"/>
-      <c r="F17" s="7" t="s">
-        <v>83</v>
-      </c>
+      <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -2702,35 +2779,37 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
+      <c r="F19" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
@@ -2740,16 +2819,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B21" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
@@ -2759,16 +2838,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
@@ -2778,16 +2857,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
@@ -2797,16 +2876,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
@@ -2816,16 +2895,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -2835,16 +2914,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -2854,16 +2933,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
@@ -2873,16 +2952,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -2892,16 +2971,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -2911,16 +2990,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -2930,16 +3009,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B31" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -2949,22 +3028,41 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2982,7 +3080,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:U64"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -2998,7 +3096,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3023,7 +3121,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3071,67 +3169,67 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3139,19 +3237,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G5" s="20" t="n">
         <f aca="false">1</f>
@@ -3161,7 +3259,7 @@
         <v>200</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J5" s="23" t="n">
         <f aca="false">H5*INDEX(MarkupVals,MATCH(I5,MarkupCodes,0))</f>
@@ -3175,7 +3273,7 @@
         <v>200</v>
       </c>
       <c r="M5" s="22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="N5" s="23" t="n">
         <f aca="false">L5*INDEX(MarkupVals,MATCH(M5,MarkupCodes,0))</f>
@@ -3189,7 +3287,7 @@
         <v>200</v>
       </c>
       <c r="Q5" s="22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="R5" s="23" t="n">
         <f aca="false">P5*INDEX(MarkupVals,MATCH(Q5,MarkupCodes,0))</f>
@@ -3201,7 +3299,7 @@
       </c>
       <c r="T5" s="25"/>
       <c r="U5" s="26" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3209,19 +3307,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="G6" s="20" t="n">
         <f aca="false">6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0)</f>
@@ -3232,7 +3330,7 @@
         <v>55</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J6" s="23" t="n">
         <f aca="false">H6*INDEX(MarkupVals,MATCH(I6,MarkupCodes,0))</f>
@@ -3247,7 +3345,7 @@
         <v>55</v>
       </c>
       <c r="M6" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N6" s="23" t="n">
         <f aca="false">L6*INDEX(MarkupVals,MATCH(M6,MarkupCodes,0))</f>
@@ -3262,7 +3360,7 @@
         <v>55</v>
       </c>
       <c r="Q6" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R6" s="23" t="n">
         <f aca="false">P6*INDEX(MarkupVals,MATCH(Q6,MarkupCodes,0))</f>
@@ -3280,19 +3378,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G7" s="20" t="n">
         <f aca="false">1</f>
@@ -3302,7 +3400,7 @@
         <v>150</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J7" s="23" t="n">
         <f aca="false">H7*INDEX(MarkupVals,MATCH(I7,MarkupCodes,0))</f>
@@ -3316,7 +3414,7 @@
         <v>150</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N7" s="23" t="n">
         <f aca="false">L7*INDEX(MarkupVals,MATCH(M7,MarkupCodes,0))</f>
@@ -3330,7 +3428,7 @@
         <v>150</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R7" s="23" t="n">
         <f aca="false">P7*INDEX(MarkupVals,MATCH(Q7,MarkupCodes,0))</f>
@@ -3348,19 +3446,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="G8" s="20" t="n">
         <f aca="false">4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0)</f>
@@ -3371,7 +3469,7 @@
         <v>55</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J8" s="23" t="n">
         <f aca="false">H8*INDEX(MarkupVals,MATCH(I8,MarkupCodes,0))</f>
@@ -3386,7 +3484,7 @@
         <v>55</v>
       </c>
       <c r="M8" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N8" s="23" t="n">
         <f aca="false">L8*INDEX(MarkupVals,MATCH(M8,MarkupCodes,0))</f>
@@ -3401,7 +3499,7 @@
         <v>55</v>
       </c>
       <c r="Q8" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R8" s="23" t="n">
         <f aca="false">P8*INDEX(MarkupVals,MATCH(Q8,MarkupCodes,0))</f>
@@ -3419,19 +3517,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G9" s="20" t="n">
         <f aca="false">1 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/400,0) + 3*p_Addition_Living_Space</f>
@@ -3441,7 +3539,7 @@
         <v>300</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J9" s="23" t="n">
         <f aca="false">H9*INDEX(MarkupVals,MATCH(I9,MarkupCodes,0))</f>
@@ -3455,7 +3553,7 @@
         <v>300</v>
       </c>
       <c r="M9" s="22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="N9" s="23" t="n">
         <f aca="false">L9*INDEX(MarkupVals,MATCH(M9,MarkupCodes,0))</f>
@@ -3469,7 +3567,7 @@
         <v>300</v>
       </c>
       <c r="Q9" s="22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="R9" s="23" t="n">
         <f aca="false">P9*INDEX(MarkupVals,MATCH(Q9,MarkupCodes,0))</f>
@@ -3481,7 +3579,7 @@
       </c>
       <c r="T9" s="25"/>
       <c r="U9" s="26" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3489,19 +3587,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G10" s="20" t="n">
         <f aca="false">4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings</f>
@@ -3512,7 +3610,7 @@
         <v>55</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J10" s="23" t="n">
         <f aca="false">H10*INDEX(MarkupVals,MATCH(I10,MarkupCodes,0))</f>
@@ -3527,7 +3625,7 @@
         <v>55</v>
       </c>
       <c r="M10" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N10" s="23" t="n">
         <f aca="false">L10*INDEX(MarkupVals,MATCH(M10,MarkupCodes,0))</f>
@@ -3542,7 +3640,7 @@
         <v>55</v>
       </c>
       <c r="Q10" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R10" s="23" t="n">
         <f aca="false">P10*INDEX(MarkupVals,MATCH(Q10,MarkupCodes,0))</f>
@@ -3554,7 +3652,7 @@
       </c>
       <c r="T10" s="25"/>
       <c r="U10" s="26" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3562,19 +3660,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G11" s="20" t="n">
         <f aca="false">p_Addition_Dumpster_Loads</f>
@@ -3584,7 +3682,7 @@
         <v>250</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J11" s="21" t="n">
         <v>450</v>
@@ -3597,7 +3695,7 @@
         <v>250</v>
       </c>
       <c r="M11" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N11" s="21" t="n">
         <v>450</v>
@@ -3610,7 +3708,7 @@
         <v>250</v>
       </c>
       <c r="Q11" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R11" s="21" t="n">
         <v>450</v>
@@ -3621,7 +3719,7 @@
       </c>
       <c r="T11" s="25"/>
       <c r="U11" s="26" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3629,19 +3727,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="G12" s="20" t="n">
         <f aca="false">2 + 2*p_Addition_Living_Space</f>
@@ -3652,7 +3750,7 @@
         <v>55</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J12" s="23" t="n">
         <f aca="false">H12*INDEX(MarkupVals,MATCH(I12,MarkupCodes,0))</f>
@@ -3667,7 +3765,7 @@
         <v>55</v>
       </c>
       <c r="M12" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N12" s="23" t="n">
         <f aca="false">L12*INDEX(MarkupVals,MATCH(M12,MarkupCodes,0))</f>
@@ -3682,7 +3780,7 @@
         <v>55</v>
       </c>
       <c r="Q12" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R12" s="23" t="n">
         <f aca="false">P12*INDEX(MarkupVals,MATCH(Q12,MarkupCodes,0))</f>
@@ -3700,19 +3798,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G13" s="20" t="n">
         <f aca="false">p_Addition_Travel_Hours</f>
@@ -3723,7 +3821,7 @@
         <v>55</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J13" s="23" t="n">
         <f aca="false">H13*INDEX(MarkupVals,MATCH(I13,MarkupCodes,0))</f>
@@ -3738,7 +3836,7 @@
         <v>55</v>
       </c>
       <c r="M13" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N13" s="23" t="n">
         <f aca="false">L13*INDEX(MarkupVals,MATCH(M13,MarkupCodes,0))</f>
@@ -3753,7 +3851,7 @@
         <v>55</v>
       </c>
       <c r="Q13" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R13" s="23" t="n">
         <f aca="false">P13*INDEX(MarkupVals,MATCH(Q13,MarkupCodes,0))</f>
@@ -3771,19 +3869,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G14" s="20" t="n">
         <f aca="false">p_Addition_Utility_Trench</f>
@@ -3793,7 +3891,7 @@
         <v>12</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J14" s="23" t="n">
         <f aca="false">H14*INDEX(MarkupVals,MATCH(I14,MarkupCodes,0))</f>
@@ -3807,7 +3905,7 @@
         <v>12</v>
       </c>
       <c r="M14" s="22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="N14" s="23" t="n">
         <f aca="false">L14*INDEX(MarkupVals,MATCH(M14,MarkupCodes,0))</f>
@@ -3821,7 +3919,7 @@
         <v>12</v>
       </c>
       <c r="Q14" s="22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="R14" s="23" t="n">
         <f aca="false">P14*INDEX(MarkupVals,MATCH(Q14,MarkupCodes,0))</f>
@@ -3833,7 +3931,7 @@
       </c>
       <c r="T14" s="25"/>
       <c r="U14" s="26" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3841,19 +3939,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G15" s="20" t="n">
         <f aca="false">16*p_Addition_Site_Excavation</f>
@@ -3864,7 +3962,7 @@
         <v>55</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J15" s="23" t="n">
         <f aca="false">H15*INDEX(MarkupVals,MATCH(I15,MarkupCodes,0))</f>
@@ -3879,7 +3977,7 @@
         <v>55</v>
       </c>
       <c r="M15" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N15" s="23" t="n">
         <f aca="false">L15*INDEX(MarkupVals,MATCH(M15,MarkupCodes,0))</f>
@@ -3894,7 +3992,7 @@
         <v>55</v>
       </c>
       <c r="Q15" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R15" s="23" t="n">
         <f aca="false">P15*INDEX(MarkupVals,MATCH(Q15,MarkupCodes,0))</f>
@@ -3906,7 +4004,7 @@
       </c>
       <c r="T15" s="25"/>
       <c r="U15" s="26" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3914,19 +4012,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="G16" s="20" t="n">
         <f aca="false">2*p_Addition_Site_Excavation</f>
@@ -3936,7 +4034,7 @@
         <v>195</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J16" s="23" t="n">
         <f aca="false">H16*INDEX(MarkupVals,MATCH(I16,MarkupCodes,0))</f>
@@ -3950,7 +4048,7 @@
         <v>195</v>
       </c>
       <c r="M16" s="22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="N16" s="23" t="n">
         <f aca="false">L16*INDEX(MarkupVals,MATCH(M16,MarkupCodes,0))</f>
@@ -3964,7 +4062,7 @@
         <v>195</v>
       </c>
       <c r="Q16" s="22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="R16" s="23" t="n">
         <f aca="false">P16*INDEX(MarkupVals,MATCH(Q16,MarkupCodes,0))</f>
@@ -3982,19 +4080,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="G17" s="20" t="n">
         <f aca="false">p_Addition_Crawl_Space*p_Addition_Width*p_Addition_Depth</f>
@@ -4004,7 +4102,7 @@
         <v>18.07</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J17" s="23" t="n">
         <f aca="false">H17*INDEX(MarkupVals,MATCH(I17,MarkupCodes,0))</f>
@@ -4018,7 +4116,7 @@
         <v>18.07</v>
       </c>
       <c r="M17" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N17" s="23" t="n">
         <f aca="false">L17*INDEX(MarkupVals,MATCH(M17,MarkupCodes,0))</f>
@@ -4032,7 +4130,7 @@
         <v>18.07</v>
       </c>
       <c r="Q17" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R17" s="23" t="n">
         <f aca="false">P17*INDEX(MarkupVals,MATCH(Q17,MarkupCodes,0))</f>
@@ -4044,7 +4142,7 @@
       </c>
       <c r="T17" s="25"/>
       <c r="U17" s="26" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4052,19 +4150,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G18" s="20" t="n">
         <f aca="false">p_Addition_Slab*p_Addition_Width*p_Addition_Depth</f>
@@ -4074,7 +4172,7 @@
         <v>21</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J18" s="23" t="n">
         <f aca="false">H18*INDEX(MarkupVals,MATCH(I18,MarkupCodes,0))</f>
@@ -4088,7 +4186,7 @@
         <v>21</v>
       </c>
       <c r="M18" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N18" s="23" t="n">
         <f aca="false">L18*INDEX(MarkupVals,MATCH(M18,MarkupCodes,0))</f>
@@ -4102,7 +4200,7 @@
         <v>21</v>
       </c>
       <c r="Q18" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R18" s="23" t="n">
         <f aca="false">P18*INDEX(MarkupVals,MATCH(Q18,MarkupCodes,0))</f>
@@ -4114,7 +4212,7 @@
       </c>
       <c r="T18" s="25"/>
       <c r="U18" s="26" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4122,19 +4220,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C19" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="E19" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="D19" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>206</v>
-      </c>
       <c r="F19" s="19" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="G19" s="20" t="n">
         <f aca="false">p_Addition_Basement*p_Addition_Width*p_Addition_Depth</f>
@@ -4144,7 +4242,7 @@
         <v>33</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J19" s="23" t="n">
         <f aca="false">H19*INDEX(MarkupVals,MATCH(I19,MarkupCodes,0))</f>
@@ -4158,7 +4256,7 @@
         <v>33</v>
       </c>
       <c r="M19" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N19" s="23" t="n">
         <f aca="false">L19*INDEX(MarkupVals,MATCH(M19,MarkupCodes,0))</f>
@@ -4172,7 +4270,7 @@
         <v>33</v>
       </c>
       <c r="Q19" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R19" s="23" t="n">
         <f aca="false">P19*INDEX(MarkupVals,MATCH(Q19,MarkupCodes,0))</f>
@@ -4184,7 +4282,7 @@
       </c>
       <c r="T19" s="25"/>
       <c r="U19" s="26" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4192,19 +4290,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G20" s="20" t="n">
         <f aca="false">p_Addition_Piers</f>
@@ -4214,7 +4312,7 @@
         <v>500</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J20" s="23" t="n">
         <f aca="false">H20*INDEX(MarkupVals,MATCH(I20,MarkupCodes,0))</f>
@@ -4228,7 +4326,7 @@
         <v>500</v>
       </c>
       <c r="M20" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N20" s="23" t="n">
         <f aca="false">L20*INDEX(MarkupVals,MATCH(M20,MarkupCodes,0))</f>
@@ -4242,7 +4340,7 @@
         <v>500</v>
       </c>
       <c r="Q20" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R20" s="23" t="n">
         <f aca="false">P20*INDEX(MarkupVals,MATCH(Q20,MarkupCodes,0))</f>
@@ -4254,7 +4352,7 @@
       </c>
       <c r="T20" s="25"/>
       <c r="U20" s="26" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4262,19 +4360,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="G21" s="20" t="n">
         <f aca="false">3*p_Addition_Piers</f>
@@ -4285,7 +4383,7 @@
         <v>55</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J21" s="23" t="n">
         <f aca="false">H21*INDEX(MarkupVals,MATCH(I21,MarkupCodes,0))</f>
@@ -4300,7 +4398,7 @@
         <v>55</v>
       </c>
       <c r="M21" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N21" s="23" t="n">
         <f aca="false">L21*INDEX(MarkupVals,MATCH(M21,MarkupCodes,0))</f>
@@ -4315,7 +4413,7 @@
         <v>55</v>
       </c>
       <c r="Q21" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R21" s="23" t="n">
         <f aca="false">P21*INDEX(MarkupVals,MATCH(Q21,MarkupCodes,0))</f>
@@ -4333,19 +4431,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G22" s="20" t="n">
         <f aca="false">p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -4355,7 +4453,7 @@
         <v>22.5</v>
       </c>
       <c r="I22" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J22" s="23" t="n">
         <f aca="false">H22*INDEX(MarkupVals,MATCH(I22,MarkupCodes,0))</f>
@@ -4369,7 +4467,7 @@
         <v>22.5</v>
       </c>
       <c r="M22" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N22" s="23" t="n">
         <f aca="false">L22*INDEX(MarkupVals,MATCH(M22,MarkupCodes,0))</f>
@@ -4383,7 +4481,7 @@
         <v>22.5</v>
       </c>
       <c r="Q22" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R22" s="23" t="n">
         <f aca="false">P22*INDEX(MarkupVals,MATCH(Q22,MarkupCodes,0))</f>
@@ -4395,7 +4493,7 @@
       </c>
       <c r="T22" s="25"/>
       <c r="U22" s="26" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4403,19 +4501,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G23" s="20" t="n">
         <f aca="false">p_Addition_Wall_Openings</f>
@@ -4425,7 +4523,7 @@
         <v>400</v>
       </c>
       <c r="I23" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J23" s="23" t="n">
         <f aca="false">H23*INDEX(MarkupVals,MATCH(I23,MarkupCodes,0))</f>
@@ -4439,7 +4537,7 @@
         <v>400</v>
       </c>
       <c r="M23" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N23" s="23" t="n">
         <f aca="false">L23*INDEX(MarkupVals,MATCH(M23,MarkupCodes,0))</f>
@@ -4453,7 +4551,7 @@
         <v>400</v>
       </c>
       <c r="Q23" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R23" s="23" t="n">
         <f aca="false">P23*INDEX(MarkupVals,MATCH(Q23,MarkupCodes,0))</f>
@@ -4471,19 +4569,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="G24" s="20" t="n">
         <f aca="false">ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In</f>
@@ -4494,7 +4592,7 @@
         <v>55</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J24" s="23" t="n">
         <f aca="false">H24*INDEX(MarkupVals,MATCH(I24,MarkupCodes,0))</f>
@@ -4509,7 +4607,7 @@
         <v>55</v>
       </c>
       <c r="M24" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N24" s="23" t="n">
         <f aca="false">L24*INDEX(MarkupVals,MATCH(M24,MarkupCodes,0))</f>
@@ -4524,7 +4622,7 @@
         <v>55</v>
       </c>
       <c r="Q24" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R24" s="23" t="n">
         <f aca="false">P24*INDEX(MarkupVals,MATCH(Q24,MarkupCodes,0))</f>
@@ -4536,7 +4634,7 @@
       </c>
       <c r="T24" s="25"/>
       <c r="U24" s="26" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4544,19 +4642,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="G25" s="20" t="n">
         <f aca="false">p_Addition_Width + p_Addition_Depth + 20</f>
@@ -4566,7 +4664,7 @@
         <v>8.25</v>
       </c>
       <c r="I25" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J25" s="23" t="n">
         <f aca="false">H25*INDEX(MarkupVals,MATCH(I25,MarkupCodes,0))</f>
@@ -4580,7 +4678,7 @@
         <v>8.25</v>
       </c>
       <c r="M25" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N25" s="23" t="n">
         <f aca="false">L25*INDEX(MarkupVals,MATCH(M25,MarkupCodes,0))</f>
@@ -4594,7 +4692,7 @@
         <v>8.25</v>
       </c>
       <c r="Q25" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R25" s="23" t="n">
         <f aca="false">P25*INDEX(MarkupVals,MATCH(Q25,MarkupCodes,0))</f>
@@ -4606,7 +4704,7 @@
       </c>
       <c r="T25" s="25"/>
       <c r="U25" s="26" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4614,19 +4712,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="G26" s="20" t="n">
         <f aca="false">p_Addition_Width + p_Addition_Depth + 20</f>
@@ -4636,7 +4734,7 @@
         <v>3.5</v>
       </c>
       <c r="I26" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="J26" s="23" t="n">
         <f aca="false">H26*INDEX(MarkupVals,MATCH(I26,MarkupCodes,0))</f>
@@ -4650,7 +4748,7 @@
         <v>3.5</v>
       </c>
       <c r="M26" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="N26" s="23" t="n">
         <f aca="false">L26*INDEX(MarkupVals,MATCH(M26,MarkupCodes,0))</f>
@@ -4664,7 +4762,7 @@
         <v>3.5</v>
       </c>
       <c r="Q26" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="R26" s="23" t="n">
         <f aca="false">P26*INDEX(MarkupVals,MATCH(Q26,MarkupCodes,0))</f>
@@ -4682,19 +4780,19 @@
         <v>23</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G27" s="20" t="n">
         <f aca="false">(p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)</f>
@@ -4704,7 +4802,7 @@
         <v>8</v>
       </c>
       <c r="I27" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J27" s="23" t="n">
         <f aca="false">H27*INDEX(MarkupVals,MATCH(I27,MarkupCodes,0))</f>
@@ -4718,7 +4816,7 @@
         <v>8</v>
       </c>
       <c r="M27" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N27" s="23" t="n">
         <f aca="false">L27*INDEX(MarkupVals,MATCH(M27,MarkupCodes,0))</f>
@@ -4732,7 +4830,7 @@
         <v>8</v>
       </c>
       <c r="Q27" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R27" s="23" t="n">
         <f aca="false">P27*INDEX(MarkupVals,MATCH(Q27,MarkupCodes,0))</f>
@@ -4750,19 +4848,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G28" s="20" t="n">
         <f aca="false">(p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)</f>
@@ -4772,7 +4870,7 @@
         <v>4.5</v>
       </c>
       <c r="I28" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J28" s="23" t="n">
         <f aca="false">H28*INDEX(MarkupVals,MATCH(I28,MarkupCodes,0))</f>
@@ -4786,7 +4884,7 @@
         <v>4.5</v>
       </c>
       <c r="M28" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="N28" s="23" t="n">
         <f aca="false">L28*INDEX(MarkupVals,MATCH(M28,MarkupCodes,0))</f>
@@ -4800,7 +4898,7 @@
         <v>4.5</v>
       </c>
       <c r="Q28" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="R28" s="23" t="n">
         <f aca="false">P28*INDEX(MarkupVals,MATCH(Q28,MarkupCodes,0))</f>
@@ -4818,19 +4916,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="G29" s="20" t="n">
         <f aca="false">ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares</f>
@@ -4841,7 +4939,7 @@
         <v>55</v>
       </c>
       <c r="I29" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J29" s="23" t="n">
         <f aca="false">H29*INDEX(MarkupVals,MATCH(I29,MarkupCodes,0))</f>
@@ -4856,7 +4954,7 @@
         <v>55</v>
       </c>
       <c r="M29" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N29" s="23" t="n">
         <f aca="false">L29*INDEX(MarkupVals,MATCH(M29,MarkupCodes,0))</f>
@@ -4871,7 +4969,7 @@
         <v>55</v>
       </c>
       <c r="Q29" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R29" s="23" t="n">
         <f aca="false">P29*INDEX(MarkupVals,MATCH(Q29,MarkupCodes,0))</f>
@@ -4883,7 +4981,7 @@
       </c>
       <c r="T29" s="25"/>
       <c r="U29" s="26" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4891,19 +4989,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="G30" s="20" t="n">
         <f aca="false">ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares</f>
@@ -4913,7 +5011,7 @@
         <v>160</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="J30" s="23" t="n">
         <f aca="false">H30*INDEX(MarkupVals,MATCH(I30,MarkupCodes,0))</f>
@@ -4927,7 +5025,7 @@
         <v>160</v>
       </c>
       <c r="M30" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="N30" s="23" t="n">
         <f aca="false">L30*INDEX(MarkupVals,MATCH(M30,MarkupCodes,0))</f>
@@ -4941,7 +5039,7 @@
         <v>160</v>
       </c>
       <c r="Q30" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="R30" s="23" t="n">
         <f aca="false">P30*INDEX(MarkupVals,MATCH(Q30,MarkupCodes,0))</f>
@@ -4953,7 +5051,7 @@
       </c>
       <c r="T30" s="25"/>
       <c r="U30" s="26" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4961,19 +5059,19 @@
         <v>27</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="G31" s="20" t="n">
         <f aca="false">2*(1 - p_Addition_Detached)</f>
@@ -4983,7 +5081,7 @@
         <v>150</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="J31" s="23" t="n">
         <f aca="false">H31*INDEX(MarkupVals,MATCH(I31,MarkupCodes,0))</f>
@@ -4997,7 +5095,7 @@
         <v>150</v>
       </c>
       <c r="M31" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="N31" s="23" t="n">
         <f aca="false">L31*INDEX(MarkupVals,MATCH(M31,MarkupCodes,0))</f>
@@ -5011,7 +5109,7 @@
         <v>150</v>
       </c>
       <c r="Q31" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="R31" s="23" t="n">
         <f aca="false">P31*INDEX(MarkupVals,MATCH(Q31,MarkupCodes,0))</f>
@@ -5029,19 +5127,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="G32" s="20" t="n">
         <f aca="false">ROUNDUP(2.5*p_Addition_Windows,0)</f>
@@ -5052,7 +5150,7 @@
         <v>55</v>
       </c>
       <c r="I32" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J32" s="23" t="n">
         <f aca="false">H32*INDEX(MarkupVals,MATCH(I32,MarkupCodes,0))</f>
@@ -5067,7 +5165,7 @@
         <v>55</v>
       </c>
       <c r="M32" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N32" s="23" t="n">
         <f aca="false">L32*INDEX(MarkupVals,MATCH(M32,MarkupCodes,0))</f>
@@ -5082,7 +5180,7 @@
         <v>55</v>
       </c>
       <c r="Q32" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R32" s="23" t="n">
         <f aca="false">P32*INDEX(MarkupVals,MATCH(Q32,MarkupCodes,0))</f>
@@ -5100,19 +5198,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G33" s="20" t="n">
         <f aca="false">p_Addition_Exterior_Doors</f>
@@ -5122,7 +5220,7 @@
         <v>1230</v>
       </c>
       <c r="I33" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J33" s="23" t="n">
         <f aca="false">H33*INDEX(MarkupVals,MATCH(I33,MarkupCodes,0))</f>
@@ -5136,7 +5234,7 @@
         <v>1230</v>
       </c>
       <c r="M33" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N33" s="23" t="n">
         <f aca="false">L33*INDEX(MarkupVals,MATCH(M33,MarkupCodes,0))</f>
@@ -5150,7 +5248,7 @@
         <v>1230</v>
       </c>
       <c r="Q33" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R33" s="23" t="n">
         <f aca="false">P33*INDEX(MarkupVals,MATCH(Q33,MarkupCodes,0))</f>
@@ -5162,7 +5260,7 @@
       </c>
       <c r="T33" s="25"/>
       <c r="U33" s="26" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5170,19 +5268,19 @@
         <v>30</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G34" s="20" t="n">
         <f aca="false">p_Addition_Garage_Doors</f>
@@ -5192,7 +5290,7 @@
         <v>1300</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J34" s="23" t="n">
         <f aca="false">H34*INDEX(MarkupVals,MATCH(I34,MarkupCodes,0))</f>
@@ -5206,7 +5304,7 @@
         <v>1300</v>
       </c>
       <c r="M34" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="N34" s="23" t="n">
         <f aca="false">L34*INDEX(MarkupVals,MATCH(M34,MarkupCodes,0))</f>
@@ -5220,7 +5318,7 @@
         <v>1300</v>
       </c>
       <c r="Q34" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="R34" s="23" t="n">
         <f aca="false">P34*INDEX(MarkupVals,MATCH(Q34,MarkupCodes,0))</f>
@@ -5232,7 +5330,7 @@
       </c>
       <c r="T34" s="25"/>
       <c r="U34" s="26" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5240,19 +5338,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G35" s="20" t="n">
         <f aca="false">p_Addition_Garage_Doors</f>
@@ -5262,7 +5360,7 @@
         <v>105</v>
       </c>
       <c r="I35" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="J35" s="23" t="n">
         <f aca="false">H35*INDEX(MarkupVals,MATCH(I35,MarkupCodes,0))</f>
@@ -5276,7 +5374,7 @@
         <v>105</v>
       </c>
       <c r="M35" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="N35" s="23" t="n">
         <f aca="false">L35*INDEX(MarkupVals,MATCH(M35,MarkupCodes,0))</f>
@@ -5290,7 +5388,7 @@
         <v>105</v>
       </c>
       <c r="Q35" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="R35" s="23" t="n">
         <f aca="false">P35*INDEX(MarkupVals,MATCH(Q35,MarkupCodes,0))</f>
@@ -5308,19 +5406,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="G36" s="20" t="n">
         <f aca="false">8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors</f>
@@ -5331,7 +5429,7 @@
         <v>55</v>
       </c>
       <c r="I36" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J36" s="23" t="n">
         <f aca="false">H36*INDEX(MarkupVals,MATCH(I36,MarkupCodes,0))</f>
@@ -5346,7 +5444,7 @@
         <v>55</v>
       </c>
       <c r="M36" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N36" s="23" t="n">
         <f aca="false">L36*INDEX(MarkupVals,MATCH(M36,MarkupCodes,0))</f>
@@ -5361,7 +5459,7 @@
         <v>55</v>
       </c>
       <c r="Q36" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R36" s="23" t="n">
         <f aca="false">P36*INDEX(MarkupVals,MATCH(Q36,MarkupCodes,0))</f>
@@ -5379,19 +5477,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G37" s="20" t="n">
         <f aca="false">p_Addition_Plumbing_Fixtures</f>
@@ -5401,7 +5499,7 @@
         <v>250</v>
       </c>
       <c r="I37" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J37" s="23" t="n">
         <f aca="false">H37*INDEX(MarkupVals,MATCH(I37,MarkupCodes,0))</f>
@@ -5415,7 +5513,7 @@
         <v>250</v>
       </c>
       <c r="M37" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N37" s="23" t="n">
         <f aca="false">L37*INDEX(MarkupVals,MATCH(M37,MarkupCodes,0))</f>
@@ -5429,7 +5527,7 @@
         <v>250</v>
       </c>
       <c r="Q37" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R37" s="23" t="n">
         <f aca="false">P37*INDEX(MarkupVals,MATCH(Q37,MarkupCodes,0))</f>
@@ -5441,7 +5539,7 @@
       </c>
       <c r="T37" s="25"/>
       <c r="U37" s="26" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5449,19 +5547,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="G38" s="20" t="n">
         <f aca="false">9*p_Addition_Plumbing_Fixtures</f>
@@ -5472,7 +5570,7 @@
         <v>55</v>
       </c>
       <c r="I38" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J38" s="23" t="n">
         <f aca="false">H38*INDEX(MarkupVals,MATCH(I38,MarkupCodes,0))</f>
@@ -5487,7 +5585,7 @@
         <v>55</v>
       </c>
       <c r="M38" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N38" s="23" t="n">
         <f aca="false">L38*INDEX(MarkupVals,MATCH(M38,MarkupCodes,0))</f>
@@ -5502,7 +5600,7 @@
         <v>55</v>
       </c>
       <c r="Q38" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R38" s="23" t="n">
         <f aca="false">P38*INDEX(MarkupVals,MATCH(Q38,MarkupCodes,0))</f>
@@ -5520,19 +5618,19 @@
         <v>35</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G39" s="20" t="n">
         <f aca="false">p_Addition_HVAC_Extend</f>
@@ -5542,7 +5640,7 @@
         <v>1310</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J39" s="23" t="n">
         <f aca="false">H39*INDEX(MarkupVals,MATCH(I39,MarkupCodes,0))</f>
@@ -5556,7 +5654,7 @@
         <v>1310</v>
       </c>
       <c r="M39" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="N39" s="23" t="n">
         <f aca="false">L39*INDEX(MarkupVals,MATCH(M39,MarkupCodes,0))</f>
@@ -5570,7 +5668,7 @@
         <v>1310</v>
       </c>
       <c r="Q39" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="R39" s="23" t="n">
         <f aca="false">P39*INDEX(MarkupVals,MATCH(Q39,MarkupCodes,0))</f>
@@ -5582,7 +5680,7 @@
       </c>
       <c r="T39" s="25"/>
       <c r="U39" s="26" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5590,19 +5688,19 @@
         <v>36</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C40" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="D40" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="D40" s="18" t="s">
-        <v>264</v>
-      </c>
       <c r="E40" s="18" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G40" s="20" t="n">
         <f aca="false">p_Addition_HVAC_New_Unit</f>
@@ -5612,7 +5710,7 @@
         <v>7500</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J40" s="23" t="n">
         <f aca="false">H40*INDEX(MarkupVals,MATCH(I40,MarkupCodes,0))</f>
@@ -5626,7 +5724,7 @@
         <v>7500</v>
       </c>
       <c r="M40" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="N40" s="23" t="n">
         <f aca="false">L40*INDEX(MarkupVals,MATCH(M40,MarkupCodes,0))</f>
@@ -5640,7 +5738,7 @@
         <v>7500</v>
       </c>
       <c r="Q40" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="R40" s="23" t="n">
         <f aca="false">P40*INDEX(MarkupVals,MATCH(Q40,MarkupCodes,0))</f>
@@ -5652,7 +5750,7 @@
       </c>
       <c r="T40" s="25"/>
       <c r="U40" s="26" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5660,19 +5758,19 @@
         <v>37</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G41" s="20" t="n">
         <f aca="false">p_Addition_Electrical*p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -5682,7 +5780,7 @@
         <v>2.61</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J41" s="23" t="n">
         <f aca="false">H41*INDEX(MarkupVals,MATCH(I41,MarkupCodes,0))</f>
@@ -5696,7 +5794,7 @@
         <v>2.61</v>
       </c>
       <c r="M41" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N41" s="23" t="n">
         <f aca="false">L41*INDEX(MarkupVals,MATCH(M41,MarkupCodes,0))</f>
@@ -5710,7 +5808,7 @@
         <v>2.61</v>
       </c>
       <c r="Q41" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R41" s="23" t="n">
         <f aca="false">P41*INDEX(MarkupVals,MATCH(Q41,MarkupCodes,0))</f>
@@ -5722,7 +5820,7 @@
       </c>
       <c r="T41" s="25"/>
       <c r="U41" s="26" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5730,19 +5828,19 @@
         <v>38</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="G42" s="20" t="n">
         <f aca="false">p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0))</f>
@@ -5753,7 +5851,7 @@
         <v>55</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J42" s="23" t="n">
         <f aca="false">H42*INDEX(MarkupVals,MATCH(I42,MarkupCodes,0))</f>
@@ -5768,7 +5866,7 @@
         <v>55</v>
       </c>
       <c r="M42" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N42" s="23" t="n">
         <f aca="false">L42*INDEX(MarkupVals,MATCH(M42,MarkupCodes,0))</f>
@@ -5783,7 +5881,7 @@
         <v>55</v>
       </c>
       <c r="Q42" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R42" s="23" t="n">
         <f aca="false">P42*INDEX(MarkupVals,MATCH(Q42,MarkupCodes,0))</f>
@@ -5795,7 +5893,7 @@
       </c>
       <c r="T42" s="25"/>
       <c r="U42" s="26" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5803,19 +5901,19 @@
         <v>39</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="G43" s="20" t="n">
         <f aca="false">p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -5825,7 +5923,7 @@
         <v>8.52</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J43" s="23" t="n">
         <f aca="false">H43*INDEX(MarkupVals,MATCH(I43,MarkupCodes,0))</f>
@@ -5839,7 +5937,7 @@
         <v>8.52</v>
       </c>
       <c r="M43" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="N43" s="23" t="n">
         <f aca="false">L43*INDEX(MarkupVals,MATCH(M43,MarkupCodes,0))</f>
@@ -5853,7 +5951,7 @@
         <v>8.52</v>
       </c>
       <c r="Q43" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="R43" s="23" t="n">
         <f aca="false">P43*INDEX(MarkupVals,MATCH(Q43,MarkupCodes,0))</f>
@@ -5865,7 +5963,7 @@
       </c>
       <c r="T43" s="25"/>
       <c r="U43" s="26" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5873,19 +5971,19 @@
         <v>40</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="G44" s="20" t="n">
         <f aca="false">p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -5895,7 +5993,7 @@
         <v>1.02</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J44" s="23" t="n">
         <f aca="false">H44*INDEX(MarkupVals,MATCH(I44,MarkupCodes,0))</f>
@@ -5909,7 +6007,7 @@
         <v>1.02</v>
       </c>
       <c r="M44" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N44" s="23" t="n">
         <f aca="false">L44*INDEX(MarkupVals,MATCH(M44,MarkupCodes,0))</f>
@@ -5923,7 +6021,7 @@
         <v>1.02</v>
       </c>
       <c r="Q44" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R44" s="23" t="n">
         <f aca="false">P44*INDEX(MarkupVals,MATCH(Q44,MarkupCodes,0))</f>
@@ -5935,7 +6033,7 @@
       </c>
       <c r="T44" s="25"/>
       <c r="U44" s="26" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5943,19 +6041,19 @@
         <v>41</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C45" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="D45" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="D45" s="18" t="s">
-        <v>282</v>
-      </c>
       <c r="E45" s="18" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="G45" s="20" t="n">
         <f aca="false">p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -5965,7 +6063,7 @@
         <v>1.31</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J45" s="23" t="n">
         <f aca="false">H45*INDEX(MarkupVals,MATCH(I45,MarkupCodes,0))</f>
@@ -5979,7 +6077,7 @@
         <v>1.31</v>
       </c>
       <c r="M45" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N45" s="23" t="n">
         <f aca="false">L45*INDEX(MarkupVals,MATCH(M45,MarkupCodes,0))</f>
@@ -5993,7 +6091,7 @@
         <v>1.31</v>
       </c>
       <c r="Q45" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R45" s="23" t="n">
         <f aca="false">P45*INDEX(MarkupVals,MATCH(Q45,MarkupCodes,0))</f>
@@ -6011,19 +6109,19 @@
         <v>42</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="G46" s="20" t="n">
         <f aca="false">p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0)</f>
@@ -6034,7 +6132,7 @@
         <v>55</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J46" s="23" t="n">
         <f aca="false">H46*INDEX(MarkupVals,MATCH(I46,MarkupCodes,0))</f>
@@ -6049,7 +6147,7 @@
         <v>55</v>
       </c>
       <c r="M46" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N46" s="23" t="n">
         <f aca="false">L46*INDEX(MarkupVals,MATCH(M46,MarkupCodes,0))</f>
@@ -6064,7 +6162,7 @@
         <v>55</v>
       </c>
       <c r="Q46" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R46" s="23" t="n">
         <f aca="false">P46*INDEX(MarkupVals,MATCH(Q46,MarkupCodes,0))</f>
@@ -6082,19 +6180,19 @@
         <v>43</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="G47" s="20" t="n">
         <f aca="false">p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/60,0)</f>
@@ -6104,7 +6202,7 @@
         <v>85</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J47" s="23" t="n">
         <f aca="false">H47*INDEX(MarkupVals,MATCH(I47,MarkupCodes,0))</f>
@@ -6118,7 +6216,7 @@
         <v>85</v>
       </c>
       <c r="M47" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N47" s="23" t="n">
         <f aca="false">L47*INDEX(MarkupVals,MATCH(M47,MarkupCodes,0))</f>
@@ -6132,7 +6230,7 @@
         <v>85</v>
       </c>
       <c r="Q47" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R47" s="23" t="n">
         <f aca="false">P47*INDEX(MarkupVals,MATCH(Q47,MarkupCodes,0))</f>
@@ -6150,19 +6248,19 @@
         <v>44</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G48" s="20" t="n">
         <f aca="false">p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0)</f>
@@ -6173,7 +6271,7 @@
         <v>55</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J48" s="23" t="n">
         <f aca="false">H48*INDEX(MarkupVals,MATCH(I48,MarkupCodes,0))</f>
@@ -6188,7 +6286,7 @@
         <v>55</v>
       </c>
       <c r="M48" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N48" s="23" t="n">
         <f aca="false">L48*INDEX(MarkupVals,MATCH(M48,MarkupCodes,0))</f>
@@ -6203,7 +6301,7 @@
         <v>55</v>
       </c>
       <c r="Q48" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R48" s="23" t="n">
         <f aca="false">P48*INDEX(MarkupVals,MATCH(Q48,MarkupCodes,0))</f>
@@ -6221,19 +6319,19 @@
         <v>45</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G49" s="20" t="n">
         <f aca="false">p_Addition_Interior_Doors</f>
@@ -6243,7 +6341,7 @@
         <v>400</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J49" s="23" t="n">
         <f aca="false">H49*INDEX(MarkupVals,MATCH(I49,MarkupCodes,0))</f>
@@ -6257,7 +6355,7 @@
         <v>400</v>
       </c>
       <c r="M49" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N49" s="23" t="n">
         <f aca="false">L49*INDEX(MarkupVals,MATCH(M49,MarkupCodes,0))</f>
@@ -6271,7 +6369,7 @@
         <v>400</v>
       </c>
       <c r="Q49" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R49" s="23" t="n">
         <f aca="false">P49*INDEX(MarkupVals,MATCH(Q49,MarkupCodes,0))</f>
@@ -6283,7 +6381,7 @@
       </c>
       <c r="T49" s="25"/>
       <c r="U49" s="26" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6291,19 +6389,19 @@
         <v>46</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="G50" s="20" t="n">
         <f aca="false">p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -6313,7 +6411,7 @@
         <v>0.75</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J50" s="23" t="n">
         <f aca="false">H50*INDEX(MarkupVals,MATCH(I50,MarkupCodes,0))</f>
@@ -6327,7 +6425,7 @@
         <v>0.75</v>
       </c>
       <c r="M50" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N50" s="23" t="n">
         <f aca="false">L50*INDEX(MarkupVals,MATCH(M50,MarkupCodes,0))</f>
@@ -6341,7 +6439,7 @@
         <v>0.75</v>
       </c>
       <c r="Q50" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R50" s="23" t="n">
         <f aca="false">P50*INDEX(MarkupVals,MATCH(Q50,MarkupCodes,0))</f>
@@ -6359,19 +6457,19 @@
         <v>47</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="G51" s="20" t="n">
         <f aca="false">p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0)</f>
@@ -6382,7 +6480,7 @@
         <v>55</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J51" s="23" t="n">
         <f aca="false">H51*INDEX(MarkupVals,MATCH(I51,MarkupCodes,0))</f>
@@ -6397,7 +6495,7 @@
         <v>55</v>
       </c>
       <c r="M51" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N51" s="23" t="n">
         <f aca="false">L51*INDEX(MarkupVals,MATCH(M51,MarkupCodes,0))</f>
@@ -6412,7 +6510,7 @@
         <v>55</v>
       </c>
       <c r="Q51" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R51" s="23" t="n">
         <f aca="false">P51*INDEX(MarkupVals,MATCH(Q51,MarkupCodes,0))</f>
@@ -6430,19 +6528,19 @@
         <v>48</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="G52" s="20" t="n">
         <f aca="false">p_Addition_Living_Space*ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/12,0)</f>
@@ -6452,7 +6550,7 @@
         <v>45.49</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J52" s="23" t="n">
         <f aca="false">H52*INDEX(MarkupVals,MATCH(I52,MarkupCodes,0))</f>
@@ -6466,7 +6564,7 @@
         <v>45.49</v>
       </c>
       <c r="M52" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N52" s="23" t="n">
         <f aca="false">L52*INDEX(MarkupVals,MATCH(M52,MarkupCodes,0))</f>
@@ -6480,7 +6578,7 @@
         <v>45.49</v>
       </c>
       <c r="Q52" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R52" s="23" t="n">
         <f aca="false">P52*INDEX(MarkupVals,MATCH(Q52,MarkupCodes,0))</f>
@@ -6498,19 +6596,19 @@
         <v>49</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G53" s="20" t="n">
         <f aca="false">p_Addition_Living_Space*(p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors)</f>
@@ -6520,7 +6618,7 @@
         <v>37.11</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J53" s="23" t="n">
         <f aca="false">H53*INDEX(MarkupVals,MATCH(I53,MarkupCodes,0))</f>
@@ -6534,7 +6632,7 @@
         <v>37.11</v>
       </c>
       <c r="M53" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N53" s="23" t="n">
         <f aca="false">L53*INDEX(MarkupVals,MATCH(M53,MarkupCodes,0))</f>
@@ -6548,7 +6646,7 @@
         <v>37.11</v>
       </c>
       <c r="Q53" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R53" s="23" t="n">
         <f aca="false">P53*INDEX(MarkupVals,MATCH(Q53,MarkupCodes,0))</f>
@@ -6566,19 +6664,19 @@
         <v>50</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="G54" s="20" t="n">
         <f aca="false">p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors)</f>
@@ -6589,7 +6687,7 @@
         <v>55</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J54" s="23" t="n">
         <f aca="false">H54*INDEX(MarkupVals,MATCH(I54,MarkupCodes,0))</f>
@@ -6604,7 +6702,7 @@
         <v>55</v>
       </c>
       <c r="M54" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N54" s="23" t="n">
         <f aca="false">L54*INDEX(MarkupVals,MATCH(M54,MarkupCodes,0))</f>
@@ -6619,7 +6717,7 @@
         <v>55</v>
       </c>
       <c r="Q54" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="R54" s="23" t="n">
         <f aca="false">P54*INDEX(MarkupVals,MATCH(Q54,MarkupCodes,0))</f>
@@ -6637,19 +6735,19 @@
         <v>51</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="G55" s="20" t="n">
         <f aca="false">ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In</f>
@@ -6659,7 +6757,7 @@
         <v>210</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J55" s="23" t="n">
         <f aca="false">H55*INDEX(MarkupVals,MATCH(I55,MarkupCodes,0))</f>
@@ -6673,7 +6771,7 @@
         <v>245</v>
       </c>
       <c r="M55" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N55" s="23" t="n">
         <f aca="false">L55*INDEX(MarkupVals,MATCH(M55,MarkupCodes,0))</f>
@@ -6687,7 +6785,7 @@
         <v>313</v>
       </c>
       <c r="Q55" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R55" s="23" t="n">
         <f aca="false">P55*INDEX(MarkupVals,MATCH(Q55,MarkupCodes,0))</f>
@@ -6698,10 +6796,10 @@
         <v>2723.1</v>
       </c>
       <c r="T55" s="25" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="U55" s="26" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6709,19 +6807,19 @@
         <v>52</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="G56" s="20" t="n">
         <f aca="false">ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In</f>
@@ -6731,7 +6829,7 @@
         <v>95</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="J56" s="23" t="n">
         <f aca="false">H56*INDEX(MarkupVals,MATCH(I56,MarkupCodes,0))</f>
@@ -6745,7 +6843,7 @@
         <v>95</v>
       </c>
       <c r="M56" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="N56" s="23" t="n">
         <f aca="false">L56*INDEX(MarkupVals,MATCH(M56,MarkupCodes,0))</f>
@@ -6759,7 +6857,7 @@
         <v>200</v>
       </c>
       <c r="Q56" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="R56" s="23" t="n">
         <f aca="false">P56*INDEX(MarkupVals,MATCH(Q56,MarkupCodes,0))</f>
@@ -6771,7 +6869,7 @@
       </c>
       <c r="T56" s="25"/>
       <c r="U56" s="26" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6779,19 +6877,19 @@
         <v>53</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="G57" s="20" t="n">
         <f aca="false">ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares</f>
@@ -6801,7 +6899,7 @@
         <v>230</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J57" s="23" t="n">
         <f aca="false">H57*INDEX(MarkupVals,MATCH(I57,MarkupCodes,0))</f>
@@ -6815,7 +6913,7 @@
         <v>320</v>
       </c>
       <c r="M57" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N57" s="23" t="n">
         <f aca="false">L57*INDEX(MarkupVals,MATCH(M57,MarkupCodes,0))</f>
@@ -6829,7 +6927,7 @@
         <v>495</v>
       </c>
       <c r="Q57" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R57" s="23" t="n">
         <f aca="false">P57*INDEX(MarkupVals,MATCH(Q57,MarkupCodes,0))</f>
@@ -6840,10 +6938,10 @@
         <v>3588.75</v>
       </c>
       <c r="T57" s="25" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="U57" s="26" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6851,19 +6949,19 @@
         <v>54</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G58" s="20" t="n">
         <f aca="false">p_Addition_Windows</f>
@@ -6873,7 +6971,7 @@
         <v>475</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J58" s="23" t="n">
         <f aca="false">H58*INDEX(MarkupVals,MATCH(I58,MarkupCodes,0))</f>
@@ -6887,7 +6985,7 @@
         <v>700</v>
       </c>
       <c r="M58" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N58" s="23" t="n">
         <f aca="false">L58*INDEX(MarkupVals,MATCH(M58,MarkupCodes,0))</f>
@@ -6901,7 +6999,7 @@
         <v>1100</v>
       </c>
       <c r="Q58" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R58" s="23" t="n">
         <f aca="false">P58*INDEX(MarkupVals,MATCH(Q58,MarkupCodes,0))</f>
@@ -6912,10 +7010,10 @@
         <v>6380</v>
       </c>
       <c r="T58" s="25" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="U58" s="26" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6923,19 +7021,19 @@
         <v>55</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G59" s="20" t="n">
         <f aca="false">p_Addition_Patio_Doors</f>
@@ -6945,7 +7043,7 @@
         <v>1750</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J59" s="23" t="n">
         <f aca="false">H59*INDEX(MarkupVals,MATCH(I59,MarkupCodes,0))</f>
@@ -6959,7 +7057,7 @@
         <v>2500</v>
       </c>
       <c r="M59" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N59" s="23" t="n">
         <f aca="false">L59*INDEX(MarkupVals,MATCH(M59,MarkupCodes,0))</f>
@@ -6973,7 +7071,7 @@
         <v>3000</v>
       </c>
       <c r="Q59" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R59" s="23" t="n">
         <f aca="false">P59*INDEX(MarkupVals,MATCH(Q59,MarkupCodes,0))</f>
@@ -6984,10 +7082,10 @@
         <v>4350</v>
       </c>
       <c r="T59" s="25" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="U59" s="26" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6995,19 +7093,19 @@
         <v>56</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="G60" s="20" t="n">
         <f aca="false">p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -7017,7 +7115,7 @@
         <v>3.5</v>
       </c>
       <c r="I60" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J60" s="23" t="n">
         <f aca="false">H60*INDEX(MarkupVals,MATCH(I60,MarkupCodes,0))</f>
@@ -7031,7 +7129,7 @@
         <v>5</v>
       </c>
       <c r="M60" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N60" s="23" t="n">
         <f aca="false">L60*INDEX(MarkupVals,MATCH(M60,MarkupCodes,0))</f>
@@ -7045,7 +7143,7 @@
         <v>9</v>
       </c>
       <c r="Q60" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R60" s="23" t="n">
         <f aca="false">P60*INDEX(MarkupVals,MATCH(Q60,MarkupCodes,0))</f>
@@ -7056,45 +7154,255 @@
         <v>4176</v>
       </c>
       <c r="T60" s="25" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="U60" s="26" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="15" t="s">
-        <v>330</v>
-      </c>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="16" t="n">
-        <f aca="false">SUM(K5:K60)</f>
-        <v>70256.81</v>
-      </c>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
-      <c r="N61" s="6"/>
-      <c r="O61" s="16" t="n">
-        <f aca="false">SUM(O5:O60)</f>
-        <v>74302.31</v>
-      </c>
-      <c r="P61" s="6"/>
-      <c r="Q61" s="6"/>
-      <c r="R61" s="6"/>
-      <c r="S61" s="16" t="n">
-        <f aca="false">SUM(S5:S60)</f>
-        <v>81977.16</v>
-      </c>
-      <c r="T61" s="6"/>
-      <c r="U61" s="6"/>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="670.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="18" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="F61" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="G61" s="20" t="n">
+        <f aca="false">p_Addition_Contingency_Rate/100*((1)*290 + (6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0))*100 + (1)*217.5 + (4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0))*100 + (1 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/400,0) + 3*p_Addition_Living_Space)*435 + (4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings)*100 + (p_Addition_Dumpster_Loads)*450 + (2 + 2*p_Addition_Living_Space)*100 + (p_Addition_Travel_Hours)*100 + (p_Addition_Utility_Trench)*17.4 + (16*p_Addition_Site_Excavation)*100 + (2*p_Addition_Site_Excavation)*282.75 + (p_Addition_Crawl_Space*p_Addition_Width*p_Addition_Depth)*26.2015 + (p_Addition_Slab*p_Addition_Width*p_Addition_Depth)*30.45 + (p_Addition_Basement*p_Addition_Width*p_Addition_Depth)*47.85 + (p_Addition_Piers)*725 + (3*p_Addition_Piers)*100 + (p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*32.625 + (p_Addition_Wall_Openings)*580 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In)*100 + (p_Addition_Width + p_Addition_Depth + 20)*11.9625 + (p_Addition_Width + p_Addition_Depth + 20)*5.075 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*11.6 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*5.85 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*100 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*232 + (2*(1 - p_Addition_Detached))*217.5 + (ROUNDUP(2.5*p_Addition_Windows,0))*100 + (p_Addition_Exterior_Doors)*1783.5 + (p_Addition_Garage_Doors)*1690 + (p_Addition_Garage_Doors)*152.25 + (8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors)*100 + (p_Addition_Plumbing_Fixtures)*362.5 + (9*p_Addition_Plumbing_Fixtures)*100 + (p_Addition_HVAC_Extend)*1703 + (p_Addition_HVAC_New_Unit)*9750 + (p_Addition_Electrical*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*3.7845 + (p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0)))*100 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*11.076 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.479 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.8995 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0))*100 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/60,0))*123.25 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0))*100 + (p_Addition_Interior_Doors)*580 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.0875 + (p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0))*100 + (p_Addition_Living_Space*ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/12,0))*65.9605 + (p_Addition_Living_Space*(p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*53.8095 + (p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*100 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*304.5 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*137.75 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*333.5 + (p_Addition_Windows)*688.75 + (p_Addition_Patio_Doors)*2537.5 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*5.075)</f>
+        <v>7025.681</v>
+      </c>
+      <c r="H61" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="J61" s="23" t="n">
+        <f aca="false">H61*INDEX(MarkupVals,MATCH(I61,MarkupCodes,0))</f>
+        <v>1</v>
+      </c>
+      <c r="K61" s="24" t="n">
+        <f aca="false">G61*J61</f>
+        <v>7025.681</v>
+      </c>
+      <c r="L61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="N61" s="23" t="n">
+        <f aca="false">L61*INDEX(MarkupVals,MATCH(M61,MarkupCodes,0))</f>
+        <v>0</v>
+      </c>
+      <c r="O61" s="24" t="n">
+        <f aca="false">G61*N61</f>
+        <v>0</v>
+      </c>
+      <c r="P61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="R61" s="23" t="n">
+        <f aca="false">P61*INDEX(MarkupVals,MATCH(Q61,MarkupCodes,0))</f>
+        <v>0</v>
+      </c>
+      <c r="S61" s="24" t="n">
+        <f aca="false">G61*R61</f>
+        <v>0</v>
+      </c>
+      <c r="T61" s="25"/>
+      <c r="U61" s="26" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="670.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="18" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="D62" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="F62" s="27" t="s">
+        <v>344</v>
+      </c>
+      <c r="G62" s="20" t="n">
+        <f aca="false">p_Addition_Contingency_Rate/100*((1)*290 + (6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0))*100 + (1)*217.5 + (4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0))*100 + (1 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/400,0) + 3*p_Addition_Living_Space)*435 + (4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings)*100 + (p_Addition_Dumpster_Loads)*450 + (2 + 2*p_Addition_Living_Space)*100 + (p_Addition_Travel_Hours)*100 + (p_Addition_Utility_Trench)*17.4 + (16*p_Addition_Site_Excavation)*100 + (2*p_Addition_Site_Excavation)*282.75 + (p_Addition_Crawl_Space*p_Addition_Width*p_Addition_Depth)*26.2015 + (p_Addition_Slab*p_Addition_Width*p_Addition_Depth)*30.45 + (p_Addition_Basement*p_Addition_Width*p_Addition_Depth)*47.85 + (p_Addition_Piers)*725 + (3*p_Addition_Piers)*100 + (p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*32.625 + (p_Addition_Wall_Openings)*580 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In)*100 + (p_Addition_Width + p_Addition_Depth + 20)*11.9625 + (p_Addition_Width + p_Addition_Depth + 20)*5.075 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*11.6 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*5.85 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*100 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*232 + (2*(1 - p_Addition_Detached))*217.5 + (ROUNDUP(2.5*p_Addition_Windows,0))*100 + (p_Addition_Exterior_Doors)*1783.5 + (p_Addition_Garage_Doors)*1690 + (p_Addition_Garage_Doors)*152.25 + (8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors)*100 + (p_Addition_Plumbing_Fixtures)*362.5 + (9*p_Addition_Plumbing_Fixtures)*100 + (p_Addition_HVAC_Extend)*1703 + (p_Addition_HVAC_New_Unit)*9750 + (p_Addition_Electrical*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*3.7845 + (p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0)))*100 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*11.076 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.479 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.8995 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0))*100 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/60,0))*123.25 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0))*100 + (p_Addition_Interior_Doors)*580 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.0875 + (p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0))*100 + (p_Addition_Living_Space*ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/12,0))*65.9605 + (p_Addition_Living_Space*(p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*53.8095 + (p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*100 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*355.25 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*137.75 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*464 + (p_Addition_Windows)*1015 + (p_Addition_Patio_Doors)*3625 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*7.25)</f>
+        <v>7430.231</v>
+      </c>
+      <c r="H62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="J62" s="23" t="n">
+        <f aca="false">H62*INDEX(MarkupVals,MATCH(I62,MarkupCodes,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K62" s="24" t="n">
+        <f aca="false">G62*J62</f>
+        <v>0</v>
+      </c>
+      <c r="L62" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="N62" s="23" t="n">
+        <f aca="false">L62*INDEX(MarkupVals,MATCH(M62,MarkupCodes,0))</f>
+        <v>1</v>
+      </c>
+      <c r="O62" s="24" t="n">
+        <f aca="false">G62*N62</f>
+        <v>7430.231</v>
+      </c>
+      <c r="P62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="R62" s="23" t="n">
+        <f aca="false">P62*INDEX(MarkupVals,MATCH(Q62,MarkupCodes,0))</f>
+        <v>0</v>
+      </c>
+      <c r="S62" s="24" t="n">
+        <f aca="false">G62*R62</f>
+        <v>0</v>
+      </c>
+      <c r="T62" s="25"/>
+      <c r="U62" s="26" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="670.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="18" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="D63" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="F63" s="27" t="s">
+        <v>347</v>
+      </c>
+      <c r="G63" s="20" t="n">
+        <f aca="false">p_Addition_Contingency_Rate/100*((1)*290 + (6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0))*100 + (1)*217.5 + (4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0))*100 + (1 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/400,0) + 3*p_Addition_Living_Space)*435 + (4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings)*100 + (p_Addition_Dumpster_Loads)*450 + (2 + 2*p_Addition_Living_Space)*100 + (p_Addition_Travel_Hours)*100 + (p_Addition_Utility_Trench)*17.4 + (16*p_Addition_Site_Excavation)*100 + (2*p_Addition_Site_Excavation)*282.75 + (p_Addition_Crawl_Space*p_Addition_Width*p_Addition_Depth)*26.2015 + (p_Addition_Slab*p_Addition_Width*p_Addition_Depth)*30.45 + (p_Addition_Basement*p_Addition_Width*p_Addition_Depth)*47.85 + (p_Addition_Piers)*725 + (3*p_Addition_Piers)*100 + (p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*32.625 + (p_Addition_Wall_Openings)*580 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In)*100 + (p_Addition_Width + p_Addition_Depth + 20)*11.9625 + (p_Addition_Width + p_Addition_Depth + 20)*5.075 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*11.6 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*5.85 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*100 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*232 + (2*(1 - p_Addition_Detached))*217.5 + (ROUNDUP(2.5*p_Addition_Windows,0))*100 + (p_Addition_Exterior_Doors)*1783.5 + (p_Addition_Garage_Doors)*1690 + (p_Addition_Garage_Doors)*152.25 + (8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors)*100 + (p_Addition_Plumbing_Fixtures)*362.5 + (9*p_Addition_Plumbing_Fixtures)*100 + (p_Addition_HVAC_Extend)*1703 + (p_Addition_HVAC_New_Unit)*9750 + (p_Addition_Electrical*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*3.7845 + (p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0)))*100 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*11.076 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.479 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.8995 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0))*100 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/60,0))*123.25 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0))*100 + (p_Addition_Interior_Doors)*580 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.0875 + (p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0))*100 + (p_Addition_Living_Space*ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/12,0))*65.9605 + (p_Addition_Living_Space*(p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*53.8095 + (p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*100 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*453.85 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*290 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*717.75 + (p_Addition_Windows)*1595 + (p_Addition_Patio_Doors)*4350 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*13.05)</f>
+        <v>8197.716</v>
+      </c>
+      <c r="H63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="J63" s="23" t="n">
+        <f aca="false">H63*INDEX(MarkupVals,MATCH(I63,MarkupCodes,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K63" s="24" t="n">
+        <f aca="false">G63*J63</f>
+        <v>0</v>
+      </c>
+      <c r="L63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="N63" s="23" t="n">
+        <f aca="false">L63*INDEX(MarkupVals,MATCH(M63,MarkupCodes,0))</f>
+        <v>0</v>
+      </c>
+      <c r="O63" s="24" t="n">
+        <f aca="false">G63*N63</f>
+        <v>0</v>
+      </c>
+      <c r="P63" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="R63" s="23" t="n">
+        <f aca="false">P63*INDEX(MarkupVals,MATCH(Q63,MarkupCodes,0))</f>
+        <v>1</v>
+      </c>
+      <c r="S63" s="24" t="n">
+        <f aca="false">G63*R63</f>
+        <v>8197.716</v>
+      </c>
+      <c r="T63" s="25"/>
+      <c r="U63" s="26" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="16" t="n">
+        <f aca="false">SUM(K5:K63)</f>
+        <v>77282.491</v>
+      </c>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="6"/>
+      <c r="O64" s="16" t="n">
+        <f aca="false">SUM(O5:O63)</f>
+        <v>81732.541</v>
+      </c>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="16" t="n">
+        <f aca="false">SUM(S5:S63)</f>
+        <v>90174.876</v>
+      </c>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7112,7 +7420,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -7124,7 +7432,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -7133,7 +7441,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -7149,496 +7457,511 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C5" s="28" t="n">
         <v>20</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C6" s="28" t="n">
         <v>16</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C7" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C8" s="28" t="n">
         <v>8</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C9" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C10" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C11" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C12" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C13" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C14" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C15" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C16" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C17" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C18" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C19" s="28" t="n">
         <v>3</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C20" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C21" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C22" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C23" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C24" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C25" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C26" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C27" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C28" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C29" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="27" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C30" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C31" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="27" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C32" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>188</v>
-      </c>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>356</v>
+      </c>
+      <c r="C33" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="28"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7656,7 +7979,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -7667,7 +7990,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -7681,127 +8004,147 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="C4" s="29" t="n">
-        <f aca="false">C10/C9</f>
+        <f aca="false">C12/C11</f>
         <v>1.81818181818182</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="C5" s="30" t="n">
         <v>1.45</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C6" s="30" t="n">
         <v>1.3</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="C7" s="30" t="n">
         <v>1.45</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="C8" s="30" t="n">
         <v>1.45</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="31" t="n">
+      <c r="A9" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="31" t="n">
-        <v>100</v>
-      </c>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
+      <c r="D11" s="7" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="B12" s="6"/>
-      <c r="C12" s="32" t="n">
+      <c r="C12" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>374</v>
+      <c r="D14" s="7" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -7830,7 +8173,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -7874,7 +8217,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -7918,7 +8261,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -8004,7 +8347,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -8048,135 +8391,135 @@
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="W6" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="X6" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Z6" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AA6" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AB6" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AC6" s="8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AD6" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AE6" s="8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AF6" s="8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AG6" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AH6" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AI6" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="AJ6" s="8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AK6" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AL6" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AM6" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AN6" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>420</v>
@@ -8295,13 +8638,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="D8" s="18" t="n">
         <v>792</v>
@@ -8420,13 +8763,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="D9" s="18" t="n">
         <v>286</v>
@@ -8545,13 +8888,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="D10" s="18" t="n">
         <v>576</v>
@@ -8670,13 +9013,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>336</v>
@@ -8795,13 +9138,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="D12" s="18" t="n">
         <v>360</v>
@@ -8920,13 +9263,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>273</v>
@@ -9045,13 +9388,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="D14" s="36" t="n">
         <v>336</v>
@@ -9212,7 +9555,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -9259,7 +9602,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -9306,7 +9649,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -9395,7 +9738,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -9439,7 +9782,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -9483,33 +9826,33 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
@@ -9543,33 +9886,33 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="18" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="K23" s="18" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
@@ -9603,33 +9946,33 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="18" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
@@ -9663,33 +10006,33 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="18" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="J25" s="18" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="K25" s="18" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
@@ -9723,33 +10066,33 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="18" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
@@ -9783,33 +10126,33 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="18" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="K27" s="18" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
@@ -9843,33 +10186,33 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="18" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="K28" s="18" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
@@ -9903,33 +10246,33 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="18" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="E29" s="18" t="s">
+        <v>455</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>480</v>
+      </c>
+      <c r="H29" s="18" t="s">
         <v>436</v>
       </c>
-      <c r="F29" s="18" t="s">
-        <v>419</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>461</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>417</v>
-      </c>
       <c r="I29" s="18" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="K29" s="18" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
@@ -9963,33 +10306,33 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="18" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
@@ -10065,7 +10408,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -10109,11 +10452,11 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="11" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -10155,11 +10498,11 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="11" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -10201,11 +10544,11 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="11" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -10247,11 +10590,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="11" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -10293,11 +10636,11 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="11" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -10339,7 +10682,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -10383,11 +10726,11 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="11" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
@@ -10429,11 +10772,11 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="11" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -10517,7 +10860,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -10561,7 +10904,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -10605,7 +10948,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>

--- a/docs/ballpark/addition-ballpark-template.xlsx
+++ b/docs/ballpark/addition-ballpark-template.xlsx
@@ -35,14 +35,15 @@
     <definedName function="false" hidden="false" name="p_Addition_Interior_Doors" vbProcedure="false">Calculator!$B$23</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Living_Space" vbProcedure="false">Calculator!$B$18</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Patio_Doors" vbProcedure="false">Calculator!$B$21</definedName>
+    <definedName function="false" hidden="false" name="p_Addition_Permit_Fee" vbProcedure="false">Calculator!$B$34</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Piers" vbProcedure="false">Calculator!$B$13</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Plumbing_Fixtures" vbProcedure="false">Calculator!$B$25</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Roof_Tie_In" vbProcedure="false">Calculator!$B$15</definedName>
+    <definedName function="false" hidden="false" name="p_Addition_Service_Zone" vbProcedure="false">Calculator!$B$32</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Site_Excavation" vbProcedure="false">Calculator!$B$14</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Slab" vbProcedure="false">Calculator!$B$11</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Stories" vbProcedure="false">Calculator!$B$7</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Structure_Removed" vbProcedure="false">Calculator!$B$29</definedName>
-    <definedName function="false" hidden="false" name="p_Addition_Travel_Hours" vbProcedure="false">Calculator!$B$32</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Utility_Trench" vbProcedure="false">Calculator!$B$30</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Wall_Height" vbProcedure="false">Calculator!$B$8</definedName>
     <definedName function="false" hidden="false" name="p_Addition_Wall_Openings" vbProcedure="false">Calculator!$B$24</definedName>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="533">
   <si>
     <t xml:space="preserve">Addition Ballpark Template — DRAFT for review</t>
   </si>
@@ -452,13 +453,13 @@
     <t xml:space="preserve">{Addition Dumpster Loads}</t>
   </si>
   <si>
-    <t xml:space="preserve">Addition Travel Hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crew travel hours for jobs past the standard service zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{Addition Travel Hours}</t>
+    <t xml:space="preserve">Addition Service Zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Zone from the job in JobTread: 1 (within ~15 mi), 2 (~15-30 mi), 3 (~30-50 mi). Zone 1 adds no travel. Extended (over 50 mi) is quoted by hand: enter 4 as a floor and flag it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{Addition Service Zone}</t>
   </si>
   <si>
     <t xml:space="preserve">Addition Contingency Rate</t>
@@ -470,6 +471,15 @@
     <t xml:space="preserve">{Addition Contingency Rate}</t>
   </si>
   <si>
+    <t xml:space="preserve">Addition Permit Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permit fee DB pays the city or township, in dollars (cost), from the permit table on the Rates tab. The estimator sets it from the job address.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{Addition Permit Fee}</t>
+  </si>
+  <si>
     <t xml:space="preserve">JobTread build sheet: cost group "BALLPARK — Addition"</t>
   </si>
   <si>
@@ -551,45 +561,45 @@
     <t xml:space="preserve">Lump Sum</t>
   </si>
   <si>
+    <t xml:space="preserve">O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity is the permit fee in dollars at $1.00 each, so it can follow the jurisdiction: the estimator enters the fee from the permit table on the Rates tab as the Permit Fee parameter. Marked up like other costs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALLPARK — Addition &gt; Phase 1 - General Requirements &gt; Project/Site Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Management (C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALLPARK — Addition &gt; Phase 1 - General Requirements &gt; Site Preparation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Prep Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Construction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each</t>
+  </si>
+  <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB's addition permits ran $58 to $1,595 price depending on the city. Adjust per jurisdiction.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BALLPARK — Addition &gt; Phase 1 - General Requirements &gt; Project/Site Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project Management (C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BALLPARK — Addition &gt; Phase 1 - General Requirements &gt; Site Preparation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Prep Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Construction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each</t>
-  </si>
-  <si>
     <t xml:space="preserve">M</t>
   </si>
   <si>
@@ -650,6 +660,12 @@
     <t xml:space="preserve">Travel Related Costs</t>
   </si>
   <si>
+    <t xml:space="preserve">ceil(({Addition Service Zone} - 1)*({Addition Service Zone} + 2)/8*((6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30)) + (4 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/200)) + (4*(1 - {Addition Detached}) + ceil({Addition Structure Removed}/3) + 8*{Addition Wall Openings}) + (2 + 2*{Addition Living Space}) + (16*{Addition Site Excavation}) + (3*{Addition Piers}) + (ceil({Addition Width}*{Addition Depth}*{Addition Stories}/6) + 8*{Addition Wall Openings} + 8*{Addition Roof Tie-In}) + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares}) + (ceil(2.5*{Addition Windows})) + (8*{Addition Exterior Doors} + 8*{Addition Patio Doors} + 3*{Addition Interior Doors}) + (9*{Addition Plumbing Fixtures}) + ({Addition Electrical}*(8 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/16))) + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/12)) + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/15)) + ({Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/25)) + ({Addition Living Space}*(4 + ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/8) + {Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors})))/8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel by the job's Service Zone (JobTread sets it from the address): hours = person-days x (z-1)(z+2)/8, which is 0, 0.5 and 1.25 h per person-day for Zones 1, 2 and 3. Those are DB's own Service Call zone charges ($85 / $115 / $155 cost) turned into travel time. Extended (over 50 mi) is quoted by hand; zone 4 gives 2.25 h per person-day as a floor.</t>
+  </si>
+  <si>
     <t xml:space="preserve">BALLPARK — Addition &gt; Phase 1 - General Requirements &gt; Utilities</t>
   </si>
   <si>
@@ -1079,7 +1095,7 @@
     <t xml:space="preserve">Contingency</t>
   </si>
   <si>
-    <t xml:space="preserve">{Addition Contingency Rate}/100*((1)*290 + (6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30))*100 + (1)*217.5 + (4 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/200))*100 + (1 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/400) + 3*{Addition Living Space})*435 + (4*(1 - {Addition Detached}) + ceil({Addition Structure Removed}/3) + 8*{Addition Wall Openings})*100 + ({Addition Dumpster Loads})*450 + (2 + 2*{Addition Living Space})*100 + ({Addition Travel Hours})*100 + ({Addition Utility Trench})*17.4 + (16*{Addition Site Excavation})*100 + (2*{Addition Site Excavation})*282.75 + ({Addition Crawl Space}*{Addition Width}*{Addition Depth})*26.2015 + ({Addition Slab}*{Addition Width}*{Addition Depth})*30.45 + ({Addition Basement}*{Addition Width}*{Addition Depth})*47.85 + ({Addition Piers})*725 + (3*{Addition Piers})*100 + ({Addition Width}*{Addition Depth}*{Addition Stories})*32.625 + ({Addition Wall Openings})*580 + (ceil({Addition Width}*{Addition Depth}*{Addition Stories}/6) + 8*{Addition Wall Openings} + 8*{Addition Roof Tie-In})*100 + ({Addition Width} + {Addition Depth} + 20)*11.9625 + ({Addition Width} + {Addition Depth} + 20)*5.075 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*11.6 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*5.85 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*100 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*232 + (2*(1 - {Addition Detached}))*217.5 + (ceil(2.5*{Addition Windows}))*100 + ({Addition Exterior Doors})*1783.5 + ({Addition Garage Doors})*1690 + ({Addition Garage Doors})*152.25 + (8*{Addition Exterior Doors} + 8*{Addition Patio Doors} + 3*{Addition Interior Doors})*100 + ({Addition Plumbing Fixtures})*362.5 + (9*{Addition Plumbing Fixtures})*100 + ({Addition HVAC Extend})*1703 + ({Addition HVAC New Unit})*9750 + ({Addition Electrical}*{Addition Width}*{Addition Depth}*{Addition Stories})*3.7845 + ({Addition Electrical}*(8 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/16)))*100 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*11.076 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.479 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.8995 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/12))*100 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/60))*123.25 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/15))*100 + ({Addition Interior Doors})*580 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.0875 + ({Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/25))*100 + ({Addition Living Space}*ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/12))*65.9605 + ({Addition Living Space}*({Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*53.8095 + ({Addition Living Space}*(4 + ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/8) + {Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*100 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*304.5 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*137.75 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*333.5 + ({Addition Windows})*688.75 + ({Addition Patio Doors})*2537.5 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*5.075)</t>
+    <t xml:space="preserve">{Addition Contingency Rate}/100*(({Addition Permit Fee})*1.45 + (6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30))*100 + (1)*217.5 + (4 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/200))*100 + (1 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/400) + 3*{Addition Living Space})*435 + (4*(1 - {Addition Detached}) + ceil({Addition Structure Removed}/3) + 8*{Addition Wall Openings})*100 + ({Addition Dumpster Loads})*450 + (2 + 2*{Addition Living Space})*100 + (ceil(({Addition Service Zone} - 1)*({Addition Service Zone} + 2)/8*((6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30)) + (4 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/200)) + (4*(1 - {Addition Detached}) + ceil({Addition Structure Removed}/3) + 8*{Addition Wall Openings}) + (2 + 2*{Addition Living Space}) + (16*{Addition Site Excavation}) + (3*{Addition Piers}) + (ceil({Addition Width}*{Addition Depth}*{Addition Stories}/6) + 8*{Addition Wall Openings} + 8*{Addition Roof Tie-In}) + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares}) + (ceil(2.5*{Addition Windows})) + (8*{Addition Exterior Doors} + 8*{Addition Patio Doors} + 3*{Addition Interior Doors}) + (9*{Addition Plumbing Fixtures}) + ({Addition Electrical}*(8 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/16))) + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/12)) + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/15)) + ({Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/25)) + ({Addition Living Space}*(4 + ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/8) + {Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors})))/8))*100 + ({Addition Utility Trench})*17.4 + (16*{Addition Site Excavation})*100 + (2*{Addition Site Excavation})*282.75 + ({Addition Crawl Space}*{Addition Width}*{Addition Depth})*26.2015 + ({Addition Slab}*{Addition Width}*{Addition Depth})*30.45 + ({Addition Basement}*{Addition Width}*{Addition Depth})*47.85 + ({Addition Piers})*725 + (3*{Addition Piers})*100 + ({Addition Width}*{Addition Depth}*{Addition Stories})*32.625 + ({Addition Wall Openings})*580 + (ceil({Addition Width}*{Addition Depth}*{Addition Stories}/6) + 8*{Addition Wall Openings} + 8*{Addition Roof Tie-In})*100 + ({Addition Width} + {Addition Depth} + 20)*11.9625 + ({Addition Width} + {Addition Depth} + 20)*5.075 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*11.6 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*5.85 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*100 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*232 + (2*(1 - {Addition Detached}))*217.5 + (ceil(2.5*{Addition Windows}))*100 + ({Addition Exterior Doors})*1783.5 + ({Addition Garage Doors})*1690 + ({Addition Garage Doors})*152.25 + (8*{Addition Exterior Doors} + 8*{Addition Patio Doors} + 3*{Addition Interior Doors})*100 + ({Addition Plumbing Fixtures})*362.5 + (9*{Addition Plumbing Fixtures})*100 + ({Addition HVAC Extend})*1703 + ({Addition HVAC New Unit})*9750 + ({Addition Electrical}*{Addition Width}*{Addition Depth}*{Addition Stories})*3.7845 + ({Addition Electrical}*(8 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/16)))*100 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*11.076 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.479 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.8995 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/12))*100 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/60))*123.25 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/15))*100 + ({Addition Interior Doors})*580 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.0875 + ({Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/25))*100 + ({Addition Living Space}*ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/12))*65.9605 + ({Addition Living Space}*({Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*53.8095 + ({Addition Living Space}*(4 + ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/8) + {Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*100 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*304.5 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*137.75 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*333.5 + ({Addition Windows})*688.75 + ({Addition Patio Doors})*2537.5 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*5.075)</t>
   </si>
   <si>
     <t xml:space="preserve">C</t>
@@ -1094,7 +1110,7 @@
     <t xml:space="preserve">Contingency — Better</t>
   </si>
   <si>
-    <t xml:space="preserve">{Addition Contingency Rate}/100*((1)*290 + (6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30))*100 + (1)*217.5 + (4 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/200))*100 + (1 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/400) + 3*{Addition Living Space})*435 + (4*(1 - {Addition Detached}) + ceil({Addition Structure Removed}/3) + 8*{Addition Wall Openings})*100 + ({Addition Dumpster Loads})*450 + (2 + 2*{Addition Living Space})*100 + ({Addition Travel Hours})*100 + ({Addition Utility Trench})*17.4 + (16*{Addition Site Excavation})*100 + (2*{Addition Site Excavation})*282.75 + ({Addition Crawl Space}*{Addition Width}*{Addition Depth})*26.2015 + ({Addition Slab}*{Addition Width}*{Addition Depth})*30.45 + ({Addition Basement}*{Addition Width}*{Addition Depth})*47.85 + ({Addition Piers})*725 + (3*{Addition Piers})*100 + ({Addition Width}*{Addition Depth}*{Addition Stories})*32.625 + ({Addition Wall Openings})*580 + (ceil({Addition Width}*{Addition Depth}*{Addition Stories}/6) + 8*{Addition Wall Openings} + 8*{Addition Roof Tie-In})*100 + ({Addition Width} + {Addition Depth} + 20)*11.9625 + ({Addition Width} + {Addition Depth} + 20)*5.075 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*11.6 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*5.85 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*100 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*232 + (2*(1 - {Addition Detached}))*217.5 + (ceil(2.5*{Addition Windows}))*100 + ({Addition Exterior Doors})*1783.5 + ({Addition Garage Doors})*1690 + ({Addition Garage Doors})*152.25 + (8*{Addition Exterior Doors} + 8*{Addition Patio Doors} + 3*{Addition Interior Doors})*100 + ({Addition Plumbing Fixtures})*362.5 + (9*{Addition Plumbing Fixtures})*100 + ({Addition HVAC Extend})*1703 + ({Addition HVAC New Unit})*9750 + ({Addition Electrical}*{Addition Width}*{Addition Depth}*{Addition Stories})*3.7845 + ({Addition Electrical}*(8 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/16)))*100 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*11.076 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.479 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.8995 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/12))*100 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/60))*123.25 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/15))*100 + ({Addition Interior Doors})*580 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.0875 + ({Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/25))*100 + ({Addition Living Space}*ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/12))*65.9605 + ({Addition Living Space}*({Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*53.8095 + ({Addition Living Space}*(4 + ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/8) + {Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*100 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*355.25 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*137.75 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*464 + ({Addition Windows})*1015 + ({Addition Patio Doors})*3625 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*7.25)</t>
+    <t xml:space="preserve">{Addition Contingency Rate}/100*(({Addition Permit Fee})*1.45 + (6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30))*100 + (1)*217.5 + (4 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/200))*100 + (1 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/400) + 3*{Addition Living Space})*435 + (4*(1 - {Addition Detached}) + ceil({Addition Structure Removed}/3) + 8*{Addition Wall Openings})*100 + ({Addition Dumpster Loads})*450 + (2 + 2*{Addition Living Space})*100 + (ceil(({Addition Service Zone} - 1)*({Addition Service Zone} + 2)/8*((6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30)) + (4 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/200)) + (4*(1 - {Addition Detached}) + ceil({Addition Structure Removed}/3) + 8*{Addition Wall Openings}) + (2 + 2*{Addition Living Space}) + (16*{Addition Site Excavation}) + (3*{Addition Piers}) + (ceil({Addition Width}*{Addition Depth}*{Addition Stories}/6) + 8*{Addition Wall Openings} + 8*{Addition Roof Tie-In}) + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares}) + (ceil(2.5*{Addition Windows})) + (8*{Addition Exterior Doors} + 8*{Addition Patio Doors} + 3*{Addition Interior Doors}) + (9*{Addition Plumbing Fixtures}) + ({Addition Electrical}*(8 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/16))) + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/12)) + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/15)) + ({Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/25)) + ({Addition Living Space}*(4 + ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/8) + {Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors})))/8))*100 + ({Addition Utility Trench})*17.4 + (16*{Addition Site Excavation})*100 + (2*{Addition Site Excavation})*282.75 + ({Addition Crawl Space}*{Addition Width}*{Addition Depth})*26.2015 + ({Addition Slab}*{Addition Width}*{Addition Depth})*30.45 + ({Addition Basement}*{Addition Width}*{Addition Depth})*47.85 + ({Addition Piers})*725 + (3*{Addition Piers})*100 + ({Addition Width}*{Addition Depth}*{Addition Stories})*32.625 + ({Addition Wall Openings})*580 + (ceil({Addition Width}*{Addition Depth}*{Addition Stories}/6) + 8*{Addition Wall Openings} + 8*{Addition Roof Tie-In})*100 + ({Addition Width} + {Addition Depth} + 20)*11.9625 + ({Addition Width} + {Addition Depth} + 20)*5.075 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*11.6 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*5.85 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*100 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*232 + (2*(1 - {Addition Detached}))*217.5 + (ceil(2.5*{Addition Windows}))*100 + ({Addition Exterior Doors})*1783.5 + ({Addition Garage Doors})*1690 + ({Addition Garage Doors})*152.25 + (8*{Addition Exterior Doors} + 8*{Addition Patio Doors} + 3*{Addition Interior Doors})*100 + ({Addition Plumbing Fixtures})*362.5 + (9*{Addition Plumbing Fixtures})*100 + ({Addition HVAC Extend})*1703 + ({Addition HVAC New Unit})*9750 + ({Addition Electrical}*{Addition Width}*{Addition Depth}*{Addition Stories})*3.7845 + ({Addition Electrical}*(8 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/16)))*100 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*11.076 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.479 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.8995 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/12))*100 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/60))*123.25 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/15))*100 + ({Addition Interior Doors})*580 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.0875 + ({Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/25))*100 + ({Addition Living Space}*ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/12))*65.9605 + ({Addition Living Space}*({Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*53.8095 + ({Addition Living Space}*(4 + ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/8) + {Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*100 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*355.25 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*137.75 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*464 + ({Addition Windows})*1015 + ({Addition Patio Doors})*3625 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*7.25)</t>
   </si>
   <si>
     <t xml:space="preserve">BALLPARK — Addition &gt; Finish Level (select one) &gt; Best</t>
@@ -1103,7 +1119,7 @@
     <t xml:space="preserve">Contingency — Best</t>
   </si>
   <si>
-    <t xml:space="preserve">{Addition Contingency Rate}/100*((1)*290 + (6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30))*100 + (1)*217.5 + (4 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/200))*100 + (1 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/400) + 3*{Addition Living Space})*435 + (4*(1 - {Addition Detached}) + ceil({Addition Structure Removed}/3) + 8*{Addition Wall Openings})*100 + ({Addition Dumpster Loads})*450 + (2 + 2*{Addition Living Space})*100 + ({Addition Travel Hours})*100 + ({Addition Utility Trench})*17.4 + (16*{Addition Site Excavation})*100 + (2*{Addition Site Excavation})*282.75 + ({Addition Crawl Space}*{Addition Width}*{Addition Depth})*26.2015 + ({Addition Slab}*{Addition Width}*{Addition Depth})*30.45 + ({Addition Basement}*{Addition Width}*{Addition Depth})*47.85 + ({Addition Piers})*725 + (3*{Addition Piers})*100 + ({Addition Width}*{Addition Depth}*{Addition Stories})*32.625 + ({Addition Wall Openings})*580 + (ceil({Addition Width}*{Addition Depth}*{Addition Stories}/6) + 8*{Addition Wall Openings} + 8*{Addition Roof Tie-In})*100 + ({Addition Width} + {Addition Depth} + 20)*11.9625 + ({Addition Width} + {Addition Depth} + 20)*5.075 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*11.6 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*5.85 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*100 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*232 + (2*(1 - {Addition Detached}))*217.5 + (ceil(2.5*{Addition Windows}))*100 + ({Addition Exterior Doors})*1783.5 + ({Addition Garage Doors})*1690 + ({Addition Garage Doors})*152.25 + (8*{Addition Exterior Doors} + 8*{Addition Patio Doors} + 3*{Addition Interior Doors})*100 + ({Addition Plumbing Fixtures})*362.5 + (9*{Addition Plumbing Fixtures})*100 + ({Addition HVAC Extend})*1703 + ({Addition HVAC New Unit})*9750 + ({Addition Electrical}*{Addition Width}*{Addition Depth}*{Addition Stories})*3.7845 + ({Addition Electrical}*(8 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/16)))*100 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*11.076 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.479 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.8995 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/12))*100 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/60))*123.25 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/15))*100 + ({Addition Interior Doors})*580 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.0875 + ({Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/25))*100 + ({Addition Living Space}*ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/12))*65.9605 + ({Addition Living Space}*({Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*53.8095 + ({Addition Living Space}*(4 + ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/8) + {Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*100 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*453.85 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*290 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*717.75 + ({Addition Windows})*1595 + ({Addition Patio Doors})*4350 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*13.05)</t>
+    <t xml:space="preserve">{Addition Contingency Rate}/100*(({Addition Permit Fee})*1.45 + (6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30))*100 + (1)*217.5 + (4 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/200))*100 + (1 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/400) + 3*{Addition Living Space})*435 + (4*(1 - {Addition Detached}) + ceil({Addition Structure Removed}/3) + 8*{Addition Wall Openings})*100 + ({Addition Dumpster Loads})*450 + (2 + 2*{Addition Living Space})*100 + (ceil(({Addition Service Zone} - 1)*({Addition Service Zone} + 2)/8*((6 + {Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/30)) + (4 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/200)) + (4*(1 - {Addition Detached}) + ceil({Addition Structure Removed}/3) + 8*{Addition Wall Openings}) + (2 + 2*{Addition Living Space}) + (16*{Addition Site Excavation}) + (3*{Addition Piers}) + (ceil({Addition Width}*{Addition Depth}*{Addition Stories}/6) + 8*{Addition Wall Openings} + 8*{Addition Roof Tie-In}) + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares}) + (ceil(2.5*{Addition Windows})) + (8*{Addition Exterior Doors} + 8*{Addition Patio Doors} + 3*{Addition Interior Doors}) + (9*{Addition Plumbing Fixtures}) + ({Addition Electrical}*(8 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/16))) + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/12)) + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/15)) + ({Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/25)) + ({Addition Living Space}*(4 + ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/8) + {Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors})))/8))*100 + ({Addition Utility Trench})*17.4 + (16*{Addition Site Excavation})*100 + (2*{Addition Site Excavation})*282.75 + ({Addition Crawl Space}*{Addition Width}*{Addition Depth})*26.2015 + ({Addition Slab}*{Addition Width}*{Addition Depth})*30.45 + ({Addition Basement}*{Addition Width}*{Addition Depth})*47.85 + ({Addition Piers})*725 + (3*{Addition Piers})*100 + ({Addition Width}*{Addition Depth}*{Addition Stories})*32.625 + ({Addition Wall Openings})*580 + (ceil({Addition Width}*{Addition Depth}*{Addition Stories}/6) + 8*{Addition Wall Openings} + 8*{Addition Roof Tie-In})*100 + ({Addition Width} + {Addition Depth} + 20)*11.9625 + ({Addition Width} + {Addition Depth} + 20)*5.075 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*11.6 + (({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width}))*5.85 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*100 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*232 + (2*(1 - {Addition Detached}))*217.5 + (ceil(2.5*{Addition Windows}))*100 + ({Addition Exterior Doors})*1783.5 + ({Addition Garage Doors})*1690 + ({Addition Garage Doors})*152.25 + (8*{Addition Exterior Doors} + 8*{Addition Patio Doors} + 3*{Addition Interior Doors})*100 + ({Addition Plumbing Fixtures})*362.5 + (9*{Addition Plumbing Fixtures})*100 + ({Addition HVAC Extend})*1703 + ({Addition HVAC New Unit})*9750 + ({Addition Electrical}*{Addition Width}*{Addition Depth}*{Addition Stories})*3.7845 + ({Addition Electrical}*(8 + ceil({Addition Width}*{Addition Depth}*{Addition Stories}/16)))*100 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*11.076 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.479 + ({Addition Drywall}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.8995 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/12))*100 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/60))*123.25 + ({Addition Drywall}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/15))*100 + ({Addition Interior Doors})*580 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*1.0875 + ({Addition Living Space}*ceil({Addition Width}*{Addition Depth}*{Addition Stories}/25))*100 + ({Addition Living Space}*ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/12))*65.9605 + ({Addition Living Space}*({Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*53.8095 + ({Addition Living Space}*(4 + ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Stories}/8) + {Addition Windows} + {Addition Exterior Doors} + {Addition Patio Doors}))*100 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*453.85 + (ceil({Addition Width}*{Addition Depth}*1.25/100) + 2*{Addition Roof Tie-In})*290 + (ceil(({Addition Width} + 2*{Addition Depth} + {Addition Detached}*{Addition Width})*{Addition Wall Height}*{Addition Stories}*1.15/100) + {Addition Extra Siding Squares})*717.75 + ({Addition Windows})*1595 + ({Addition Patio Doors})*4350 + ({Addition Living Space}*{Addition Width}*{Addition Depth}*{Addition Stories})*13.05)</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -1133,55 +1149,58 @@
     <t xml:space="preserve">Number</t>
   </si>
   <si>
-    <t xml:space="preserve">Concrete Foundation - 6" Stem, Concrete Foundation - Basement, Concrete Foundation - Crawl, Drywall Board - Mat, Drywall Labor, Drywall Mud - Mat, Electrical Labor, Electrical Materials, Fascia and Soffit Install, Flooring - Misc. Material, Flooring Labor, Flooring Material, Framing/Sheathing Labor, Framing/Sheathing Materials, Gutter Labor, Gutters &amp; Downspouts, House Wrap Labor, Insulation - Sub, Paint, Paint Labor, Project Management (C), Rentals &amp; Delivery, Roofing Install, Roofing Material, Siding Labor, Siding Material, Site Prep Labor, Soffit &amp; Fascia Material, Trim - Baseboard, Trim Labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drywall Board - Mat, Drywall Labor, Drywall Mud - Mat, Electrical Labor, Electrical Materials, Flooring - Misc. Material, Flooring Labor, Flooring Material, Framing/Sheathing Labor, Framing/Sheathing Materials, House Wrap Labor, Insulation - Sub, Paint, Paint Labor, Project Management (C), Rentals &amp; Delivery, Siding Labor, Siding Material, Site Prep Labor, Trim - Baseboard, Trim Labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House Wrap Labor, Siding Labor, Siding Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demolition, Fascia and Soffit Install, House Wrap Labor, Siding Labor, Siding Labor for Flashing, Siding Material, Soffit &amp; Fascia Material, Trim - Baseboard, Trim Labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concrete Piers, Pier Labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excavation &amp; Grading, Rental - Mini Excavator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Framing/Sheathing Labor, Roofing Install, Roofing Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical Labor, Electrical Materials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drywall Board - Mat, Drywall Labor, Drywall Mud - Mat, Insulation - Sub, Paint, Paint Labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Clean, Flooring - Misc. Material, Flooring Labor, Flooring Material, Project Management (C), Rentals &amp; Delivery, Trim - Baseboard, Trim - Casing, Trim Labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trim - Casing, Trim Labor, Window Labor, Windows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Door Labor, Exterior Door &amp; Lockset, Trim - Casing, Trim Labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Door Labor, Patio Door, Trim - Casing, Trim Labor</t>
+    <t xml:space="preserve">Concrete Foundation - 6" Stem, Concrete Foundation - Basement, Concrete Foundation - Crawl, Drywall Board - Mat, Drywall Labor, Drywall Mud - Mat, Electrical Labor, Electrical Materials, Fascia and Soffit Install, Flooring - Misc. Material, Flooring Labor, Flooring Material, Framing/Sheathing Labor, Framing/Sheathing Materials, Gutter Labor, Gutters &amp; Downspouts, House Wrap Labor, Insulation - Sub, Paint, Paint Labor, Project Management (C), Rentals &amp; Delivery, Roofing Install, Roofing Material, Siding Labor, Siding Material, Site Prep Labor, Soffit &amp; Fascia Material, Travel, Trim - Baseboard, Trim Labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drywall Board - Mat, Drywall Labor, Drywall Mud - Mat, Electrical Labor, Electrical Materials, Flooring - Misc. Material, Flooring Labor, Flooring Material, Framing/Sheathing Labor, Framing/Sheathing Materials, House Wrap Labor, Insulation - Sub, Paint, Paint Labor, Project Management (C), Rentals &amp; Delivery, Siding Labor, Siding Material, Site Prep Labor, Travel, Trim - Baseboard, Trim Labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House Wrap Labor, Siding Labor, Siding Material, Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demolition, Fascia and Soffit Install, House Wrap Labor, Siding Labor, Siding Labor for Flashing, Siding Material, Soffit &amp; Fascia Material, Travel, Trim - Baseboard, Trim Labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concrete Piers, Pier Labor, Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excavation &amp; Grading, Rental - Mini Excavator, Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Framing/Sheathing Labor, Roofing Install, Roofing Material, Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electrical Labor, Electrical Materials, Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drywall Board - Mat, Drywall Labor, Drywall Mud - Mat, Insulation - Sub, Paint, Paint Labor, Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Clean, Flooring - Misc. Material, Flooring Labor, Flooring Material, Project Management (C), Rentals &amp; Delivery, Travel, Trim - Baseboard, Trim - Casing, Trim Labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel, Trim - Casing, Trim Labor, Window Labor, Windows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Door Labor, Exterior Door &amp; Lockset, Travel, Trim - Casing, Trim Labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Door Labor, Patio Door, Travel, Trim - Casing, Trim Labor</t>
   </si>
   <si>
     <t xml:space="preserve">Garage Door, Garage Door Wrapping</t>
   </si>
   <si>
-    <t xml:space="preserve">Door Labor, Interior Door</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demolition, Framing/Sheathing Labor, Header &amp; Opening Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plumbing Labor, Plumbing Materials</t>
+    <t xml:space="preserve">Door Labor, Interior Door, Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demolition, Framing/Sheathing Labor, Header &amp; Opening Material, Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plumbing Labor, Plumbing Materials, Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demolition, Travel</t>
   </si>
   <si>
     <t xml:space="preserve">Markup by cost type</t>
@@ -1242,6 +1261,84 @@
   </si>
   <si>
     <t xml:space="preserve">Additions are quoted at ±20% and always go on to the Design &amp; Pricing Agreement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permit fees by jurisdiction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB's vendor bills for permits, last 6 months. Enter the job's fee as the Permit Fee parameter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jurisdiction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fee DB pays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Village of Convoy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City of Van Wert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$20 for the first $10K of project cost, plus $2 per additional $1K (paid $20–$122, average $36)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City of Lima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$75.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Union Township</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pleasant Township Trustees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deitemeyer Brothers internal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$32–$40, average $36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel by service zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours per person-day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone 1 (within ~15 mi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone 2 (~15–30 mi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone 3 (~30–50 mi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended (over 50 mi): quote by hand</t>
   </si>
   <si>
     <t xml:space="preserve">Checks against DB's addition estimates since the move to JobTread</t>
@@ -2322,7 +2419,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
@@ -3031,7 +3128,7 @@
         <v>130</v>
       </c>
       <c r="B32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>131</v>
@@ -3063,6 +3160,25 @@
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3096,7 +3212,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3121,7 +3237,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3169,67 +3285,67 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3237,61 +3353,61 @@
         <v>1</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="G5" s="20" t="n">
-        <f aca="false">1</f>
+        <f aca="false">p_Addition_Permit_Fee</f>
+        <v>200</v>
+      </c>
+      <c r="H5" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="21" t="n">
-        <v>200</v>
-      </c>
       <c r="I5" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J5" s="23" t="n">
         <f aca="false">H5*INDEX(MarkupVals,MATCH(I5,MarkupCodes,0))</f>
-        <v>290</v>
+        <v>1.45</v>
       </c>
       <c r="K5" s="24" t="n">
         <f aca="false">G5*J5</f>
         <v>290</v>
       </c>
       <c r="L5" s="21" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="M5" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N5" s="23" t="n">
         <f aca="false">L5*INDEX(MarkupVals,MATCH(M5,MarkupCodes,0))</f>
-        <v>290</v>
+        <v>1.45</v>
       </c>
       <c r="O5" s="24" t="n">
         <f aca="false">G5*N5</f>
         <v>290</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="R5" s="23" t="n">
         <f aca="false">P5*INDEX(MarkupVals,MATCH(Q5,MarkupCodes,0))</f>
-        <v>290</v>
+        <v>1.45</v>
       </c>
       <c r="S5" s="24" t="n">
         <f aca="false">G5*R5</f>
@@ -3299,7 +3415,7 @@
       </c>
       <c r="T5" s="25"/>
       <c r="U5" s="26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3307,19 +3423,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G6" s="20" t="n">
         <f aca="false">6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0)</f>
@@ -3330,7 +3446,7 @@
         <v>55</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J6" s="23" t="n">
         <f aca="false">H6*INDEX(MarkupVals,MATCH(I6,MarkupCodes,0))</f>
@@ -3345,7 +3461,7 @@
         <v>55</v>
       </c>
       <c r="M6" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N6" s="23" t="n">
         <f aca="false">L6*INDEX(MarkupVals,MATCH(M6,MarkupCodes,0))</f>
@@ -3360,7 +3476,7 @@
         <v>55</v>
       </c>
       <c r="Q6" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R6" s="23" t="n">
         <f aca="false">P6*INDEX(MarkupVals,MATCH(Q6,MarkupCodes,0))</f>
@@ -3378,19 +3494,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="G7" s="20" t="n">
         <f aca="false">1</f>
@@ -3400,7 +3516,7 @@
         <v>150</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J7" s="23" t="n">
         <f aca="false">H7*INDEX(MarkupVals,MATCH(I7,MarkupCodes,0))</f>
@@ -3414,7 +3530,7 @@
         <v>150</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N7" s="23" t="n">
         <f aca="false">L7*INDEX(MarkupVals,MATCH(M7,MarkupCodes,0))</f>
@@ -3428,7 +3544,7 @@
         <v>150</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R7" s="23" t="n">
         <f aca="false">P7*INDEX(MarkupVals,MATCH(Q7,MarkupCodes,0))</f>
@@ -3446,19 +3562,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G8" s="20" t="n">
         <f aca="false">4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0)</f>
@@ -3469,7 +3585,7 @@
         <v>55</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J8" s="23" t="n">
         <f aca="false">H8*INDEX(MarkupVals,MATCH(I8,MarkupCodes,0))</f>
@@ -3484,7 +3600,7 @@
         <v>55</v>
       </c>
       <c r="M8" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N8" s="23" t="n">
         <f aca="false">L8*INDEX(MarkupVals,MATCH(M8,MarkupCodes,0))</f>
@@ -3499,7 +3615,7 @@
         <v>55</v>
       </c>
       <c r="Q8" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R8" s="23" t="n">
         <f aca="false">P8*INDEX(MarkupVals,MATCH(Q8,MarkupCodes,0))</f>
@@ -3517,19 +3633,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G9" s="20" t="n">
         <f aca="false">1 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/400,0) + 3*p_Addition_Living_Space</f>
@@ -3539,7 +3655,7 @@
         <v>300</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J9" s="23" t="n">
         <f aca="false">H9*INDEX(MarkupVals,MATCH(I9,MarkupCodes,0))</f>
@@ -3553,7 +3669,7 @@
         <v>300</v>
       </c>
       <c r="M9" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N9" s="23" t="n">
         <f aca="false">L9*INDEX(MarkupVals,MATCH(M9,MarkupCodes,0))</f>
@@ -3567,7 +3683,7 @@
         <v>300</v>
       </c>
       <c r="Q9" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="R9" s="23" t="n">
         <f aca="false">P9*INDEX(MarkupVals,MATCH(Q9,MarkupCodes,0))</f>
@@ -3579,7 +3695,7 @@
       </c>
       <c r="T9" s="25"/>
       <c r="U9" s="26" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3587,19 +3703,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G10" s="20" t="n">
         <f aca="false">4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings</f>
@@ -3610,7 +3726,7 @@
         <v>55</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J10" s="23" t="n">
         <f aca="false">H10*INDEX(MarkupVals,MATCH(I10,MarkupCodes,0))</f>
@@ -3625,7 +3741,7 @@
         <v>55</v>
       </c>
       <c r="M10" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N10" s="23" t="n">
         <f aca="false">L10*INDEX(MarkupVals,MATCH(M10,MarkupCodes,0))</f>
@@ -3640,7 +3756,7 @@
         <v>55</v>
       </c>
       <c r="Q10" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R10" s="23" t="n">
         <f aca="false">P10*INDEX(MarkupVals,MATCH(Q10,MarkupCodes,0))</f>
@@ -3652,7 +3768,7 @@
       </c>
       <c r="T10" s="25"/>
       <c r="U10" s="26" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3660,16 +3776,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>129</v>
@@ -3682,7 +3798,7 @@
         <v>250</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J11" s="21" t="n">
         <v>450</v>
@@ -3695,7 +3811,7 @@
         <v>250</v>
       </c>
       <c r="M11" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N11" s="21" t="n">
         <v>450</v>
@@ -3708,7 +3824,7 @@
         <v>250</v>
       </c>
       <c r="Q11" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R11" s="21" t="n">
         <v>450</v>
@@ -3719,7 +3835,7 @@
       </c>
       <c r="T11" s="25"/>
       <c r="U11" s="26" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3727,19 +3843,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G12" s="20" t="n">
         <f aca="false">2 + 2*p_Addition_Living_Space</f>
@@ -3750,7 +3866,7 @@
         <v>55</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J12" s="23" t="n">
         <f aca="false">H12*INDEX(MarkupVals,MATCH(I12,MarkupCodes,0))</f>
@@ -3765,7 +3881,7 @@
         <v>55</v>
       </c>
       <c r="M12" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N12" s="23" t="n">
         <f aca="false">L12*INDEX(MarkupVals,MATCH(M12,MarkupCodes,0))</f>
@@ -3780,7 +3896,7 @@
         <v>55</v>
       </c>
       <c r="Q12" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R12" s="23" t="n">
         <f aca="false">P12*INDEX(MarkupVals,MATCH(Q12,MarkupCodes,0))</f>
@@ -3798,22 +3914,22 @@
         <v>9</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="G13" s="20" t="n">
-        <f aca="false">p_Addition_Travel_Hours</f>
+        <f aca="false">ROUNDUP((p_Addition_Service_Zone - 1)*(p_Addition_Service_Zone + 2)/8*((6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0)) + (4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0)) + (4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings) + (2 + 2*p_Addition_Living_Space) + (16*p_Addition_Site_Excavation) + (3*p_Addition_Piers) + (ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In) + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares) + (ROUNDUP(2.5*p_Addition_Windows,0)) + (8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors) + (9*p_Addition_Plumbing_Fixtures) + (p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0))) + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0)) + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0)) + (p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0)) + (p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors)))/8,0)</f>
         <v>0</v>
       </c>
       <c r="H13" s="23" t="n">
@@ -3821,7 +3937,7 @@
         <v>55</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J13" s="23" t="n">
         <f aca="false">H13*INDEX(MarkupVals,MATCH(I13,MarkupCodes,0))</f>
@@ -3836,7 +3952,7 @@
         <v>55</v>
       </c>
       <c r="M13" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N13" s="23" t="n">
         <f aca="false">L13*INDEX(MarkupVals,MATCH(M13,MarkupCodes,0))</f>
@@ -3851,7 +3967,7 @@
         <v>55</v>
       </c>
       <c r="Q13" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R13" s="23" t="n">
         <f aca="false">P13*INDEX(MarkupVals,MATCH(Q13,MarkupCodes,0))</f>
@@ -3862,23 +3978,25 @@
         <v>0</v>
       </c>
       <c r="T13" s="25"/>
-      <c r="U13" s="26"/>
+      <c r="U13" s="26" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F14" s="19" t="s">
         <v>126</v>
@@ -3891,7 +4009,7 @@
         <v>12</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J14" s="23" t="n">
         <f aca="false">H14*INDEX(MarkupVals,MATCH(I14,MarkupCodes,0))</f>
@@ -3905,7 +4023,7 @@
         <v>12</v>
       </c>
       <c r="M14" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N14" s="23" t="n">
         <f aca="false">L14*INDEX(MarkupVals,MATCH(M14,MarkupCodes,0))</f>
@@ -3919,7 +4037,7 @@
         <v>12</v>
       </c>
       <c r="Q14" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="R14" s="23" t="n">
         <f aca="false">P14*INDEX(MarkupVals,MATCH(Q14,MarkupCodes,0))</f>
@@ -3931,7 +4049,7 @@
       </c>
       <c r="T14" s="25"/>
       <c r="U14" s="26" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3939,19 +4057,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="G15" s="20" t="n">
         <f aca="false">16*p_Addition_Site_Excavation</f>
@@ -3962,7 +4080,7 @@
         <v>55</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J15" s="23" t="n">
         <f aca="false">H15*INDEX(MarkupVals,MATCH(I15,MarkupCodes,0))</f>
@@ -3977,7 +4095,7 @@
         <v>55</v>
       </c>
       <c r="M15" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N15" s="23" t="n">
         <f aca="false">L15*INDEX(MarkupVals,MATCH(M15,MarkupCodes,0))</f>
@@ -3992,7 +4110,7 @@
         <v>55</v>
       </c>
       <c r="Q15" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R15" s="23" t="n">
         <f aca="false">P15*INDEX(MarkupVals,MATCH(Q15,MarkupCodes,0))</f>
@@ -4004,7 +4122,7 @@
       </c>
       <c r="T15" s="25"/>
       <c r="U15" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4012,19 +4130,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G16" s="20" t="n">
         <f aca="false">2*p_Addition_Site_Excavation</f>
@@ -4034,7 +4152,7 @@
         <v>195</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J16" s="23" t="n">
         <f aca="false">H16*INDEX(MarkupVals,MATCH(I16,MarkupCodes,0))</f>
@@ -4048,7 +4166,7 @@
         <v>195</v>
       </c>
       <c r="M16" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N16" s="23" t="n">
         <f aca="false">L16*INDEX(MarkupVals,MATCH(M16,MarkupCodes,0))</f>
@@ -4062,7 +4180,7 @@
         <v>195</v>
       </c>
       <c r="Q16" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="R16" s="23" t="n">
         <f aca="false">P16*INDEX(MarkupVals,MATCH(Q16,MarkupCodes,0))</f>
@@ -4080,19 +4198,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G17" s="20" t="n">
         <f aca="false">p_Addition_Crawl_Space*p_Addition_Width*p_Addition_Depth</f>
@@ -4102,7 +4220,7 @@
         <v>18.07</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J17" s="23" t="n">
         <f aca="false">H17*INDEX(MarkupVals,MATCH(I17,MarkupCodes,0))</f>
@@ -4116,7 +4234,7 @@
         <v>18.07</v>
       </c>
       <c r="M17" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N17" s="23" t="n">
         <f aca="false">L17*INDEX(MarkupVals,MATCH(M17,MarkupCodes,0))</f>
@@ -4130,7 +4248,7 @@
         <v>18.07</v>
       </c>
       <c r="Q17" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R17" s="23" t="n">
         <f aca="false">P17*INDEX(MarkupVals,MATCH(Q17,MarkupCodes,0))</f>
@@ -4142,7 +4260,7 @@
       </c>
       <c r="T17" s="25"/>
       <c r="U17" s="26" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4150,19 +4268,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G18" s="20" t="n">
         <f aca="false">p_Addition_Slab*p_Addition_Width*p_Addition_Depth</f>
@@ -4172,7 +4290,7 @@
         <v>21</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J18" s="23" t="n">
         <f aca="false">H18*INDEX(MarkupVals,MATCH(I18,MarkupCodes,0))</f>
@@ -4186,7 +4304,7 @@
         <v>21</v>
       </c>
       <c r="M18" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N18" s="23" t="n">
         <f aca="false">L18*INDEX(MarkupVals,MATCH(M18,MarkupCodes,0))</f>
@@ -4200,7 +4318,7 @@
         <v>21</v>
       </c>
       <c r="Q18" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R18" s="23" t="n">
         <f aca="false">P18*INDEX(MarkupVals,MATCH(Q18,MarkupCodes,0))</f>
@@ -4212,7 +4330,7 @@
       </c>
       <c r="T18" s="25"/>
       <c r="U18" s="26" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4220,19 +4338,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G19" s="20" t="n">
         <f aca="false">p_Addition_Basement*p_Addition_Width*p_Addition_Depth</f>
@@ -4242,7 +4360,7 @@
         <v>33</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J19" s="23" t="n">
         <f aca="false">H19*INDEX(MarkupVals,MATCH(I19,MarkupCodes,0))</f>
@@ -4256,7 +4374,7 @@
         <v>33</v>
       </c>
       <c r="M19" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N19" s="23" t="n">
         <f aca="false">L19*INDEX(MarkupVals,MATCH(M19,MarkupCodes,0))</f>
@@ -4270,7 +4388,7 @@
         <v>33</v>
       </c>
       <c r="Q19" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R19" s="23" t="n">
         <f aca="false">P19*INDEX(MarkupVals,MATCH(Q19,MarkupCodes,0))</f>
@@ -4282,7 +4400,7 @@
       </c>
       <c r="T19" s="25"/>
       <c r="U19" s="26" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4290,16 +4408,16 @@
         <v>16</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F20" s="19" t="s">
         <v>70</v>
@@ -4312,7 +4430,7 @@
         <v>500</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J20" s="23" t="n">
         <f aca="false">H20*INDEX(MarkupVals,MATCH(I20,MarkupCodes,0))</f>
@@ -4326,7 +4444,7 @@
         <v>500</v>
       </c>
       <c r="M20" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N20" s="23" t="n">
         <f aca="false">L20*INDEX(MarkupVals,MATCH(M20,MarkupCodes,0))</f>
@@ -4340,7 +4458,7 @@
         <v>500</v>
       </c>
       <c r="Q20" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R20" s="23" t="n">
         <f aca="false">P20*INDEX(MarkupVals,MATCH(Q20,MarkupCodes,0))</f>
@@ -4352,7 +4470,7 @@
       </c>
       <c r="T20" s="25"/>
       <c r="U20" s="26" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4360,19 +4478,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="G21" s="20" t="n">
         <f aca="false">3*p_Addition_Piers</f>
@@ -4383,7 +4501,7 @@
         <v>55</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J21" s="23" t="n">
         <f aca="false">H21*INDEX(MarkupVals,MATCH(I21,MarkupCodes,0))</f>
@@ -4398,7 +4516,7 @@
         <v>55</v>
       </c>
       <c r="M21" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N21" s="23" t="n">
         <f aca="false">L21*INDEX(MarkupVals,MATCH(M21,MarkupCodes,0))</f>
@@ -4413,7 +4531,7 @@
         <v>55</v>
       </c>
       <c r="Q21" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R21" s="23" t="n">
         <f aca="false">P21*INDEX(MarkupVals,MATCH(Q21,MarkupCodes,0))</f>
@@ -4431,19 +4549,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="G22" s="20" t="n">
         <f aca="false">p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -4453,7 +4571,7 @@
         <v>22.5</v>
       </c>
       <c r="I22" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J22" s="23" t="n">
         <f aca="false">H22*INDEX(MarkupVals,MATCH(I22,MarkupCodes,0))</f>
@@ -4467,7 +4585,7 @@
         <v>22.5</v>
       </c>
       <c r="M22" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N22" s="23" t="n">
         <f aca="false">L22*INDEX(MarkupVals,MATCH(M22,MarkupCodes,0))</f>
@@ -4481,7 +4599,7 @@
         <v>22.5</v>
       </c>
       <c r="Q22" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R22" s="23" t="n">
         <f aca="false">P22*INDEX(MarkupVals,MATCH(Q22,MarkupCodes,0))</f>
@@ -4493,7 +4611,7 @@
       </c>
       <c r="T22" s="25"/>
       <c r="U22" s="26" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4501,16 +4619,16 @@
         <v>19</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F23" s="19" t="s">
         <v>108</v>
@@ -4523,7 +4641,7 @@
         <v>400</v>
       </c>
       <c r="I23" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J23" s="23" t="n">
         <f aca="false">H23*INDEX(MarkupVals,MATCH(I23,MarkupCodes,0))</f>
@@ -4537,7 +4655,7 @@
         <v>400</v>
       </c>
       <c r="M23" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N23" s="23" t="n">
         <f aca="false">L23*INDEX(MarkupVals,MATCH(M23,MarkupCodes,0))</f>
@@ -4551,7 +4669,7 @@
         <v>400</v>
       </c>
       <c r="Q23" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R23" s="23" t="n">
         <f aca="false">P23*INDEX(MarkupVals,MATCH(Q23,MarkupCodes,0))</f>
@@ -4569,19 +4687,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="G24" s="20" t="n">
         <f aca="false">ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In</f>
@@ -4592,7 +4710,7 @@
         <v>55</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J24" s="23" t="n">
         <f aca="false">H24*INDEX(MarkupVals,MATCH(I24,MarkupCodes,0))</f>
@@ -4607,7 +4725,7 @@
         <v>55</v>
       </c>
       <c r="M24" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N24" s="23" t="n">
         <f aca="false">L24*INDEX(MarkupVals,MATCH(M24,MarkupCodes,0))</f>
@@ -4622,7 +4740,7 @@
         <v>55</v>
       </c>
       <c r="Q24" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R24" s="23" t="n">
         <f aca="false">P24*INDEX(MarkupVals,MATCH(Q24,MarkupCodes,0))</f>
@@ -4634,7 +4752,7 @@
       </c>
       <c r="T24" s="25"/>
       <c r="U24" s="26" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4642,19 +4760,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="G25" s="20" t="n">
         <f aca="false">p_Addition_Width + p_Addition_Depth + 20</f>
@@ -4664,7 +4782,7 @@
         <v>8.25</v>
       </c>
       <c r="I25" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J25" s="23" t="n">
         <f aca="false">H25*INDEX(MarkupVals,MATCH(I25,MarkupCodes,0))</f>
@@ -4678,7 +4796,7 @@
         <v>8.25</v>
       </c>
       <c r="M25" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N25" s="23" t="n">
         <f aca="false">L25*INDEX(MarkupVals,MATCH(M25,MarkupCodes,0))</f>
@@ -4692,7 +4810,7 @@
         <v>8.25</v>
       </c>
       <c r="Q25" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R25" s="23" t="n">
         <f aca="false">P25*INDEX(MarkupVals,MATCH(Q25,MarkupCodes,0))</f>
@@ -4704,7 +4822,7 @@
       </c>
       <c r="T25" s="25"/>
       <c r="U25" s="26" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4712,19 +4830,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="G26" s="20" t="n">
         <f aca="false">p_Addition_Width + p_Addition_Depth + 20</f>
@@ -4734,7 +4852,7 @@
         <v>3.5</v>
       </c>
       <c r="I26" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="J26" s="23" t="n">
         <f aca="false">H26*INDEX(MarkupVals,MATCH(I26,MarkupCodes,0))</f>
@@ -4748,7 +4866,7 @@
         <v>3.5</v>
       </c>
       <c r="M26" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="N26" s="23" t="n">
         <f aca="false">L26*INDEX(MarkupVals,MATCH(M26,MarkupCodes,0))</f>
@@ -4762,7 +4880,7 @@
         <v>3.5</v>
       </c>
       <c r="Q26" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="R26" s="23" t="n">
         <f aca="false">P26*INDEX(MarkupVals,MATCH(Q26,MarkupCodes,0))</f>
@@ -4780,19 +4898,19 @@
         <v>23</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G27" s="20" t="n">
         <f aca="false">(p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)</f>
@@ -4802,7 +4920,7 @@
         <v>8</v>
       </c>
       <c r="I27" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J27" s="23" t="n">
         <f aca="false">H27*INDEX(MarkupVals,MATCH(I27,MarkupCodes,0))</f>
@@ -4816,7 +4934,7 @@
         <v>8</v>
       </c>
       <c r="M27" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N27" s="23" t="n">
         <f aca="false">L27*INDEX(MarkupVals,MATCH(M27,MarkupCodes,0))</f>
@@ -4830,7 +4948,7 @@
         <v>8</v>
       </c>
       <c r="Q27" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R27" s="23" t="n">
         <f aca="false">P27*INDEX(MarkupVals,MATCH(Q27,MarkupCodes,0))</f>
@@ -4848,19 +4966,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G28" s="20" t="n">
         <f aca="false">(p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)</f>
@@ -4870,7 +4988,7 @@
         <v>4.5</v>
       </c>
       <c r="I28" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J28" s="23" t="n">
         <f aca="false">H28*INDEX(MarkupVals,MATCH(I28,MarkupCodes,0))</f>
@@ -4884,7 +5002,7 @@
         <v>4.5</v>
       </c>
       <c r="M28" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N28" s="23" t="n">
         <f aca="false">L28*INDEX(MarkupVals,MATCH(M28,MarkupCodes,0))</f>
@@ -4898,7 +5016,7 @@
         <v>4.5</v>
       </c>
       <c r="Q28" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="R28" s="23" t="n">
         <f aca="false">P28*INDEX(MarkupVals,MATCH(Q28,MarkupCodes,0))</f>
@@ -4916,19 +5034,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G29" s="20" t="n">
         <f aca="false">ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares</f>
@@ -4939,7 +5057,7 @@
         <v>55</v>
       </c>
       <c r="I29" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J29" s="23" t="n">
         <f aca="false">H29*INDEX(MarkupVals,MATCH(I29,MarkupCodes,0))</f>
@@ -4954,7 +5072,7 @@
         <v>55</v>
       </c>
       <c r="M29" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N29" s="23" t="n">
         <f aca="false">L29*INDEX(MarkupVals,MATCH(M29,MarkupCodes,0))</f>
@@ -4969,7 +5087,7 @@
         <v>55</v>
       </c>
       <c r="Q29" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R29" s="23" t="n">
         <f aca="false">P29*INDEX(MarkupVals,MATCH(Q29,MarkupCodes,0))</f>
@@ -4981,7 +5099,7 @@
       </c>
       <c r="T29" s="25"/>
       <c r="U29" s="26" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4989,19 +5107,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G30" s="20" t="n">
         <f aca="false">ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares</f>
@@ -5011,7 +5129,7 @@
         <v>160</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="J30" s="23" t="n">
         <f aca="false">H30*INDEX(MarkupVals,MATCH(I30,MarkupCodes,0))</f>
@@ -5025,7 +5143,7 @@
         <v>160</v>
       </c>
       <c r="M30" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="N30" s="23" t="n">
         <f aca="false">L30*INDEX(MarkupVals,MATCH(M30,MarkupCodes,0))</f>
@@ -5039,7 +5157,7 @@
         <v>160</v>
       </c>
       <c r="Q30" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="R30" s="23" t="n">
         <f aca="false">P30*INDEX(MarkupVals,MATCH(Q30,MarkupCodes,0))</f>
@@ -5051,7 +5169,7 @@
       </c>
       <c r="T30" s="25"/>
       <c r="U30" s="26" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5059,19 +5177,19 @@
         <v>27</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="G31" s="20" t="n">
         <f aca="false">2*(1 - p_Addition_Detached)</f>
@@ -5081,7 +5199,7 @@
         <v>150</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="J31" s="23" t="n">
         <f aca="false">H31*INDEX(MarkupVals,MATCH(I31,MarkupCodes,0))</f>
@@ -5095,7 +5213,7 @@
         <v>150</v>
       </c>
       <c r="M31" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="N31" s="23" t="n">
         <f aca="false">L31*INDEX(MarkupVals,MATCH(M31,MarkupCodes,0))</f>
@@ -5109,7 +5227,7 @@
         <v>150</v>
       </c>
       <c r="Q31" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="R31" s="23" t="n">
         <f aca="false">P31*INDEX(MarkupVals,MATCH(Q31,MarkupCodes,0))</f>
@@ -5127,19 +5245,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="G32" s="20" t="n">
         <f aca="false">ROUNDUP(2.5*p_Addition_Windows,0)</f>
@@ -5150,7 +5268,7 @@
         <v>55</v>
       </c>
       <c r="I32" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J32" s="23" t="n">
         <f aca="false">H32*INDEX(MarkupVals,MATCH(I32,MarkupCodes,0))</f>
@@ -5165,7 +5283,7 @@
         <v>55</v>
       </c>
       <c r="M32" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N32" s="23" t="n">
         <f aca="false">L32*INDEX(MarkupVals,MATCH(M32,MarkupCodes,0))</f>
@@ -5180,7 +5298,7 @@
         <v>55</v>
       </c>
       <c r="Q32" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R32" s="23" t="n">
         <f aca="false">P32*INDEX(MarkupVals,MATCH(Q32,MarkupCodes,0))</f>
@@ -5198,16 +5316,16 @@
         <v>29</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F33" s="19" t="s">
         <v>96</v>
@@ -5220,7 +5338,7 @@
         <v>1230</v>
       </c>
       <c r="I33" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J33" s="23" t="n">
         <f aca="false">H33*INDEX(MarkupVals,MATCH(I33,MarkupCodes,0))</f>
@@ -5234,7 +5352,7 @@
         <v>1230</v>
       </c>
       <c r="M33" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N33" s="23" t="n">
         <f aca="false">L33*INDEX(MarkupVals,MATCH(M33,MarkupCodes,0))</f>
@@ -5248,7 +5366,7 @@
         <v>1230</v>
       </c>
       <c r="Q33" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R33" s="23" t="n">
         <f aca="false">P33*INDEX(MarkupVals,MATCH(Q33,MarkupCodes,0))</f>
@@ -5260,7 +5378,7 @@
       </c>
       <c r="T33" s="25"/>
       <c r="U33" s="26" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5268,16 +5386,16 @@
         <v>30</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F34" s="19" t="s">
         <v>102</v>
@@ -5290,7 +5408,7 @@
         <v>1300</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J34" s="23" t="n">
         <f aca="false">H34*INDEX(MarkupVals,MATCH(I34,MarkupCodes,0))</f>
@@ -5304,7 +5422,7 @@
         <v>1300</v>
       </c>
       <c r="M34" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N34" s="23" t="n">
         <f aca="false">L34*INDEX(MarkupVals,MATCH(M34,MarkupCodes,0))</f>
@@ -5318,7 +5436,7 @@
         <v>1300</v>
       </c>
       <c r="Q34" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="R34" s="23" t="n">
         <f aca="false">P34*INDEX(MarkupVals,MATCH(Q34,MarkupCodes,0))</f>
@@ -5330,7 +5448,7 @@
       </c>
       <c r="T34" s="25"/>
       <c r="U34" s="26" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5338,16 +5456,16 @@
         <v>31</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F35" s="19" t="s">
         <v>102</v>
@@ -5360,7 +5478,7 @@
         <v>105</v>
       </c>
       <c r="I35" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="J35" s="23" t="n">
         <f aca="false">H35*INDEX(MarkupVals,MATCH(I35,MarkupCodes,0))</f>
@@ -5374,7 +5492,7 @@
         <v>105</v>
       </c>
       <c r="M35" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="N35" s="23" t="n">
         <f aca="false">L35*INDEX(MarkupVals,MATCH(M35,MarkupCodes,0))</f>
@@ -5388,7 +5506,7 @@
         <v>105</v>
       </c>
       <c r="Q35" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="R35" s="23" t="n">
         <f aca="false">P35*INDEX(MarkupVals,MATCH(Q35,MarkupCodes,0))</f>
@@ -5406,19 +5524,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C36" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="D36" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="D36" s="18" t="s">
-        <v>261</v>
-      </c>
       <c r="E36" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G36" s="20" t="n">
         <f aca="false">8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors</f>
@@ -5429,7 +5547,7 @@
         <v>55</v>
       </c>
       <c r="I36" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J36" s="23" t="n">
         <f aca="false">H36*INDEX(MarkupVals,MATCH(I36,MarkupCodes,0))</f>
@@ -5444,7 +5562,7 @@
         <v>55</v>
       </c>
       <c r="M36" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N36" s="23" t="n">
         <f aca="false">L36*INDEX(MarkupVals,MATCH(M36,MarkupCodes,0))</f>
@@ -5459,7 +5577,7 @@
         <v>55</v>
       </c>
       <c r="Q36" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R36" s="23" t="n">
         <f aca="false">P36*INDEX(MarkupVals,MATCH(Q36,MarkupCodes,0))</f>
@@ -5477,16 +5595,16 @@
         <v>33</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F37" s="19" t="s">
         <v>111</v>
@@ -5499,7 +5617,7 @@
         <v>250</v>
       </c>
       <c r="I37" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J37" s="23" t="n">
         <f aca="false">H37*INDEX(MarkupVals,MATCH(I37,MarkupCodes,0))</f>
@@ -5513,7 +5631,7 @@
         <v>250</v>
       </c>
       <c r="M37" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N37" s="23" t="n">
         <f aca="false">L37*INDEX(MarkupVals,MATCH(M37,MarkupCodes,0))</f>
@@ -5527,7 +5645,7 @@
         <v>250</v>
       </c>
       <c r="Q37" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R37" s="23" t="n">
         <f aca="false">P37*INDEX(MarkupVals,MATCH(Q37,MarkupCodes,0))</f>
@@ -5539,7 +5657,7 @@
       </c>
       <c r="T37" s="25"/>
       <c r="U37" s="26" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5547,19 +5665,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G38" s="20" t="n">
         <f aca="false">9*p_Addition_Plumbing_Fixtures</f>
@@ -5570,7 +5688,7 @@
         <v>55</v>
       </c>
       <c r="I38" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J38" s="23" t="n">
         <f aca="false">H38*INDEX(MarkupVals,MATCH(I38,MarkupCodes,0))</f>
@@ -5585,7 +5703,7 @@
         <v>55</v>
       </c>
       <c r="M38" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N38" s="23" t="n">
         <f aca="false">L38*INDEX(MarkupVals,MATCH(M38,MarkupCodes,0))</f>
@@ -5600,7 +5718,7 @@
         <v>55</v>
       </c>
       <c r="Q38" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R38" s="23" t="n">
         <f aca="false">P38*INDEX(MarkupVals,MATCH(Q38,MarkupCodes,0))</f>
@@ -5618,16 +5736,16 @@
         <v>35</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F39" s="19" t="s">
         <v>114</v>
@@ -5640,7 +5758,7 @@
         <v>1310</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J39" s="23" t="n">
         <f aca="false">H39*INDEX(MarkupVals,MATCH(I39,MarkupCodes,0))</f>
@@ -5654,7 +5772,7 @@
         <v>1310</v>
       </c>
       <c r="M39" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N39" s="23" t="n">
         <f aca="false">L39*INDEX(MarkupVals,MATCH(M39,MarkupCodes,0))</f>
@@ -5668,7 +5786,7 @@
         <v>1310</v>
       </c>
       <c r="Q39" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="R39" s="23" t="n">
         <f aca="false">P39*INDEX(MarkupVals,MATCH(Q39,MarkupCodes,0))</f>
@@ -5680,7 +5798,7 @@
       </c>
       <c r="T39" s="25"/>
       <c r="U39" s="26" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5688,16 +5806,16 @@
         <v>36</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F40" s="19" t="s">
         <v>117</v>
@@ -5710,7 +5828,7 @@
         <v>7500</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J40" s="23" t="n">
         <f aca="false">H40*INDEX(MarkupVals,MATCH(I40,MarkupCodes,0))</f>
@@ -5724,7 +5842,7 @@
         <v>7500</v>
       </c>
       <c r="M40" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N40" s="23" t="n">
         <f aca="false">L40*INDEX(MarkupVals,MATCH(M40,MarkupCodes,0))</f>
@@ -5738,7 +5856,7 @@
         <v>7500</v>
       </c>
       <c r="Q40" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="R40" s="23" t="n">
         <f aca="false">P40*INDEX(MarkupVals,MATCH(Q40,MarkupCodes,0))</f>
@@ -5750,7 +5868,7 @@
       </c>
       <c r="T40" s="25"/>
       <c r="U40" s="26" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5758,19 +5876,19 @@
         <v>37</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G41" s="20" t="n">
         <f aca="false">p_Addition_Electrical*p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -5780,7 +5898,7 @@
         <v>2.61</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J41" s="23" t="n">
         <f aca="false">H41*INDEX(MarkupVals,MATCH(I41,MarkupCodes,0))</f>
@@ -5794,7 +5912,7 @@
         <v>2.61</v>
       </c>
       <c r="M41" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N41" s="23" t="n">
         <f aca="false">L41*INDEX(MarkupVals,MATCH(M41,MarkupCodes,0))</f>
@@ -5808,7 +5926,7 @@
         <v>2.61</v>
       </c>
       <c r="Q41" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R41" s="23" t="n">
         <f aca="false">P41*INDEX(MarkupVals,MATCH(Q41,MarkupCodes,0))</f>
@@ -5820,7 +5938,7 @@
       </c>
       <c r="T41" s="25"/>
       <c r="U41" s="26" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5828,19 +5946,19 @@
         <v>38</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G42" s="20" t="n">
         <f aca="false">p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0))</f>
@@ -5851,7 +5969,7 @@
         <v>55</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J42" s="23" t="n">
         <f aca="false">H42*INDEX(MarkupVals,MATCH(I42,MarkupCodes,0))</f>
@@ -5866,7 +5984,7 @@
         <v>55</v>
       </c>
       <c r="M42" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N42" s="23" t="n">
         <f aca="false">L42*INDEX(MarkupVals,MATCH(M42,MarkupCodes,0))</f>
@@ -5881,7 +5999,7 @@
         <v>55</v>
       </c>
       <c r="Q42" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R42" s="23" t="n">
         <f aca="false">P42*INDEX(MarkupVals,MATCH(Q42,MarkupCodes,0))</f>
@@ -5893,7 +6011,7 @@
       </c>
       <c r="T42" s="25"/>
       <c r="U42" s="26" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5901,19 +6019,19 @@
         <v>39</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="G43" s="20" t="n">
         <f aca="false">p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -5923,7 +6041,7 @@
         <v>8.52</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J43" s="23" t="n">
         <f aca="false">H43*INDEX(MarkupVals,MATCH(I43,MarkupCodes,0))</f>
@@ -5937,7 +6055,7 @@
         <v>8.52</v>
       </c>
       <c r="M43" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N43" s="23" t="n">
         <f aca="false">L43*INDEX(MarkupVals,MATCH(M43,MarkupCodes,0))</f>
@@ -5951,7 +6069,7 @@
         <v>8.52</v>
       </c>
       <c r="Q43" s="22" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="R43" s="23" t="n">
         <f aca="false">P43*INDEX(MarkupVals,MATCH(Q43,MarkupCodes,0))</f>
@@ -5963,7 +6081,7 @@
       </c>
       <c r="T43" s="25"/>
       <c r="U43" s="26" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5971,19 +6089,19 @@
         <v>40</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="G44" s="20" t="n">
         <f aca="false">p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -5993,7 +6111,7 @@
         <v>1.02</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J44" s="23" t="n">
         <f aca="false">H44*INDEX(MarkupVals,MATCH(I44,MarkupCodes,0))</f>
@@ -6007,7 +6125,7 @@
         <v>1.02</v>
       </c>
       <c r="M44" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N44" s="23" t="n">
         <f aca="false">L44*INDEX(MarkupVals,MATCH(M44,MarkupCodes,0))</f>
@@ -6021,7 +6139,7 @@
         <v>1.02</v>
       </c>
       <c r="Q44" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R44" s="23" t="n">
         <f aca="false">P44*INDEX(MarkupVals,MATCH(Q44,MarkupCodes,0))</f>
@@ -6033,7 +6151,7 @@
       </c>
       <c r="T44" s="25"/>
       <c r="U44" s="26" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6041,19 +6159,19 @@
         <v>41</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C45" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="F45" s="19" t="s">
         <v>294</v>
-      </c>
-      <c r="D45" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>289</v>
       </c>
       <c r="G45" s="20" t="n">
         <f aca="false">p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -6063,7 +6181,7 @@
         <v>1.31</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J45" s="23" t="n">
         <f aca="false">H45*INDEX(MarkupVals,MATCH(I45,MarkupCodes,0))</f>
@@ -6077,7 +6195,7 @@
         <v>1.31</v>
       </c>
       <c r="M45" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N45" s="23" t="n">
         <f aca="false">L45*INDEX(MarkupVals,MATCH(M45,MarkupCodes,0))</f>
@@ -6091,7 +6209,7 @@
         <v>1.31</v>
       </c>
       <c r="Q45" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R45" s="23" t="n">
         <f aca="false">P45*INDEX(MarkupVals,MATCH(Q45,MarkupCodes,0))</f>
@@ -6109,19 +6227,19 @@
         <v>42</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="G46" s="20" t="n">
         <f aca="false">p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0)</f>
@@ -6132,7 +6250,7 @@
         <v>55</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J46" s="23" t="n">
         <f aca="false">H46*INDEX(MarkupVals,MATCH(I46,MarkupCodes,0))</f>
@@ -6147,7 +6265,7 @@
         <v>55</v>
       </c>
       <c r="M46" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N46" s="23" t="n">
         <f aca="false">L46*INDEX(MarkupVals,MATCH(M46,MarkupCodes,0))</f>
@@ -6162,7 +6280,7 @@
         <v>55</v>
       </c>
       <c r="Q46" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R46" s="23" t="n">
         <f aca="false">P46*INDEX(MarkupVals,MATCH(Q46,MarkupCodes,0))</f>
@@ -6180,19 +6298,19 @@
         <v>43</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="G47" s="20" t="n">
         <f aca="false">p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/60,0)</f>
@@ -6202,7 +6320,7 @@
         <v>85</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J47" s="23" t="n">
         <f aca="false">H47*INDEX(MarkupVals,MATCH(I47,MarkupCodes,0))</f>
@@ -6216,7 +6334,7 @@
         <v>85</v>
       </c>
       <c r="M47" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N47" s="23" t="n">
         <f aca="false">L47*INDEX(MarkupVals,MATCH(M47,MarkupCodes,0))</f>
@@ -6230,7 +6348,7 @@
         <v>85</v>
       </c>
       <c r="Q47" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R47" s="23" t="n">
         <f aca="false">P47*INDEX(MarkupVals,MATCH(Q47,MarkupCodes,0))</f>
@@ -6248,19 +6366,19 @@
         <v>44</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="G48" s="20" t="n">
         <f aca="false">p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0)</f>
@@ -6271,7 +6389,7 @@
         <v>55</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J48" s="23" t="n">
         <f aca="false">H48*INDEX(MarkupVals,MATCH(I48,MarkupCodes,0))</f>
@@ -6286,7 +6404,7 @@
         <v>55</v>
       </c>
       <c r="M48" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N48" s="23" t="n">
         <f aca="false">L48*INDEX(MarkupVals,MATCH(M48,MarkupCodes,0))</f>
@@ -6301,7 +6419,7 @@
         <v>55</v>
       </c>
       <c r="Q48" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R48" s="23" t="n">
         <f aca="false">P48*INDEX(MarkupVals,MATCH(Q48,MarkupCodes,0))</f>
@@ -6319,16 +6437,16 @@
         <v>45</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F49" s="19" t="s">
         <v>105</v>
@@ -6341,7 +6459,7 @@
         <v>400</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J49" s="23" t="n">
         <f aca="false">H49*INDEX(MarkupVals,MATCH(I49,MarkupCodes,0))</f>
@@ -6355,7 +6473,7 @@
         <v>400</v>
       </c>
       <c r="M49" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N49" s="23" t="n">
         <f aca="false">L49*INDEX(MarkupVals,MATCH(M49,MarkupCodes,0))</f>
@@ -6369,7 +6487,7 @@
         <v>400</v>
       </c>
       <c r="Q49" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R49" s="23" t="n">
         <f aca="false">P49*INDEX(MarkupVals,MATCH(Q49,MarkupCodes,0))</f>
@@ -6381,7 +6499,7 @@
       </c>
       <c r="T49" s="25"/>
       <c r="U49" s="26" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6389,19 +6507,19 @@
         <v>46</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G50" s="20" t="n">
         <f aca="false">p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -6411,7 +6529,7 @@
         <v>0.75</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J50" s="23" t="n">
         <f aca="false">H50*INDEX(MarkupVals,MATCH(I50,MarkupCodes,0))</f>
@@ -6425,7 +6543,7 @@
         <v>0.75</v>
       </c>
       <c r="M50" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N50" s="23" t="n">
         <f aca="false">L50*INDEX(MarkupVals,MATCH(M50,MarkupCodes,0))</f>
@@ -6439,7 +6557,7 @@
         <v>0.75</v>
       </c>
       <c r="Q50" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R50" s="23" t="n">
         <f aca="false">P50*INDEX(MarkupVals,MATCH(Q50,MarkupCodes,0))</f>
@@ -6457,19 +6575,19 @@
         <v>47</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="G51" s="20" t="n">
         <f aca="false">p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0)</f>
@@ -6480,7 +6598,7 @@
         <v>55</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J51" s="23" t="n">
         <f aca="false">H51*INDEX(MarkupVals,MATCH(I51,MarkupCodes,0))</f>
@@ -6495,7 +6613,7 @@
         <v>55</v>
       </c>
       <c r="M51" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N51" s="23" t="n">
         <f aca="false">L51*INDEX(MarkupVals,MATCH(M51,MarkupCodes,0))</f>
@@ -6510,7 +6628,7 @@
         <v>55</v>
       </c>
       <c r="Q51" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R51" s="23" t="n">
         <f aca="false">P51*INDEX(MarkupVals,MATCH(Q51,MarkupCodes,0))</f>
@@ -6528,19 +6646,19 @@
         <v>48</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="G52" s="20" t="n">
         <f aca="false">p_Addition_Living_Space*ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/12,0)</f>
@@ -6550,7 +6668,7 @@
         <v>45.49</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J52" s="23" t="n">
         <f aca="false">H52*INDEX(MarkupVals,MATCH(I52,MarkupCodes,0))</f>
@@ -6564,7 +6682,7 @@
         <v>45.49</v>
       </c>
       <c r="M52" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N52" s="23" t="n">
         <f aca="false">L52*INDEX(MarkupVals,MATCH(M52,MarkupCodes,0))</f>
@@ -6578,7 +6696,7 @@
         <v>45.49</v>
       </c>
       <c r="Q52" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R52" s="23" t="n">
         <f aca="false">P52*INDEX(MarkupVals,MATCH(Q52,MarkupCodes,0))</f>
@@ -6596,19 +6714,19 @@
         <v>49</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="G53" s="20" t="n">
         <f aca="false">p_Addition_Living_Space*(p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors)</f>
@@ -6618,7 +6736,7 @@
         <v>37.11</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J53" s="23" t="n">
         <f aca="false">H53*INDEX(MarkupVals,MATCH(I53,MarkupCodes,0))</f>
@@ -6632,7 +6750,7 @@
         <v>37.11</v>
       </c>
       <c r="M53" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N53" s="23" t="n">
         <f aca="false">L53*INDEX(MarkupVals,MATCH(M53,MarkupCodes,0))</f>
@@ -6646,7 +6764,7 @@
         <v>37.11</v>
       </c>
       <c r="Q53" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R53" s="23" t="n">
         <f aca="false">P53*INDEX(MarkupVals,MATCH(Q53,MarkupCodes,0))</f>
@@ -6664,19 +6782,19 @@
         <v>50</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G54" s="20" t="n">
         <f aca="false">p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors)</f>
@@ -6687,7 +6805,7 @@
         <v>55</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J54" s="23" t="n">
         <f aca="false">H54*INDEX(MarkupVals,MATCH(I54,MarkupCodes,0))</f>
@@ -6702,7 +6820,7 @@
         <v>55</v>
       </c>
       <c r="M54" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N54" s="23" t="n">
         <f aca="false">L54*INDEX(MarkupVals,MATCH(M54,MarkupCodes,0))</f>
@@ -6717,7 +6835,7 @@
         <v>55</v>
       </c>
       <c r="Q54" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R54" s="23" t="n">
         <f aca="false">P54*INDEX(MarkupVals,MATCH(Q54,MarkupCodes,0))</f>
@@ -6735,19 +6853,19 @@
         <v>51</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="G55" s="20" t="n">
         <f aca="false">ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In</f>
@@ -6757,7 +6875,7 @@
         <v>210</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J55" s="23" t="n">
         <f aca="false">H55*INDEX(MarkupVals,MATCH(I55,MarkupCodes,0))</f>
@@ -6771,7 +6889,7 @@
         <v>245</v>
       </c>
       <c r="M55" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N55" s="23" t="n">
         <f aca="false">L55*INDEX(MarkupVals,MATCH(M55,MarkupCodes,0))</f>
@@ -6785,7 +6903,7 @@
         <v>313</v>
       </c>
       <c r="Q55" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R55" s="23" t="n">
         <f aca="false">P55*INDEX(MarkupVals,MATCH(Q55,MarkupCodes,0))</f>
@@ -6796,10 +6914,10 @@
         <v>2723.1</v>
       </c>
       <c r="T55" s="25" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="U55" s="26" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6807,19 +6925,19 @@
         <v>52</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="G56" s="20" t="n">
         <f aca="false">ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In</f>
@@ -6829,7 +6947,7 @@
         <v>95</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="J56" s="23" t="n">
         <f aca="false">H56*INDEX(MarkupVals,MATCH(I56,MarkupCodes,0))</f>
@@ -6843,7 +6961,7 @@
         <v>95</v>
       </c>
       <c r="M56" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="N56" s="23" t="n">
         <f aca="false">L56*INDEX(MarkupVals,MATCH(M56,MarkupCodes,0))</f>
@@ -6857,7 +6975,7 @@
         <v>200</v>
       </c>
       <c r="Q56" s="22" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="R56" s="23" t="n">
         <f aca="false">P56*INDEX(MarkupVals,MATCH(Q56,MarkupCodes,0))</f>
@@ -6869,7 +6987,7 @@
       </c>
       <c r="T56" s="25"/>
       <c r="U56" s="26" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6877,19 +6995,19 @@
         <v>53</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G57" s="20" t="n">
         <f aca="false">ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares</f>
@@ -6899,7 +7017,7 @@
         <v>230</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J57" s="23" t="n">
         <f aca="false">H57*INDEX(MarkupVals,MATCH(I57,MarkupCodes,0))</f>
@@ -6913,7 +7031,7 @@
         <v>320</v>
       </c>
       <c r="M57" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N57" s="23" t="n">
         <f aca="false">L57*INDEX(MarkupVals,MATCH(M57,MarkupCodes,0))</f>
@@ -6927,7 +7045,7 @@
         <v>495</v>
       </c>
       <c r="Q57" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R57" s="23" t="n">
         <f aca="false">P57*INDEX(MarkupVals,MATCH(Q57,MarkupCodes,0))</f>
@@ -6938,10 +7056,10 @@
         <v>3588.75</v>
       </c>
       <c r="T57" s="25" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="U57" s="26" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6949,16 +7067,16 @@
         <v>54</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F58" s="19" t="s">
         <v>92</v>
@@ -6971,7 +7089,7 @@
         <v>475</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J58" s="23" t="n">
         <f aca="false">H58*INDEX(MarkupVals,MATCH(I58,MarkupCodes,0))</f>
@@ -6985,7 +7103,7 @@
         <v>700</v>
       </c>
       <c r="M58" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N58" s="23" t="n">
         <f aca="false">L58*INDEX(MarkupVals,MATCH(M58,MarkupCodes,0))</f>
@@ -6999,7 +7117,7 @@
         <v>1100</v>
       </c>
       <c r="Q58" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R58" s="23" t="n">
         <f aca="false">P58*INDEX(MarkupVals,MATCH(Q58,MarkupCodes,0))</f>
@@ -7010,10 +7128,10 @@
         <v>6380</v>
       </c>
       <c r="T58" s="25" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="U58" s="26" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7021,16 +7139,16 @@
         <v>55</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F59" s="19" t="s">
         <v>99</v>
@@ -7043,7 +7161,7 @@
         <v>1750</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J59" s="23" t="n">
         <f aca="false">H59*INDEX(MarkupVals,MATCH(I59,MarkupCodes,0))</f>
@@ -7057,7 +7175,7 @@
         <v>2500</v>
       </c>
       <c r="M59" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N59" s="23" t="n">
         <f aca="false">L59*INDEX(MarkupVals,MATCH(M59,MarkupCodes,0))</f>
@@ -7071,7 +7189,7 @@
         <v>3000</v>
       </c>
       <c r="Q59" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R59" s="23" t="n">
         <f aca="false">P59*INDEX(MarkupVals,MATCH(Q59,MarkupCodes,0))</f>
@@ -7082,10 +7200,10 @@
         <v>4350</v>
       </c>
       <c r="T59" s="25" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="U59" s="26" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7093,19 +7211,19 @@
         <v>56</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G60" s="20" t="n">
         <f aca="false">p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories</f>
@@ -7115,7 +7233,7 @@
         <v>3.5</v>
       </c>
       <c r="I60" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J60" s="23" t="n">
         <f aca="false">H60*INDEX(MarkupVals,MATCH(I60,MarkupCodes,0))</f>
@@ -7129,7 +7247,7 @@
         <v>5</v>
       </c>
       <c r="M60" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N60" s="23" t="n">
         <f aca="false">L60*INDEX(MarkupVals,MATCH(M60,MarkupCodes,0))</f>
@@ -7143,7 +7261,7 @@
         <v>9</v>
       </c>
       <c r="Q60" s="22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R60" s="23" t="n">
         <f aca="false">P60*INDEX(MarkupVals,MATCH(Q60,MarkupCodes,0))</f>
@@ -7154,40 +7272,40 @@
         <v>4176</v>
       </c>
       <c r="T60" s="25" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="U60" s="26" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="670.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="901.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="18" t="n">
         <v>57</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="G61" s="20" t="n">
-        <f aca="false">p_Addition_Contingency_Rate/100*((1)*290 + (6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0))*100 + (1)*217.5 + (4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0))*100 + (1 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/400,0) + 3*p_Addition_Living_Space)*435 + (4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings)*100 + (p_Addition_Dumpster_Loads)*450 + (2 + 2*p_Addition_Living_Space)*100 + (p_Addition_Travel_Hours)*100 + (p_Addition_Utility_Trench)*17.4 + (16*p_Addition_Site_Excavation)*100 + (2*p_Addition_Site_Excavation)*282.75 + (p_Addition_Crawl_Space*p_Addition_Width*p_Addition_Depth)*26.2015 + (p_Addition_Slab*p_Addition_Width*p_Addition_Depth)*30.45 + (p_Addition_Basement*p_Addition_Width*p_Addition_Depth)*47.85 + (p_Addition_Piers)*725 + (3*p_Addition_Piers)*100 + (p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*32.625 + (p_Addition_Wall_Openings)*580 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In)*100 + (p_Addition_Width + p_Addition_Depth + 20)*11.9625 + (p_Addition_Width + p_Addition_Depth + 20)*5.075 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*11.6 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*5.85 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*100 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*232 + (2*(1 - p_Addition_Detached))*217.5 + (ROUNDUP(2.5*p_Addition_Windows,0))*100 + (p_Addition_Exterior_Doors)*1783.5 + (p_Addition_Garage_Doors)*1690 + (p_Addition_Garage_Doors)*152.25 + (8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors)*100 + (p_Addition_Plumbing_Fixtures)*362.5 + (9*p_Addition_Plumbing_Fixtures)*100 + (p_Addition_HVAC_Extend)*1703 + (p_Addition_HVAC_New_Unit)*9750 + (p_Addition_Electrical*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*3.7845 + (p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0)))*100 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*11.076 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.479 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.8995 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0))*100 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/60,0))*123.25 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0))*100 + (p_Addition_Interior_Doors)*580 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.0875 + (p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0))*100 + (p_Addition_Living_Space*ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/12,0))*65.9605 + (p_Addition_Living_Space*(p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*53.8095 + (p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*100 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*304.5 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*137.75 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*333.5 + (p_Addition_Windows)*688.75 + (p_Addition_Patio_Doors)*2537.5 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*5.075)</f>
+        <f aca="false">p_Addition_Contingency_Rate/100*((p_Addition_Permit_Fee)*1.45 + (6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0))*100 + (1)*217.5 + (4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0))*100 + (1 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/400,0) + 3*p_Addition_Living_Space)*435 + (4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings)*100 + (p_Addition_Dumpster_Loads)*450 + (2 + 2*p_Addition_Living_Space)*100 + (ROUNDUP((p_Addition_Service_Zone - 1)*(p_Addition_Service_Zone + 2)/8*((6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0)) + (4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0)) + (4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings) + (2 + 2*p_Addition_Living_Space) + (16*p_Addition_Site_Excavation) + (3*p_Addition_Piers) + (ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In) + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares) + (ROUNDUP(2.5*p_Addition_Windows,0)) + (8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors) + (9*p_Addition_Plumbing_Fixtures) + (p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0))) + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0)) + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0)) + (p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0)) + (p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors)))/8,0))*100 + (p_Addition_Utility_Trench)*17.4 + (16*p_Addition_Site_Excavation)*100 + (2*p_Addition_Site_Excavation)*282.75 + (p_Addition_Crawl_Space*p_Addition_Width*p_Addition_Depth)*26.2015 + (p_Addition_Slab*p_Addition_Width*p_Addition_Depth)*30.45 + (p_Addition_Basement*p_Addition_Width*p_Addition_Depth)*47.85 + (p_Addition_Piers)*725 + (3*p_Addition_Piers)*100 + (p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*32.625 + (p_Addition_Wall_Openings)*580 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In)*100 + (p_Addition_Width + p_Addition_Depth + 20)*11.9625 + (p_Addition_Width + p_Addition_Depth + 20)*5.075 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*11.6 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*5.85 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*100 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*232 + (2*(1 - p_Addition_Detached))*217.5 + (ROUNDUP(2.5*p_Addition_Windows,0))*100 + (p_Addition_Exterior_Doors)*1783.5 + (p_Addition_Garage_Doors)*1690 + (p_Addition_Garage_Doors)*152.25 + (8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors)*100 + (p_Addition_Plumbing_Fixtures)*362.5 + (9*p_Addition_Plumbing_Fixtures)*100 + (p_Addition_HVAC_Extend)*1703 + (p_Addition_HVAC_New_Unit)*9750 + (p_Addition_Electrical*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*3.7845 + (p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0)))*100 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*11.076 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.479 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.8995 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0))*100 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/60,0))*123.25 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0))*100 + (p_Addition_Interior_Doors)*580 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.0875 + (p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0))*100 + (p_Addition_Living_Space*ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/12,0))*65.9605 + (p_Addition_Living_Space*(p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*53.8095 + (p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*100 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*304.5 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*137.75 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*333.5 + (p_Addition_Windows)*688.75 + (p_Addition_Patio_Doors)*2537.5 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*5.075)</f>
         <v>7025.681</v>
       </c>
       <c r="H61" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J61" s="23" t="n">
         <f aca="false">H61*INDEX(MarkupVals,MATCH(I61,MarkupCodes,0))</f>
@@ -7201,7 +7319,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="22" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="N61" s="23" t="n">
         <f aca="false">L61*INDEX(MarkupVals,MATCH(M61,MarkupCodes,0))</f>
@@ -7215,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="22" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="R61" s="23" t="n">
         <f aca="false">P61*INDEX(MarkupVals,MATCH(Q61,MarkupCodes,0))</f>
@@ -7227,37 +7345,37 @@
       </c>
       <c r="T61" s="25"/>
       <c r="U61" s="26" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="670.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="901.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="18" t="n">
         <v>58</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C62" s="18" t="s">
+        <v>348</v>
+      </c>
+      <c r="D62" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="D62" s="18" t="s">
-        <v>338</v>
-      </c>
       <c r="E62" s="18" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F62" s="27" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="G62" s="20" t="n">
-        <f aca="false">p_Addition_Contingency_Rate/100*((1)*290 + (6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0))*100 + (1)*217.5 + (4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0))*100 + (1 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/400,0) + 3*p_Addition_Living_Space)*435 + (4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings)*100 + (p_Addition_Dumpster_Loads)*450 + (2 + 2*p_Addition_Living_Space)*100 + (p_Addition_Travel_Hours)*100 + (p_Addition_Utility_Trench)*17.4 + (16*p_Addition_Site_Excavation)*100 + (2*p_Addition_Site_Excavation)*282.75 + (p_Addition_Crawl_Space*p_Addition_Width*p_Addition_Depth)*26.2015 + (p_Addition_Slab*p_Addition_Width*p_Addition_Depth)*30.45 + (p_Addition_Basement*p_Addition_Width*p_Addition_Depth)*47.85 + (p_Addition_Piers)*725 + (3*p_Addition_Piers)*100 + (p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*32.625 + (p_Addition_Wall_Openings)*580 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In)*100 + (p_Addition_Width + p_Addition_Depth + 20)*11.9625 + (p_Addition_Width + p_Addition_Depth + 20)*5.075 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*11.6 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*5.85 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*100 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*232 + (2*(1 - p_Addition_Detached))*217.5 + (ROUNDUP(2.5*p_Addition_Windows,0))*100 + (p_Addition_Exterior_Doors)*1783.5 + (p_Addition_Garage_Doors)*1690 + (p_Addition_Garage_Doors)*152.25 + (8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors)*100 + (p_Addition_Plumbing_Fixtures)*362.5 + (9*p_Addition_Plumbing_Fixtures)*100 + (p_Addition_HVAC_Extend)*1703 + (p_Addition_HVAC_New_Unit)*9750 + (p_Addition_Electrical*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*3.7845 + (p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0)))*100 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*11.076 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.479 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.8995 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0))*100 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/60,0))*123.25 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0))*100 + (p_Addition_Interior_Doors)*580 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.0875 + (p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0))*100 + (p_Addition_Living_Space*ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/12,0))*65.9605 + (p_Addition_Living_Space*(p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*53.8095 + (p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*100 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*355.25 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*137.75 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*464 + (p_Addition_Windows)*1015 + (p_Addition_Patio_Doors)*3625 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*7.25)</f>
+        <f aca="false">p_Addition_Contingency_Rate/100*((p_Addition_Permit_Fee)*1.45 + (6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0))*100 + (1)*217.5 + (4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0))*100 + (1 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/400,0) + 3*p_Addition_Living_Space)*435 + (4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings)*100 + (p_Addition_Dumpster_Loads)*450 + (2 + 2*p_Addition_Living_Space)*100 + (ROUNDUP((p_Addition_Service_Zone - 1)*(p_Addition_Service_Zone + 2)/8*((6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0)) + (4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0)) + (4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings) + (2 + 2*p_Addition_Living_Space) + (16*p_Addition_Site_Excavation) + (3*p_Addition_Piers) + (ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In) + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares) + (ROUNDUP(2.5*p_Addition_Windows,0)) + (8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors) + (9*p_Addition_Plumbing_Fixtures) + (p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0))) + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0)) + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0)) + (p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0)) + (p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors)))/8,0))*100 + (p_Addition_Utility_Trench)*17.4 + (16*p_Addition_Site_Excavation)*100 + (2*p_Addition_Site_Excavation)*282.75 + (p_Addition_Crawl_Space*p_Addition_Width*p_Addition_Depth)*26.2015 + (p_Addition_Slab*p_Addition_Width*p_Addition_Depth)*30.45 + (p_Addition_Basement*p_Addition_Width*p_Addition_Depth)*47.85 + (p_Addition_Piers)*725 + (3*p_Addition_Piers)*100 + (p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*32.625 + (p_Addition_Wall_Openings)*580 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In)*100 + (p_Addition_Width + p_Addition_Depth + 20)*11.9625 + (p_Addition_Width + p_Addition_Depth + 20)*5.075 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*11.6 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*5.85 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*100 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*232 + (2*(1 - p_Addition_Detached))*217.5 + (ROUNDUP(2.5*p_Addition_Windows,0))*100 + (p_Addition_Exterior_Doors)*1783.5 + (p_Addition_Garage_Doors)*1690 + (p_Addition_Garage_Doors)*152.25 + (8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors)*100 + (p_Addition_Plumbing_Fixtures)*362.5 + (9*p_Addition_Plumbing_Fixtures)*100 + (p_Addition_HVAC_Extend)*1703 + (p_Addition_HVAC_New_Unit)*9750 + (p_Addition_Electrical*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*3.7845 + (p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0)))*100 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*11.076 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.479 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.8995 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0))*100 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/60,0))*123.25 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0))*100 + (p_Addition_Interior_Doors)*580 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.0875 + (p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0))*100 + (p_Addition_Living_Space*ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/12,0))*65.9605 + (p_Addition_Living_Space*(p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*53.8095 + (p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*100 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*355.25 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*137.75 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*464 + (p_Addition_Windows)*1015 + (p_Addition_Patio_Doors)*3625 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*7.25)</f>
         <v>7430.231</v>
       </c>
       <c r="H62" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="22" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J62" s="23" t="n">
         <f aca="false">H62*INDEX(MarkupVals,MATCH(I62,MarkupCodes,0))</f>
@@ -7271,7 +7389,7 @@
         <v>1</v>
       </c>
       <c r="M62" s="22" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="N62" s="23" t="n">
         <f aca="false">L62*INDEX(MarkupVals,MATCH(M62,MarkupCodes,0))</f>
@@ -7285,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="22" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="R62" s="23" t="n">
         <f aca="false">P62*INDEX(MarkupVals,MATCH(Q62,MarkupCodes,0))</f>
@@ -7297,37 +7415,37 @@
       </c>
       <c r="T62" s="25"/>
       <c r="U62" s="26" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="670.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="901.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="18" t="n">
         <v>59</v>
       </c>
       <c r="B63" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="D63" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="F63" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="G63" s="20" t="n">
+        <f aca="false">p_Addition_Contingency_Rate/100*((p_Addition_Permit_Fee)*1.45 + (6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0))*100 + (1)*217.5 + (4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0))*100 + (1 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/400,0) + 3*p_Addition_Living_Space)*435 + (4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings)*100 + (p_Addition_Dumpster_Loads)*450 + (2 + 2*p_Addition_Living_Space)*100 + (ROUNDUP((p_Addition_Service_Zone - 1)*(p_Addition_Service_Zone + 2)/8*((6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0)) + (4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0)) + (4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings) + (2 + 2*p_Addition_Living_Space) + (16*p_Addition_Site_Excavation) + (3*p_Addition_Piers) + (ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In) + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares) + (ROUNDUP(2.5*p_Addition_Windows,0)) + (8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors) + (9*p_Addition_Plumbing_Fixtures) + (p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0))) + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0)) + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0)) + (p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0)) + (p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors)))/8,0))*100 + (p_Addition_Utility_Trench)*17.4 + (16*p_Addition_Site_Excavation)*100 + (2*p_Addition_Site_Excavation)*282.75 + (p_Addition_Crawl_Space*p_Addition_Width*p_Addition_Depth)*26.2015 + (p_Addition_Slab*p_Addition_Width*p_Addition_Depth)*30.45 + (p_Addition_Basement*p_Addition_Width*p_Addition_Depth)*47.85 + (p_Addition_Piers)*725 + (3*p_Addition_Piers)*100 + (p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*32.625 + (p_Addition_Wall_Openings)*580 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In)*100 + (p_Addition_Width + p_Addition_Depth + 20)*11.9625 + (p_Addition_Width + p_Addition_Depth + 20)*5.075 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*11.6 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*5.85 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*100 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*232 + (2*(1 - p_Addition_Detached))*217.5 + (ROUNDUP(2.5*p_Addition_Windows,0))*100 + (p_Addition_Exterior_Doors)*1783.5 + (p_Addition_Garage_Doors)*1690 + (p_Addition_Garage_Doors)*152.25 + (8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors)*100 + (p_Addition_Plumbing_Fixtures)*362.5 + (9*p_Addition_Plumbing_Fixtures)*100 + (p_Addition_HVAC_Extend)*1703 + (p_Addition_HVAC_New_Unit)*9750 + (p_Addition_Electrical*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*3.7845 + (p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0)))*100 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*11.076 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.479 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.8995 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0))*100 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/60,0))*123.25 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0))*100 + (p_Addition_Interior_Doors)*580 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.0875 + (p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0))*100 + (p_Addition_Living_Space*ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/12,0))*65.9605 + (p_Addition_Living_Space*(p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*53.8095 + (p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*100 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*453.85 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*290 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*717.75 + (p_Addition_Windows)*1595 + (p_Addition_Patio_Doors)*4350 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*13.05)</f>
+        <v>8197.716</v>
+      </c>
+      <c r="H63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="22" t="s">
         <v>345</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="D63" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="F63" s="27" t="s">
-        <v>347</v>
-      </c>
-      <c r="G63" s="20" t="n">
-        <f aca="false">p_Addition_Contingency_Rate/100*((1)*290 + (6 + p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/30,0))*100 + (1)*217.5 + (4 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/200,0))*100 + (1 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/400,0) + 3*p_Addition_Living_Space)*435 + (4*(1 - p_Addition_Detached) + ROUNDUP(p_Addition_Structure_Removed/3,0) + 8*p_Addition_Wall_Openings)*100 + (p_Addition_Dumpster_Loads)*450 + (2 + 2*p_Addition_Living_Space)*100 + (p_Addition_Travel_Hours)*100 + (p_Addition_Utility_Trench)*17.4 + (16*p_Addition_Site_Excavation)*100 + (2*p_Addition_Site_Excavation)*282.75 + (p_Addition_Crawl_Space*p_Addition_Width*p_Addition_Depth)*26.2015 + (p_Addition_Slab*p_Addition_Width*p_Addition_Depth)*30.45 + (p_Addition_Basement*p_Addition_Width*p_Addition_Depth)*47.85 + (p_Addition_Piers)*725 + (3*p_Addition_Piers)*100 + (p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*32.625 + (p_Addition_Wall_Openings)*580 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/6,0) + 8*p_Addition_Wall_Openings + 8*p_Addition_Roof_Tie_In)*100 + (p_Addition_Width + p_Addition_Depth + 20)*11.9625 + (p_Addition_Width + p_Addition_Depth + 20)*5.075 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*11.6 + ((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width))*5.85 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*100 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*232 + (2*(1 - p_Addition_Detached))*217.5 + (ROUNDUP(2.5*p_Addition_Windows,0))*100 + (p_Addition_Exterior_Doors)*1783.5 + (p_Addition_Garage_Doors)*1690 + (p_Addition_Garage_Doors)*152.25 + (8*p_Addition_Exterior_Doors + 8*p_Addition_Patio_Doors + 3*p_Addition_Interior_Doors)*100 + (p_Addition_Plumbing_Fixtures)*362.5 + (9*p_Addition_Plumbing_Fixtures)*100 + (p_Addition_HVAC_Extend)*1703 + (p_Addition_HVAC_New_Unit)*9750 + (p_Addition_Electrical*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*3.7845 + (p_Addition_Electrical*(8 + ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/16,0)))*100 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*11.076 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.479 + (p_Addition_Drywall*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.8995 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/12,0))*100 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/60,0))*123.25 + (p_Addition_Drywall*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/15,0))*100 + (p_Addition_Interior_Doors)*580 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*1.0875 + (p_Addition_Living_Space*ROUNDUP(p_Addition_Width*p_Addition_Depth*p_Addition_Stories/25,0))*100 + (p_Addition_Living_Space*ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/12,0))*65.9605 + (p_Addition_Living_Space*(p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*53.8095 + (p_Addition_Living_Space*(4 + ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Stories/8,0) + p_Addition_Windows + p_Addition_Exterior_Doors + p_Addition_Patio_Doors))*100 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*453.85 + (ROUNDUP(p_Addition_Width*p_Addition_Depth*1.25/100,0) + 2*p_Addition_Roof_Tie_In)*290 + (ROUNDUP((p_Addition_Width + 2*p_Addition_Depth + p_Addition_Detached*p_Addition_Width)*p_Addition_Wall_Height*p_Addition_Stories*1.15/100,0) + p_Addition_Extra_Siding_Squares)*717.75 + (p_Addition_Windows)*1595 + (p_Addition_Patio_Doors)*4350 + (p_Addition_Living_Space*p_Addition_Width*p_Addition_Depth*p_Addition_Stories)*13.05)</f>
-        <v>8197.716</v>
-      </c>
-      <c r="H63" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="22" t="s">
-        <v>340</v>
       </c>
       <c r="J63" s="23" t="n">
         <f aca="false">H63*INDEX(MarkupVals,MATCH(I63,MarkupCodes,0))</f>
@@ -7341,7 +7459,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="22" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="N63" s="23" t="n">
         <f aca="false">L63*INDEX(MarkupVals,MATCH(M63,MarkupCodes,0))</f>
@@ -7355,7 +7473,7 @@
         <v>1</v>
       </c>
       <c r="Q63" s="22" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="R63" s="23" t="n">
         <f aca="false">P63*INDEX(MarkupVals,MATCH(Q63,MarkupCodes,0))</f>
@@ -7367,14 +7485,14 @@
       </c>
       <c r="T63" s="25"/>
       <c r="U63" s="26" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="15" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
@@ -7420,7 +7538,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -7432,7 +7550,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -7441,7 +7559,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -7457,19 +7575,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7477,7 +7595,7 @@
         <v>36</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C5" s="28" t="n">
         <v>20</v>
@@ -7486,7 +7604,7 @@
         <v>37</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7494,7 +7612,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C6" s="28" t="n">
         <v>16</v>
@@ -7503,7 +7621,7 @@
         <v>41</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7511,7 +7629,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C7" s="28" t="n">
         <v>1</v>
@@ -7520,7 +7638,7 @@
         <v>45</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7528,7 +7646,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C8" s="28" t="n">
         <v>8</v>
@@ -7537,7 +7655,7 @@
         <v>49</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7545,7 +7663,7 @@
         <v>52</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C9" s="28" t="n">
         <v>0</v>
@@ -7554,7 +7672,7 @@
         <v>53</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7562,7 +7680,7 @@
         <v>56</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C10" s="28" t="n">
         <v>0</v>
@@ -7571,7 +7689,7 @@
         <v>57</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7579,7 +7697,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C11" s="28" t="n">
         <v>0</v>
@@ -7588,7 +7706,7 @@
         <v>61</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7596,7 +7714,7 @@
         <v>64</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C12" s="28" t="n">
         <v>0</v>
@@ -7605,7 +7723,7 @@
         <v>65</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7613,7 +7731,7 @@
         <v>68</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C13" s="28" t="n">
         <v>0</v>
@@ -7622,7 +7740,7 @@
         <v>69</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7630,7 +7748,7 @@
         <v>71</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C14" s="28" t="n">
         <v>0</v>
@@ -7639,7 +7757,7 @@
         <v>72</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7647,7 +7765,7 @@
         <v>75</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C15" s="28" t="n">
         <v>1</v>
@@ -7656,7 +7774,7 @@
         <v>76</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7664,7 +7782,7 @@
         <v>79</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C16" s="28" t="n">
         <v>1</v>
@@ -7673,7 +7791,7 @@
         <v>80</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7681,7 +7799,7 @@
         <v>83</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C17" s="28" t="n">
         <v>1</v>
@@ -7690,7 +7808,7 @@
         <v>84</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7698,7 +7816,7 @@
         <v>86</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C18" s="28" t="n">
         <v>1</v>
@@ -7707,7 +7825,7 @@
         <v>87</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7715,7 +7833,7 @@
         <v>90</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C19" s="28" t="n">
         <v>3</v>
@@ -7724,7 +7842,7 @@
         <v>91</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7732,7 +7850,7 @@
         <v>94</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C20" s="28" t="n">
         <v>0</v>
@@ -7741,7 +7859,7 @@
         <v>95</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7749,7 +7867,7 @@
         <v>97</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C21" s="28" t="n">
         <v>0</v>
@@ -7758,7 +7876,7 @@
         <v>98</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7766,7 +7884,7 @@
         <v>100</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C22" s="28" t="n">
         <v>0</v>
@@ -7775,7 +7893,7 @@
         <v>101</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7783,7 +7901,7 @@
         <v>103</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C23" s="28" t="n">
         <v>0</v>
@@ -7792,7 +7910,7 @@
         <v>104</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7800,7 +7918,7 @@
         <v>106</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C24" s="28" t="n">
         <v>1</v>
@@ -7809,7 +7927,7 @@
         <v>107</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7817,7 +7935,7 @@
         <v>109</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C25" s="28" t="n">
         <v>0</v>
@@ -7826,7 +7944,7 @@
         <v>110</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7834,7 +7952,7 @@
         <v>112</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C26" s="28" t="n">
         <v>0</v>
@@ -7843,7 +7961,7 @@
         <v>113</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7851,7 +7969,7 @@
         <v>115</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C27" s="28" t="n">
         <v>0</v>
@@ -7860,7 +7978,7 @@
         <v>116</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7868,7 +7986,7 @@
         <v>118</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C28" s="28" t="n">
         <v>0</v>
@@ -7877,7 +7995,7 @@
         <v>119</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7885,7 +8003,7 @@
         <v>121</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C29" s="28" t="n">
         <v>0</v>
@@ -7894,7 +8012,7 @@
         <v>122</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>184</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7902,7 +8020,7 @@
         <v>124</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C30" s="28" t="n">
         <v>0</v>
@@ -7911,7 +8029,7 @@
         <v>125</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7919,7 +8037,7 @@
         <v>127</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C31" s="28" t="n">
         <v>1</v>
@@ -7928,24 +8046,24 @@
         <v>128</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="27" t="s">
         <v>130</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C32" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" s="28" t="s">
         <v>131</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7953,7 +8071,7 @@
         <v>133</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C33" s="28" t="n">
         <v>10</v>
@@ -7962,6 +8080,23 @@
         <v>134</v>
       </c>
       <c r="E33" s="28"/>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="C34" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>163</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7979,18 +8114,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -8004,101 +8139,101 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C4" s="29" t="n">
         <f aca="false">C12/C11</f>
         <v>1.81818181818182</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C5" s="30" t="n">
         <v>1.45</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C6" s="30" t="n">
         <v>1.3</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C7" s="30" t="n">
         <v>1.45</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C8" s="30" t="n">
         <v>1.45</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C9" s="30" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8109,19 +8244,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="31" t="n">
         <v>55</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="31" t="n">
@@ -8137,15 +8272,187 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="32" t="n">
         <v>0.2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>393</v>
-      </c>
+        <v>399</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="18" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="18" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="18" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="18" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="18" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="18" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="18" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="7" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="B29" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="B30" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D30" s="6"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="B31" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D31" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -8163,7 +8470,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AN44"/>
+  <dimension ref="A1:AO44"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -8173,7 +8480,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>394</v>
+        <v>426</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -8214,10 +8521,11 @@
       <c r="AL1" s="6"/>
       <c r="AM1" s="6"/>
       <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>395</v>
+        <v>427</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -8258,10 +8566,11 @@
       <c r="AL2" s="6"/>
       <c r="AM2" s="6"/>
       <c r="AN2" s="6"/>
+      <c r="AO2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -8302,6 +8611,7 @@
       <c r="AL3" s="6"/>
       <c r="AM3" s="6"/>
       <c r="AN3" s="6"/>
+      <c r="AO3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
@@ -8344,10 +8654,11 @@
       <c r="AL4" s="6"/>
       <c r="AM4" s="6"/>
       <c r="AN4" s="6"/>
+      <c r="AO4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -8388,43 +8699,44 @@
       <c r="AL5" s="6"/>
       <c r="AM5" s="6"/>
       <c r="AN5" s="6"/>
+      <c r="AO5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>401</v>
+        <v>433</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>403</v>
+        <v>435</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>404</v>
+        <v>436</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>405</v>
+        <v>437</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>406</v>
+        <v>438</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>407</v>
+        <v>439</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>409</v>
+        <v>441</v>
       </c>
       <c r="M6" s="8" t="s">
         <v>36</v>
@@ -8510,16 +8822,19 @@
       <c r="AN6" s="8" t="s">
         <v>130</v>
       </c>
+      <c r="AO6" s="8" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>410</v>
+        <v>442</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>420</v>
@@ -8633,18 +8948,21 @@
         <v>1</v>
       </c>
       <c r="AN7" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AO7" s="18" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>414</v>
+        <v>446</v>
       </c>
       <c r="D8" s="18" t="n">
         <v>792</v>
@@ -8758,18 +9076,21 @@
         <v>1</v>
       </c>
       <c r="AN8" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AO8" s="18" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>415</v>
+        <v>447</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>416</v>
+        <v>448</v>
       </c>
       <c r="D9" s="18" t="n">
         <v>286</v>
@@ -8883,18 +9204,21 @@
         <v>1</v>
       </c>
       <c r="AN9" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AO9" s="18" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>417</v>
+        <v>449</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>418</v>
+        <v>450</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="D10" s="18" t="n">
         <v>576</v>
@@ -9008,18 +9332,21 @@
         <v>1</v>
       </c>
       <c r="AN10" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AO10" s="18" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>421</v>
+        <v>453</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>336</v>
@@ -9133,18 +9460,21 @@
         <v>1</v>
       </c>
       <c r="AN11" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AO11" s="18" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>423</v>
+        <v>455</v>
       </c>
       <c r="D12" s="18" t="n">
         <v>360</v>
@@ -9258,18 +9588,21 @@
         <v>1</v>
       </c>
       <c r="AN12" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AO12" s="18" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>424</v>
+        <v>456</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>425</v>
+        <v>457</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>426</v>
+        <v>458</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>273</v>
@@ -9383,18 +9716,21 @@
         <v>1</v>
       </c>
       <c r="AN13" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AO13" s="18" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>428</v>
+        <v>460</v>
       </c>
       <c r="D14" s="36" t="n">
         <v>336</v>
@@ -9508,7 +9844,10 @@
         <v>2</v>
       </c>
       <c r="AN14" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AO14" s="36" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9552,10 +9891,11 @@
       <c r="AL15" s="6"/>
       <c r="AM15" s="6"/>
       <c r="AN15" s="6"/>
+      <c r="AO15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>429</v>
+        <v>461</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -9599,10 +9939,11 @@
       <c r="AL16" s="6"/>
       <c r="AM16" s="6"/>
       <c r="AN16" s="6"/>
+      <c r="AO16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -9646,10 +9987,11 @@
       <c r="AL17" s="6"/>
       <c r="AM17" s="6"/>
       <c r="AN17" s="6"/>
+      <c r="AO17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>431</v>
+        <v>463</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -9693,6 +10035,7 @@
       <c r="AL18" s="6"/>
       <c r="AM18" s="6"/>
       <c r="AN18" s="6"/>
+      <c r="AO18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
@@ -9735,10 +10078,11 @@
       <c r="AL19" s="6"/>
       <c r="AM19" s="6"/>
       <c r="AN19" s="6"/>
+      <c r="AO19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>432</v>
+        <v>464</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -9779,10 +10123,11 @@
       <c r="AL20" s="6"/>
       <c r="AM20" s="6"/>
       <c r="AN20" s="6"/>
+      <c r="AO20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>433</v>
+        <v>465</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -9823,36 +10168,37 @@
       <c r="AL21" s="6"/>
       <c r="AM21" s="6"/>
       <c r="AN21" s="6"/>
+      <c r="AO21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>434</v>
+        <v>466</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8" t="s">
-        <v>410</v>
+        <v>442</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>415</v>
+        <v>447</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>417</v>
+        <v>449</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>424</v>
+        <v>456</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
@@ -9883,36 +10229,37 @@
       <c r="AL22" s="6"/>
       <c r="AM22" s="6"/>
       <c r="AN22" s="6"/>
+      <c r="AO22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>435</v>
+        <v>467</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="18" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>439</v>
+        <v>471</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>440</v>
+        <v>472</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>441</v>
+        <v>473</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>442</v>
+        <v>474</v>
       </c>
       <c r="K23" s="18" t="s">
-        <v>443</v>
+        <v>475</v>
       </c>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
@@ -9943,36 +10290,37 @@
       <c r="AL23" s="6"/>
       <c r="AM23" s="6"/>
       <c r="AN23" s="6"/>
+      <c r="AO23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>444</v>
+        <v>476</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="18" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>449</v>
+        <v>481</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>450</v>
+        <v>482</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>451</v>
+        <v>483</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>452</v>
+        <v>484</v>
       </c>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
@@ -10003,36 +10351,37 @@
       <c r="AL24" s="6"/>
       <c r="AM24" s="6"/>
       <c r="AN24" s="6"/>
+      <c r="AO24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>453</v>
+        <v>485</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="18" t="s">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>441</v>
+        <v>473</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>443</v>
+        <v>475</v>
       </c>
       <c r="J25" s="18" t="s">
-        <v>457</v>
+        <v>489</v>
       </c>
       <c r="K25" s="18" t="s">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
@@ -10063,36 +10412,37 @@
       <c r="AL25" s="6"/>
       <c r="AM25" s="6"/>
       <c r="AN25" s="6"/>
+      <c r="AO25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>459</v>
+        <v>491</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="18" t="s">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
@@ -10123,36 +10473,37 @@
       <c r="AL26" s="6"/>
       <c r="AM26" s="6"/>
       <c r="AN26" s="6"/>
+      <c r="AO26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="18" t="s">
-        <v>467</v>
+        <v>499</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>469</v>
+        <v>501</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="K27" s="18" t="s">
-        <v>471</v>
+        <v>503</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
@@ -10183,36 +10534,37 @@
       <c r="AL27" s="6"/>
       <c r="AM27" s="6"/>
       <c r="AN27" s="6"/>
+      <c r="AO27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="18" t="s">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="K28" s="18" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
@@ -10243,36 +10595,37 @@
       <c r="AL28" s="6"/>
       <c r="AM28" s="6"/>
       <c r="AN28" s="6"/>
+      <c r="AO28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="18" t="s">
-        <v>479</v>
+        <v>511</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="K29" s="18" t="s">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
@@ -10303,36 +10656,37 @@
       <c r="AL29" s="6"/>
       <c r="AM29" s="6"/>
       <c r="AN29" s="6"/>
+      <c r="AO29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="18" t="s">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="E30" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>517</v>
+      </c>
+      <c r="G30" s="18" t="s">
         <v>484</v>
       </c>
-      <c r="F30" s="18" t="s">
-        <v>485</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>452</v>
-      </c>
       <c r="H30" s="18" t="s">
-        <v>486</v>
+        <v>518</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>488</v>
+        <v>520</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
@@ -10363,6 +10717,7 @@
       <c r="AL30" s="6"/>
       <c r="AM30" s="6"/>
       <c r="AN30" s="6"/>
+      <c r="AO30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6"/>
@@ -10405,10 +10760,11 @@
       <c r="AL31" s="6"/>
       <c r="AM31" s="6"/>
       <c r="AN31" s="6"/>
+      <c r="AO31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>490</v>
+        <v>522</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -10449,14 +10805,15 @@
       <c r="AL32" s="6"/>
       <c r="AM32" s="6"/>
       <c r="AN32" s="6"/>
+      <c r="AO32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>410</v>
+        <v>442</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="11" t="s">
-        <v>491</v>
+        <v>523</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -10495,14 +10852,15 @@
       <c r="AL33" s="6"/>
       <c r="AM33" s="6"/>
       <c r="AN33" s="6"/>
+      <c r="AO33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="11" t="s">
-        <v>492</v>
+        <v>524</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -10541,14 +10899,15 @@
       <c r="AL34" s="6"/>
       <c r="AM34" s="6"/>
       <c r="AN34" s="6"/>
+      <c r="AO34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="11" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -10587,14 +10946,15 @@
       <c r="AL35" s="6"/>
       <c r="AM35" s="6"/>
       <c r="AN35" s="6"/>
+      <c r="AO35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>424</v>
+        <v>456</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="11" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -10633,14 +10993,15 @@
       <c r="AL36" s="6"/>
       <c r="AM36" s="6"/>
       <c r="AN36" s="6"/>
+      <c r="AO36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="11" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -10679,10 +11040,11 @@
       <c r="AL37" s="6"/>
       <c r="AM37" s="6"/>
       <c r="AN37" s="6"/>
+      <c r="AO37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -10723,14 +11085,15 @@
       <c r="AL38" s="6"/>
       <c r="AM38" s="6"/>
       <c r="AN38" s="6"/>
+      <c r="AO38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="11" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
@@ -10769,14 +11132,15 @@
       <c r="AL39" s="6"/>
       <c r="AM39" s="6"/>
       <c r="AN39" s="6"/>
+      <c r="AO39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>417</v>
+        <v>449</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="11" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -10815,6 +11179,7 @@
       <c r="AL40" s="6"/>
       <c r="AM40" s="6"/>
       <c r="AN40" s="6"/>
+      <c r="AO40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6"/>
@@ -10857,10 +11222,11 @@
       <c r="AL41" s="6"/>
       <c r="AM41" s="6"/>
       <c r="AN41" s="6"/>
+      <c r="AO41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -10901,10 +11267,11 @@
       <c r="AL42" s="6"/>
       <c r="AM42" s="6"/>
       <c r="AN42" s="6"/>
+      <c r="AO42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -10945,10 +11312,11 @@
       <c r="AL43" s="6"/>
       <c r="AM43" s="6"/>
       <c r="AN43" s="6"/>
+      <c r="AO43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -10989,6 +11357,7 @@
       <c r="AL44" s="6"/>
       <c r="AM44" s="6"/>
       <c r="AN44" s="6"/>
+      <c r="AO44" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
